--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_South_Kore" displayName="AveragesTable_South_Kore" ref="A1:DD7" headerRowCount="1">
-  <autoFilter ref="A1:DD7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_South_Kore" displayName="AveragesTable_South_Kore" ref="A1:DD13" headerRowCount="1">
+  <autoFilter ref="A1:DD13"/>
   <tableColumns count="108">
     <tableColumn id="1" name="team_name"/>
     <tableColumn id="2" name="total_games"/>
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD7"/>
+  <dimension ref="A1:DD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.4" customWidth="1" min="1" max="1"/>
@@ -1200,7 +1200,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1243,19 +1243,19 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL2" t="n">
         <v>3</v>
@@ -1264,19 +1264,19 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
         <v>2</v>
       </c>
       <c r="AP2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AR2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS2" t="n">
         <v>-1</v>
@@ -1285,49 +1285,49 @@
         <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
         <v>3</v>
       </c>
       <c r="BC2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD2" t="n">
         <v>-1</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="BF2" t="n">
         <v>4</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BH2" t="n">
         <v>9</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
@@ -1339,10 +1339,10 @@
         <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BN2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO2" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
         <v>100</v>
       </c>
       <c r="BT2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
@@ -1377,92 +1377,92 @@
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="inlineStr"/>
       <c r="CA2" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.06</v>
+        <v>3.53</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.19</v>
+        <v>3.8</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.76</v>
+        <v>3.78</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.36</v>
+        <v>2.81</v>
       </c>
       <c r="CH2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="n">
         <v>1.3</v>
       </c>
-      <c r="CI2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="CR2" t="inlineStr"/>
-      <c r="CS2" t="inlineStr"/>
-      <c r="CT2" t="inlineStr"/>
-      <c r="CU2" t="inlineStr"/>
-      <c r="CV2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1.39</v>
-      </c>
       <c r="DC2" t="n">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.16</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1508,10 +1508,10 @@
         <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1526,94 +1526,94 @@
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU3" t="n">
         <v>3</v>
       </c>
-      <c r="AU3" t="n">
-        <v>1</v>
-      </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC3" t="n">
         <v>3</v>
       </c>
       <c r="BD3" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.44</v>
+        <v>1.09</v>
       </c>
       <c r="BF3" t="n">
         <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BI3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL3" t="n">
         <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BN3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BO3" t="n">
         <v>2</v>
       </c>
       <c r="BP3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1628,7 +1628,7 @@
         <v>100</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
@@ -1639,100 +1639,100 @@
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="inlineStr"/>
       <c r="CA3" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.04</v>
+        <v>4.67</v>
       </c>
       <c r="CC3" t="n">
-        <v>3</v>
+        <v>7.25</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.87</v>
+        <v>7.54</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="CF3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CG3" t="n">
         <v>3.1</v>
       </c>
-      <c r="CG3" t="n">
-        <v>2.41</v>
-      </c>
       <c r="CH3" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="CO3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CR3" t="n">
         <v>1.38</v>
       </c>
-      <c r="CP3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>1.5</v>
-      </c>
       <c r="CS3" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.67</v>
+        <v>3.12</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.24</v>
+        <v>1.84</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.04</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1748,19 +1748,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>6</v>
@@ -1769,16 +1769,16 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
         <v>18</v>
@@ -1787,43 +1787,43 @@
         <v>-1</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB4" t="n">
         <v>5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
       </c>
       <c r="AC4" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.96</v>
+        <v>1.68</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
@@ -1853,13 +1853,13 @@
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BH4" t="n">
         <v>9</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
@@ -1871,10 +1871,10 @@
         <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BN4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
@@ -1892,7 +1892,7 @@
         <v>100</v>
       </c>
       <c r="BT4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
         <v>0</v>
@@ -1907,94 +1907,94 @@
         <v>100</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.5</v>
+        <v>1.73</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.86</v>
+        <v>2.03</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.06</v>
+        <v>3.53</v>
       </c>
       <c r="CC4" t="inlineStr"/>
       <c r="CD4" t="inlineStr"/>
       <c r="CE4" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.36</v>
+        <v>2.81</v>
       </c>
       <c r="CH4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="n">
         <v>1.3</v>
       </c>
-      <c r="CI4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="CR4" t="inlineStr"/>
-      <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr"/>
-      <c r="CV4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CW4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CX4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DB4" t="n">
-        <v>1.39</v>
-      </c>
       <c r="DC4" t="n">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.16</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2040,112 +2040,112 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK5" t="n">
         <v>5</v>
       </c>
       <c r="AL5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP5" t="n">
         <v>3</v>
       </c>
       <c r="AQ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS5" t="n">
         <v>9</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD5" t="n">
         <v>12</v>
       </c>
-      <c r="AS5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>43</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA5" t="n">
+      <c r="BE5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
         <v>5</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BQ5" t="n">
         <v>4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>2</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
@@ -2154,7 +2154,7 @@
         <v>100</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
@@ -2171,248 +2171,240 @@
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="inlineStr"/>
       <c r="CA5" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.79</v>
+        <v>2.54</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>1.33</v>
-      </c>
+        <v>3.85</v>
+      </c>
+      <c r="CR5" t="inlineStr"/>
+      <c r="CS5" t="inlineStr"/>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DC5" t="n">
         <v>2.29</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.05</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>124</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>70</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>9</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>57</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>152</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
         <v>3</v>
       </c>
-      <c r="AB6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>99</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>66</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3</v>
+      </c>
       <c r="BG6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BH6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BI6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
         <v>1</v>
       </c>
       <c r="BN6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BQ6" t="n">
         <v>2</v>
@@ -2424,10 +2416,10 @@
         <v>100</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -2438,366 +2430,1978 @@
       <c r="BX6" t="n">
         <v>100</v>
       </c>
-      <c r="BY6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>3.01</v>
-      </c>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
       <c r="CA6" t="n">
         <v>3</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="CC6" t="inlineStr"/>
-      <c r="CD6" t="inlineStr"/>
+        <v>3.04</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>2.87</v>
+      </c>
       <c r="CE6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="CJ6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CK6" t="n">
         <v>1.73</v>
       </c>
-      <c r="CK6" t="n">
-        <v>1.79</v>
-      </c>
       <c r="CL6" t="n">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CU6" t="n">
         <v>1.33</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>107</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>49</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>66</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>99</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>51</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>16</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>80</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>44</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>14</v>
+      </c>
+      <c r="R9" t="n">
+        <v>12</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>124</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>70</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>11</v>
+      </c>
+      <c r="R10" t="n">
+        <v>8</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>102</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>49</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>124</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>70</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>52</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>3</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Ulsan</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>81</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
         <v>49</v>
       </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
         <v>10</v>
       </c>
-      <c r="Q7" t="n">
-        <v>15</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="Q13" t="n">
+        <v>17</v>
+      </c>
+      <c r="R13" t="n">
+        <v>9</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>35</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB13" t="n">
         <v>5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="n">
+      <c r="AC13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="n">
         <v>4</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BH13" t="n">
         <v>4</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BI13" t="n">
         <v>4</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR7" t="n">
+      <c r="BJ13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR13" t="n">
         <v>100</v>
       </c>
-      <c r="BS7" t="n">
+      <c r="BS13" t="n">
         <v>100</v>
       </c>
-      <c r="BT7" t="n">
+      <c r="BT13" t="n">
         <v>100</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="BU13" t="n">
         <v>100</v>
       </c>
-      <c r="BV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
         <v>100</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="BY13" t="n">
         <v>2.2</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="BZ13" t="n">
         <v>2.77</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CA13" t="n">
         <v>3</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CB13" t="n">
         <v>3.04</v>
       </c>
-      <c r="CC7" t="inlineStr"/>
-      <c r="CD7" t="inlineStr"/>
-      <c r="CE7" t="n">
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="n">
         <v>1.5</v>
       </c>
-      <c r="CF7" t="n">
+      <c r="CF13" t="n">
         <v>3.1</v>
       </c>
-      <c r="CG7" t="n">
+      <c r="CG13" t="n">
         <v>2.41</v>
       </c>
-      <c r="CH7" t="n">
+      <c r="CH13" t="n">
         <v>1.32</v>
       </c>
-      <c r="CI7" t="n">
+      <c r="CI13" t="n">
         <v>1.85</v>
       </c>
-      <c r="CJ7" t="n">
+      <c r="CJ13" t="n">
         <v>1.85</v>
       </c>
-      <c r="CK7" t="n">
+      <c r="CK13" t="n">
         <v>1.73</v>
       </c>
-      <c r="CL7" t="n">
+      <c r="CL13" t="n">
         <v>2.63</v>
       </c>
-      <c r="CM7" t="n">
+      <c r="CM13" t="n">
         <v>1.98</v>
       </c>
-      <c r="CN7" t="n">
+      <c r="CN13" t="n">
         <v>1.59</v>
       </c>
-      <c r="CO7" t="n">
+      <c r="CO13" t="n">
         <v>1.38</v>
       </c>
-      <c r="CP7" t="n">
+      <c r="CP13" t="n">
         <v>2.17</v>
       </c>
-      <c r="CQ7" t="n">
+      <c r="CQ13" t="n">
         <v>3.9</v>
       </c>
-      <c r="CR7" t="n">
+      <c r="CR13" t="n">
         <v>1.5</v>
       </c>
-      <c r="CS7" t="n">
+      <c r="CS13" t="n">
         <v>3.4</v>
       </c>
-      <c r="CT7" t="n">
+      <c r="CT13" t="n">
         <v>2.67</v>
       </c>
-      <c r="CU7" t="n">
+      <c r="CU13" t="n">
         <v>1.33</v>
       </c>
-      <c r="CV7" t="n">
+      <c r="CV13" t="n">
         <v>1.97</v>
       </c>
-      <c r="CW7" t="n">
+      <c r="CW13" t="n">
         <v>1.86</v>
       </c>
-      <c r="CX7" t="n">
+      <c r="CX13" t="n">
         <v>1.78</v>
       </c>
-      <c r="CY7" t="n">
+      <c r="CY13" t="n">
         <v>2.25</v>
       </c>
-      <c r="CZ7" t="n">
+      <c r="CZ13" t="n">
         <v>2.02</v>
       </c>
-      <c r="DA7" t="n">
+      <c r="DA13" t="n">
         <v>1.62</v>
       </c>
-      <c r="DB7" t="n">
+      <c r="DB13" t="n">
         <v>1.38</v>
       </c>
-      <c r="DC7" t="n">
+      <c r="DC13" t="n">
         <v>2.24</v>
       </c>
-      <c r="DD7" t="n">
+      <c r="DD13" t="n">
         <v>4.04</v>
       </c>
     </row>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -1276,10 +1276,10 @@
         <v>16</v>
       </c>
       <c r="AR2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
         <v>1</v>
@@ -1297,25 +1297,25 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="BF2" t="n">
         <v>4</v>
@@ -1781,10 +1781,10 @@
         <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1802,25 +1802,25 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AE4" t="n">
         <v>5</v>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -137,9 +137,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_South_Kore" displayName="AveragesTable_South_Kore" ref="A1:DD13" headerRowCount="1">
-  <autoFilter ref="A1:DD13"/>
-  <tableColumns count="108">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_South_Kore" displayName="AveragesTable_South_Kore" ref="A1:EC13" headerRowCount="1">
+  <autoFilter ref="A1:EC13"/>
+  <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>
     <tableColumn id="2" name="total_games"/>
     <tableColumn id="3" name="home_games"/>
@@ -248,6 +248,31 @@
     <tableColumn id="106" name="avg_pinnacle_ft_over15_odd"/>
     <tableColumn id="107" name="avg_pinnacle_ft_over25_odd"/>
     <tableColumn id="108" name="avg_pinnacle_ft_over35_odd"/>
+    <tableColumn id="109" name="total_avg_0_10_min_goals"/>
+    <tableColumn id="110" name="total_avg_2h_cards"/>
+    <tableColumn id="111" name="total_avg_2h_corners"/>
+    <tableColumn id="112" name="total_avg_attacks"/>
+    <tableColumn id="113" name="total_avg_cards_0_10_min"/>
+    <tableColumn id="114" name="total_avg_cards_num"/>
+    <tableColumn id="115" name="total_avg_corners"/>
+    <tableColumn id="116" name="total_avg_corners_0_10_min"/>
+    <tableColumn id="117" name="total_avg_dangerous_attacks"/>
+    <tableColumn id="118" name="total_avg_fh_cards"/>
+    <tableColumn id="119" name="total_avg_fh_corners"/>
+    <tableColumn id="120" name="total_avg_fouls"/>
+    <tableColumn id="121" name="total_avg_freekicks"/>
+    <tableColumn id="122" name="total_avg_goalkicks"/>
+    <tableColumn id="123" name="total_avg_penalties_won"/>
+    <tableColumn id="124" name="total_avg_penalty_goals"/>
+    <tableColumn id="125" name="total_avg_penalty_missed"/>
+    <tableColumn id="126" name="total_avg_possession"/>
+    <tableColumn id="127" name="total_avg_red_cards"/>
+    <tableColumn id="128" name="total_avg_shots"/>
+    <tableColumn id="129" name="total_avg_shotsOffTarget"/>
+    <tableColumn id="130" name="total_avg_shotsOnTarget"/>
+    <tableColumn id="131" name="total_avg_throwins"/>
+    <tableColumn id="132" name="total_avg_xg"/>
+    <tableColumn id="133" name="total_avg_yellow_cards"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -542,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD13"/>
+  <dimension ref="A1:EC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.4" customWidth="1" min="1" max="1"/>
@@ -653,6 +678,31 @@
     <col width="33.6" customWidth="1" min="106" max="106"/>
     <col width="33.6" customWidth="1" min="107" max="107"/>
     <col width="33.6" customWidth="1" min="108" max="108"/>
+    <col width="31.2" customWidth="1" min="109" max="109"/>
+    <col width="24" customWidth="1" min="110" max="110"/>
+    <col width="26.4" customWidth="1" min="111" max="111"/>
+    <col width="22.8" customWidth="1" min="112" max="112"/>
+    <col width="31.2" customWidth="1" min="113" max="113"/>
+    <col width="25.2" customWidth="1" min="114" max="114"/>
+    <col width="22.8" customWidth="1" min="115" max="115"/>
+    <col width="33.6" customWidth="1" min="116" max="116"/>
+    <col width="34.8" customWidth="1" min="117" max="117"/>
+    <col width="24" customWidth="1" min="118" max="118"/>
+    <col width="26.4" customWidth="1" min="119" max="119"/>
+    <col width="20.4" customWidth="1" min="120" max="120"/>
+    <col width="25.2" customWidth="1" min="121" max="121"/>
+    <col width="25.2" customWidth="1" min="122" max="122"/>
+    <col width="30" customWidth="1" min="123" max="123"/>
+    <col width="30" customWidth="1" min="124" max="124"/>
+    <col width="31.2" customWidth="1" min="125" max="125"/>
+    <col width="26.4" customWidth="1" min="126" max="126"/>
+    <col width="25.2" customWidth="1" min="127" max="127"/>
+    <col width="20.4" customWidth="1" min="128" max="128"/>
+    <col width="31.2" customWidth="1" min="129" max="129"/>
+    <col width="30" customWidth="1" min="130" max="130"/>
+    <col width="24" customWidth="1" min="131" max="131"/>
+    <col width="16.8" customWidth="1" min="132" max="132"/>
+    <col width="28.8" customWidth="1" min="133" max="133"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1194,6 +1244,131 @@
       <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_0_10_min_goals</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_2h_cards</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_2h_corners</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_attacks</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_cards_0_10_min</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_cards_num</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_corners</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_corners_0_10_min</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_fh_cards</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_fh_corners</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_fouls</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_freekicks</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_goalkicks</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_penalties_won</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_penalty_goals</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_penalty_missed</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_possession</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_red_cards</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_shots</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_shotsOffTarget</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_shotsOnTarget</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_throwins</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_xg</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_yellow_cards</t>
         </is>
       </c>
     </row>
@@ -1458,6 +1633,31 @@
       <c r="DD2" t="n">
         <v>3.36</v>
       </c>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="inlineStr"/>
+      <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="inlineStr"/>
+      <c r="DM2" t="inlineStr"/>
+      <c r="DN2" t="inlineStr"/>
+      <c r="DO2" t="inlineStr"/>
+      <c r="DP2" t="inlineStr"/>
+      <c r="DQ2" t="inlineStr"/>
+      <c r="DR2" t="inlineStr"/>
+      <c r="DS2" t="inlineStr"/>
+      <c r="DT2" t="inlineStr"/>
+      <c r="DU2" t="inlineStr"/>
+      <c r="DV2" t="inlineStr"/>
+      <c r="DW2" t="inlineStr"/>
+      <c r="DX2" t="inlineStr"/>
+      <c r="DY2" t="inlineStr"/>
+      <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1466,41 +1666,95 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>79</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>43</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
@@ -1583,37 +1837,37 @@
         <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BI3" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1622,13 +1876,13 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
@@ -1636,13 +1890,17 @@
       <c r="BX3" t="n">
         <v>100</v>
       </c>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
+      <c r="BY3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>3.84</v>
+      </c>
       <c r="CA3" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.67</v>
+        <v>4.04</v>
       </c>
       <c r="CC3" t="n">
         <v>7.25</v>
@@ -1651,43 +1909,43 @@
         <v>7.54</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="CK3" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -1702,31 +1960,106 @@
         <v>1.44</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="CX3" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.12</v>
+        <v>3.27</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>51</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>10</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>37</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>6</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>9</v>
+      </c>
+      <c r="EB3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="EC3" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
@@ -1736,13 +2069,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1825,38 +2158,92 @@
       <c r="AE4" t="n">
         <v>5</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>146</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>79</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
       <c r="BG4" t="n">
         <v>2</v>
       </c>
       <c r="BH4" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BI4" t="n">
         <v>2</v>
@@ -1883,7 +2270,7 @@
         <v>5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -1913,51 +2300,55 @@
         <v>2.03</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="CC4" t="inlineStr"/>
-      <c r="CD4" t="inlineStr"/>
+        <v>3.47</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>2.08</v>
+      </c>
       <c r="CE4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="CR4" t="n">
         <v>1.41</v>
@@ -1972,23 +2363,106 @@
         <v>1.4</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="inlineStr"/>
-      <c r="DA4" t="inlineStr"/>
+        <v>1.78</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>1.68</v>
+      </c>
       <c r="DB4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>145</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>60</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>11</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>7</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>4</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>9</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -2252,6 +2726,31 @@
       <c r="DD5" t="n">
         <v>4.16</v>
       </c>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
+      <c r="DH5" t="inlineStr"/>
+      <c r="DI5" t="inlineStr"/>
+      <c r="DJ5" t="inlineStr"/>
+      <c r="DK5" t="inlineStr"/>
+      <c r="DL5" t="inlineStr"/>
+      <c r="DM5" t="inlineStr"/>
+      <c r="DN5" t="inlineStr"/>
+      <c r="DO5" t="inlineStr"/>
+      <c r="DP5" t="inlineStr"/>
+      <c r="DQ5" t="inlineStr"/>
+      <c r="DR5" t="inlineStr"/>
+      <c r="DS5" t="inlineStr"/>
+      <c r="DT5" t="inlineStr"/>
+      <c r="DU5" t="inlineStr"/>
+      <c r="DV5" t="inlineStr"/>
+      <c r="DW5" t="inlineStr"/>
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr"/>
+      <c r="DZ5" t="inlineStr"/>
+      <c r="EA5" t="inlineStr"/>
+      <c r="EB5" t="inlineStr"/>
+      <c r="EC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2522,6 +3021,31 @@
       <c r="DD6" t="n">
         <v>4.04</v>
       </c>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="inlineStr"/>
+      <c r="DG6" t="inlineStr"/>
+      <c r="DH6" t="inlineStr"/>
+      <c r="DI6" t="inlineStr"/>
+      <c r="DJ6" t="inlineStr"/>
+      <c r="DK6" t="inlineStr"/>
+      <c r="DL6" t="inlineStr"/>
+      <c r="DM6" t="inlineStr"/>
+      <c r="DN6" t="inlineStr"/>
+      <c r="DO6" t="inlineStr"/>
+      <c r="DP6" t="inlineStr"/>
+      <c r="DQ6" t="inlineStr"/>
+      <c r="DR6" t="inlineStr"/>
+      <c r="DS6" t="inlineStr"/>
+      <c r="DT6" t="inlineStr"/>
+      <c r="DU6" t="inlineStr"/>
+      <c r="DV6" t="inlineStr"/>
+      <c r="DW6" t="inlineStr"/>
+      <c r="DX6" t="inlineStr"/>
+      <c r="DY6" t="inlineStr"/>
+      <c r="DZ6" t="inlineStr"/>
+      <c r="EA6" t="inlineStr"/>
+      <c r="EB6" t="inlineStr"/>
+      <c r="EC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2530,41 +3054,95 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>106</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>39</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>20</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
@@ -2647,66 +3225,70 @@
         <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
         <v>2</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY7" t="inlineStr"/>
-      <c r="BZ7" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>3.79</v>
+      </c>
       <c r="CA7" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="CC7" t="n">
         <v>3.14</v>
@@ -2715,40 +3297,40 @@
         <v>3.42</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.48</v>
+        <v>2.11</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="CQ7" t="n">
         <v>4.65</v>
@@ -2760,37 +3342,112 @@
         <v>3.34</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CU7" t="n">
         <v>1.34</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="CY7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
         <v>2.5</v>
       </c>
-      <c r="CZ7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>4.98</v>
+      <c r="DK7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>44</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>14</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>56</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>4</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>9</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -2800,13 +3457,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2889,65 +3546,119 @@
       <c r="AE8" t="n">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>124</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>93</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>54</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4</v>
+      </c>
       <c r="BG8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH8" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BN8" t="n">
         <v>3</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -2959,10 +3670,10 @@
         <v>100</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -2977,82 +3688,165 @@
         <v>2.86</v>
       </c>
       <c r="CA8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CB8" t="n">
         <v>2.96</v>
       </c>
-      <c r="CB8" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="CC8" t="inlineStr"/>
-      <c r="CD8" t="inlineStr"/>
+      <c r="CC8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>2.39</v>
+      </c>
       <c r="CE8" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.54</v>
+        <v>2.14</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="CR8" t="inlineStr"/>
+        <v>4.25</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>1.61</v>
+      </c>
       <c r="CS8" t="inlineStr"/>
-      <c r="CT8" t="inlineStr"/>
+      <c r="CT8" t="n">
+        <v>2.38</v>
+      </c>
       <c r="CU8" t="inlineStr"/>
       <c r="CV8" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="CX8" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.16</v>
+        <v>4.86</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>72</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>10</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -3324,6 +4118,31 @@
       <c r="DD9" t="n">
         <v>4.98</v>
       </c>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="inlineStr"/>
+      <c r="DG9" t="inlineStr"/>
+      <c r="DH9" t="inlineStr"/>
+      <c r="DI9" t="inlineStr"/>
+      <c r="DJ9" t="inlineStr"/>
+      <c r="DK9" t="inlineStr"/>
+      <c r="DL9" t="inlineStr"/>
+      <c r="DM9" t="inlineStr"/>
+      <c r="DN9" t="inlineStr"/>
+      <c r="DO9" t="inlineStr"/>
+      <c r="DP9" t="inlineStr"/>
+      <c r="DQ9" t="inlineStr"/>
+      <c r="DR9" t="inlineStr"/>
+      <c r="DS9" t="inlineStr"/>
+      <c r="DT9" t="inlineStr"/>
+      <c r="DU9" t="inlineStr"/>
+      <c r="DV9" t="inlineStr"/>
+      <c r="DW9" t="inlineStr"/>
+      <c r="DX9" t="inlineStr"/>
+      <c r="DY9" t="inlineStr"/>
+      <c r="DZ9" t="inlineStr"/>
+      <c r="EA9" t="inlineStr"/>
+      <c r="EB9" t="inlineStr"/>
+      <c r="EC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3594,6 +4413,31 @@
       <c r="DD10" t="n">
         <v>3.12</v>
       </c>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
+      <c r="DG10" t="inlineStr"/>
+      <c r="DH10" t="inlineStr"/>
+      <c r="DI10" t="inlineStr"/>
+      <c r="DJ10" t="inlineStr"/>
+      <c r="DK10" t="inlineStr"/>
+      <c r="DL10" t="inlineStr"/>
+      <c r="DM10" t="inlineStr"/>
+      <c r="DN10" t="inlineStr"/>
+      <c r="DO10" t="inlineStr"/>
+      <c r="DP10" t="inlineStr"/>
+      <c r="DQ10" t="inlineStr"/>
+      <c r="DR10" t="inlineStr"/>
+      <c r="DS10" t="inlineStr"/>
+      <c r="DT10" t="inlineStr"/>
+      <c r="DU10" t="inlineStr"/>
+      <c r="DV10" t="inlineStr"/>
+      <c r="DW10" t="inlineStr"/>
+      <c r="DX10" t="inlineStr"/>
+      <c r="DY10" t="inlineStr"/>
+      <c r="DZ10" t="inlineStr"/>
+      <c r="EA10" t="inlineStr"/>
+      <c r="EB10" t="inlineStr"/>
+      <c r="EC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3864,6 +4708,31 @@
       <c r="DD11" t="n">
         <v>4.05</v>
       </c>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="inlineStr"/>
+      <c r="DG11" t="inlineStr"/>
+      <c r="DH11" t="inlineStr"/>
+      <c r="DI11" t="inlineStr"/>
+      <c r="DJ11" t="inlineStr"/>
+      <c r="DK11" t="inlineStr"/>
+      <c r="DL11" t="inlineStr"/>
+      <c r="DM11" t="inlineStr"/>
+      <c r="DN11" t="inlineStr"/>
+      <c r="DO11" t="inlineStr"/>
+      <c r="DP11" t="inlineStr"/>
+      <c r="DQ11" t="inlineStr"/>
+      <c r="DR11" t="inlineStr"/>
+      <c r="DS11" t="inlineStr"/>
+      <c r="DT11" t="inlineStr"/>
+      <c r="DU11" t="inlineStr"/>
+      <c r="DV11" t="inlineStr"/>
+      <c r="DW11" t="inlineStr"/>
+      <c r="DX11" t="inlineStr"/>
+      <c r="DY11" t="inlineStr"/>
+      <c r="DZ11" t="inlineStr"/>
+      <c r="EA11" t="inlineStr"/>
+      <c r="EB11" t="inlineStr"/>
+      <c r="EC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4134,6 +5003,31 @@
       <c r="DD12" t="n">
         <v>4.05</v>
       </c>
+      <c r="DE12" t="inlineStr"/>
+      <c r="DF12" t="inlineStr"/>
+      <c r="DG12" t="inlineStr"/>
+      <c r="DH12" t="inlineStr"/>
+      <c r="DI12" t="inlineStr"/>
+      <c r="DJ12" t="inlineStr"/>
+      <c r="DK12" t="inlineStr"/>
+      <c r="DL12" t="inlineStr"/>
+      <c r="DM12" t="inlineStr"/>
+      <c r="DN12" t="inlineStr"/>
+      <c r="DO12" t="inlineStr"/>
+      <c r="DP12" t="inlineStr"/>
+      <c r="DQ12" t="inlineStr"/>
+      <c r="DR12" t="inlineStr"/>
+      <c r="DS12" t="inlineStr"/>
+      <c r="DT12" t="inlineStr"/>
+      <c r="DU12" t="inlineStr"/>
+      <c r="DV12" t="inlineStr"/>
+      <c r="DW12" t="inlineStr"/>
+      <c r="DX12" t="inlineStr"/>
+      <c r="DY12" t="inlineStr"/>
+      <c r="DZ12" t="inlineStr"/>
+      <c r="EA12" t="inlineStr"/>
+      <c r="EB12" t="inlineStr"/>
+      <c r="EC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4404,6 +5298,31 @@
       <c r="DD13" t="n">
         <v>4.04</v>
       </c>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="inlineStr"/>
+      <c r="DG13" t="inlineStr"/>
+      <c r="DH13" t="inlineStr"/>
+      <c r="DI13" t="inlineStr"/>
+      <c r="DJ13" t="inlineStr"/>
+      <c r="DK13" t="inlineStr"/>
+      <c r="DL13" t="inlineStr"/>
+      <c r="DM13" t="inlineStr"/>
+      <c r="DN13" t="inlineStr"/>
+      <c r="DO13" t="inlineStr"/>
+      <c r="DP13" t="inlineStr"/>
+      <c r="DQ13" t="inlineStr"/>
+      <c r="DR13" t="inlineStr"/>
+      <c r="DS13" t="inlineStr"/>
+      <c r="DT13" t="inlineStr"/>
+      <c r="DU13" t="inlineStr"/>
+      <c r="DV13" t="inlineStr"/>
+      <c r="DW13" t="inlineStr"/>
+      <c r="DX13" t="inlineStr"/>
+      <c r="DY13" t="inlineStr"/>
+      <c r="DZ13" t="inlineStr"/>
+      <c r="EA13" t="inlineStr"/>
+      <c r="EB13" t="inlineStr"/>
+      <c r="EC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -1379,41 +1379,95 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>91</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>52</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>16</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>4</v>
+      </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
@@ -1496,13 +1550,13 @@
         <v>4</v>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BH2" t="n">
         <v>9</v>
       </c>
       <c r="BI2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
@@ -1511,13 +1565,13 @@
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BM2" t="n">
         <v>1</v>
       </c>
       <c r="BN2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BO2" t="n">
         <v>0</v>
@@ -1535,7 +1589,7 @@
         <v>100</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
@@ -1549,13 +1603,17 @@
       <c r="BX2" t="n">
         <v>100</v>
       </c>
-      <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="inlineStr"/>
+      <c r="BY2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>2.26</v>
+      </c>
       <c r="CA2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.53</v>
+        <v>3.34</v>
       </c>
       <c r="CC2" t="n">
         <v>3.8</v>
@@ -1564,100 +1622,158 @@
         <v>3.78</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="CS2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
         <v>3</v>
       </c>
-      <c r="CT2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CX2" t="inlineStr"/>
-      <c r="CY2" t="inlineStr"/>
-      <c r="CZ2" t="inlineStr"/>
-      <c r="DA2" t="inlineStr"/>
-      <c r="DB2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="DE2" t="inlineStr"/>
-      <c r="DF2" t="inlineStr"/>
-      <c r="DG2" t="inlineStr"/>
-      <c r="DH2" t="inlineStr"/>
-      <c r="DI2" t="inlineStr"/>
-      <c r="DJ2" t="inlineStr"/>
-      <c r="DK2" t="inlineStr"/>
-      <c r="DL2" t="inlineStr"/>
-      <c r="DM2" t="inlineStr"/>
-      <c r="DN2" t="inlineStr"/>
-      <c r="DO2" t="inlineStr"/>
-      <c r="DP2" t="inlineStr"/>
-      <c r="DQ2" t="inlineStr"/>
-      <c r="DR2" t="inlineStr"/>
-      <c r="DS2" t="inlineStr"/>
-      <c r="DT2" t="inlineStr"/>
-      <c r="DU2" t="inlineStr"/>
-      <c r="DV2" t="inlineStr"/>
-      <c r="DW2" t="inlineStr"/>
-      <c r="DX2" t="inlineStr"/>
-      <c r="DY2" t="inlineStr"/>
-      <c r="DZ2" t="inlineStr"/>
-      <c r="EA2" t="inlineStr"/>
-      <c r="EB2" t="inlineStr"/>
-      <c r="EC2" t="inlineStr"/>
+      <c r="DG2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>4</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>56</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>4</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>8</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>2</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>6</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1711,11 +1827,11 @@
         <v>8</v>
       </c>
       <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
         <v>8</v>
       </c>
-      <c r="R3" t="n">
-        <v>-1</v>
-      </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
@@ -1732,25 +1848,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AB3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -2023,40 +2139,40 @@
         <v>10</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="DR3" t="n">
+        <v>7</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>6</v>
+      </c>
+      <c r="DZ3" t="n">
         <v>2.5</v>
       </c>
-      <c r="DS3" t="n">
-        <v>1</v>
-      </c>
-      <c r="DT3" t="n">
-        <v>1</v>
-      </c>
-      <c r="DU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV3" t="n">
-        <v>37</v>
-      </c>
-      <c r="DW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX3" t="n">
-        <v>6</v>
-      </c>
-      <c r="DY3" t="n">
-        <v>3</v>
-      </c>
-      <c r="DZ3" t="n">
-        <v>3</v>
-      </c>
       <c r="EA3" t="n">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="EC3" t="n">
         <v>1.5</v>
@@ -2195,10 +2311,10 @@
         <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
@@ -2216,25 +2332,25 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
         <v>2</v>
       </c>
       <c r="BD4" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
@@ -2426,10 +2542,10 @@
         <v>9.5</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2441,25 +2557,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>60</v>
+        <v>64.5</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="DY4" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="DZ4" t="n">
         <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="EC4" t="n">
         <v>2.5</v>
@@ -3066,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -3078,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -3099,10 +3215,10 @@
         <v>14</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -3120,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -3135,13 +3251,13 @@
         <v>5</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AD7" t="n">
         <v>1.03</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3378,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DG7" t="n">
         <v>2</v>
@@ -3390,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="DK7" t="n">
         <v>2</v>
@@ -3411,10 +3527,10 @@
         <v>14</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="DR7" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="DS7" t="n">
         <v>0.5</v>
@@ -3426,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>56</v>
+        <v>51.5</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
@@ -3441,13 +3557,13 @@
         <v>3.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="EB7" t="n">
         <v>1.05</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3583,10 +3699,10 @@
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
         <v>3</v>
@@ -3604,25 +3720,25 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
-        <v>-1</v>
+        <v>31</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="BF8" t="n">
         <v>4</v>
@@ -3810,10 +3926,10 @@
         <v>15.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="DR8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DS8" t="n">
         <v>0.5</v>
@@ -3825,25 +3941,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>54.5</v>
+        <v>59</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="EA8" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="EC8" t="n">
         <v>2</v>
@@ -3856,13 +3972,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -3945,41 +4061,95 @@
       <c r="AE9" t="n">
         <v>2</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>106</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>51</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1</v>
+      </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
@@ -3988,31 +4158,31 @@
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BO9" t="n">
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>4</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -4024,7 +4194,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.37</v>
@@ -4033,116 +4203,170 @@
         <v>2.36</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="CB9" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CC9" t="n">
         <v>3.1</v>
       </c>
-      <c r="CC9" t="inlineStr"/>
-      <c r="CD9" t="inlineStr"/>
+      <c r="CD9" t="n">
+        <v>3.66</v>
+      </c>
       <c r="CE9" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="CU9" t="n">
         <v>1.34</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="CY9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>93</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
         <v>2.5</v>
       </c>
-      <c r="CZ9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="DA9" t="n">
+      <c r="DK9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>42</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO9" t="n">
         <v>1.5</v>
       </c>
-      <c r="DB9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="DE9" t="inlineStr"/>
-      <c r="DF9" t="inlineStr"/>
-      <c r="DG9" t="inlineStr"/>
-      <c r="DH9" t="inlineStr"/>
-      <c r="DI9" t="inlineStr"/>
-      <c r="DJ9" t="inlineStr"/>
-      <c r="DK9" t="inlineStr"/>
-      <c r="DL9" t="inlineStr"/>
-      <c r="DM9" t="inlineStr"/>
-      <c r="DN9" t="inlineStr"/>
-      <c r="DO9" t="inlineStr"/>
-      <c r="DP9" t="inlineStr"/>
-      <c r="DQ9" t="inlineStr"/>
-      <c r="DR9" t="inlineStr"/>
-      <c r="DS9" t="inlineStr"/>
-      <c r="DT9" t="inlineStr"/>
-      <c r="DU9" t="inlineStr"/>
-      <c r="DV9" t="inlineStr"/>
-      <c r="DW9" t="inlineStr"/>
-      <c r="DX9" t="inlineStr"/>
-      <c r="DY9" t="inlineStr"/>
-      <c r="DZ9" t="inlineStr"/>
-      <c r="EA9" t="inlineStr"/>
-      <c r="EB9" t="inlineStr"/>
-      <c r="EC9" t="inlineStr"/>
+      <c r="DP9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4151,13 +4375,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4240,65 +4464,119 @@
       <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>114</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>51</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>49</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1</v>
+      </c>
       <c r="BG10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BH10" t="n">
         <v>5</v>
       </c>
-      <c r="BH10" t="n">
-        <v>6</v>
-      </c>
       <c r="BI10" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
         <v>1</v>
       </c>
       <c r="BM10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BN10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>3</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4307,13 +4585,13 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -4328,116 +4606,170 @@
         <v>1.43</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="CC10" t="inlineStr"/>
-      <c r="CD10" t="inlineStr"/>
+        <v>3.94</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>2.3</v>
+      </c>
       <c r="CE10" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="CK10" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.83</v>
+        <v>2.96</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="CX10" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="DE10" t="inlineStr"/>
-      <c r="DF10" t="inlineStr"/>
-      <c r="DG10" t="inlineStr"/>
-      <c r="DH10" t="inlineStr"/>
-      <c r="DI10" t="inlineStr"/>
-      <c r="DJ10" t="inlineStr"/>
-      <c r="DK10" t="inlineStr"/>
-      <c r="DL10" t="inlineStr"/>
-      <c r="DM10" t="inlineStr"/>
-      <c r="DN10" t="inlineStr"/>
-      <c r="DO10" t="inlineStr"/>
-      <c r="DP10" t="inlineStr"/>
-      <c r="DQ10" t="inlineStr"/>
-      <c r="DR10" t="inlineStr"/>
-      <c r="DS10" t="inlineStr"/>
-      <c r="DT10" t="inlineStr"/>
-      <c r="DU10" t="inlineStr"/>
-      <c r="DV10" t="inlineStr"/>
-      <c r="DW10" t="inlineStr"/>
-      <c r="DX10" t="inlineStr"/>
-      <c r="DY10" t="inlineStr"/>
-      <c r="DZ10" t="inlineStr"/>
-      <c r="EA10" t="inlineStr"/>
-      <c r="EB10" t="inlineStr"/>
-      <c r="EC10" t="inlineStr"/>
+        <v>3.3</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>119</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>12</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>9</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4741,25 +5073,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>124</v>
+        <v>119.5</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4771,61 +5103,61 @@
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>70</v>
+        <v>58.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
       <c r="P12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>12</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
         <v>9</v>
       </c>
-      <c r="Q12" t="n">
-        <v>11</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="AA12" t="n">
         <v>6</v>
       </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>52</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>9</v>
-      </c>
       <c r="AB12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC12" t="n">
-        <v>18</v>
+        <v>8.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.61</v>
+        <v>1.21</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -4861,34 +5193,34 @@
         <v>2</v>
       </c>
       <c r="BH12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BI12" t="n">
         <v>2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BM12" t="n">
         <v>1</v>
       </c>
       <c r="BN12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
@@ -4912,16 +5244,16 @@
         <v>100</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.01</v>
+        <v>3.24</v>
       </c>
       <c r="CA12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="CC12" t="inlineStr"/>
       <c r="CD12" t="inlineStr"/>
@@ -4929,79 +5261,79 @@
         <v>1.4</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="CJ12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CK12" t="n">
         <v>1.73</v>
       </c>
-      <c r="CK12" t="n">
-        <v>1.79</v>
-      </c>
       <c r="CL12" t="n">
-        <v>2.79</v>
+        <v>2.49</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.39</v>
+        <v>3.24</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.05</v>
+        <v>3.77</v>
       </c>
       <c r="DE12" t="inlineStr"/>
       <c r="DF12" t="inlineStr"/>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -1424,10 +1424,10 @@
         <v>11</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1451,19 +1451,19 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AE2" t="n">
         <v>4</v>
@@ -1736,10 +1736,10 @@
         <v>13.5</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="DR2" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="DS2" t="n">
         <v>1</v>
@@ -1757,19 +1757,19 @@
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="DY2" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="EA2" t="n">
-        <v>9.5</v>
+        <v>20</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="EC2" t="n">
         <v>4</v>
@@ -4098,10 +4098,10 @@
         <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
@@ -4125,19 +4125,19 @@
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
       </c>
       <c r="BD9" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BF9" t="n">
         <v>1</v>
@@ -4329,10 +4329,10 @@
         <v>12.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="DR9" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="DS9" t="n">
         <v>0.5</v>
@@ -4350,19 +4350,19 @@
         <v>0.5</v>
       </c>
       <c r="DX9" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="DY9" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="DZ9" t="n">
         <v>2.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>8.5</v>
+        <v>18.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="EC9" t="n">
         <v>1.5</v>
@@ -4501,10 +4501,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
         <v>1</v>
@@ -4528,19 +4528,19 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC10" t="n">
         <v>3</v>
       </c>
       <c r="BD10" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="BF10" t="n">
         <v>1</v>
@@ -4732,10 +4732,10 @@
         <v>12</v>
       </c>
       <c r="DQ10" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="DR10" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4753,19 +4753,19 @@
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="DZ10" t="n">
         <v>3.5</v>
       </c>
       <c r="EA10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="EC10" t="n">
         <v>1</v>
@@ -5118,10 +5118,10 @@
         <v>8.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -5145,19 +5145,19 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE4" t="n">
         <v>3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>15</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>5</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>2</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.5</v>
+        <v>9.33</v>
       </c>
       <c r="BI4" t="n">
         <v>2</v>
@@ -2368,25 +2368,25 @@
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="BL4" t="n">
         <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="BN4" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="BP4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2410,16 +2410,16 @@
         <v>100</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="CC4" t="n">
         <v>2.02</v>
@@ -2428,34 +2428,34 @@
         <v>2.08</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="CO4" t="n">
         <v>1.28</v>
@@ -2464,25 +2464,25 @@
         <v>1.92</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="CX4" t="n">
         <v>1.72</v>
@@ -2497,55 +2497,55 @@
         <v>1.68</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DG4" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DH4" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.5</v>
+        <v>-0.33</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="DL4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DM4" t="n">
-        <v>73.5</v>
+        <v>73</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.5</v>
+        <v>9.33</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.5</v>
+        <v>3.33</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>64.5</v>
+        <v>65.67</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.5</v>
+        <v>13.67</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.5</v>
+        <v>9.33</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.5</v>
+        <v>11.33</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -3185,10 +3185,10 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3197,13 +3197,13 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -3212,49 +3212,49 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q7" t="n">
         <v>15</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="n">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>16</v>
+        <v>7.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.03</v>
+        <v>0.74</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -3341,70 +3341,70 @@
         <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="BH7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="BP7" t="n">
         <v>2</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.5</v>
+        <v>3.67</v>
       </c>
       <c r="BR7" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.9</v>
+        <v>3.47</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.79</v>
+        <v>4.07</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="CB7" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="CC7" t="n">
         <v>3.14</v>
@@ -3413,82 +3413,82 @@
         <v>3.42</v>
       </c>
       <c r="CE7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CN7" t="n">
         <v>1.6</v>
       </c>
-      <c r="CF7" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>1.7</v>
-      </c>
       <c r="CO7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.65</v>
+        <v>4.53</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="CU7" t="n">
         <v>1.34</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="CY7" t="n">
         <v>2.41</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="DA7" t="n">
         <v>1.54</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.71</v>
+        <v>2.58</v>
       </c>
       <c r="DD7" t="n">
-        <v>5.26</v>
+        <v>4.94</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3500,70 +3500,70 @@
         <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>106.5</v>
+        <v>107.67</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>16</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>4</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="DY7" t="n">
         <v>3</v>
       </c>
-      <c r="DK7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>44</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>14</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>13</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>4</v>
-      </c>
       <c r="DZ7" t="n">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.5</v>
+        <v>11.33</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.05</v>
+        <v>0.85</v>
       </c>
       <c r="EC7" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="8">
@@ -4375,13 +4375,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4468,136 +4468,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>114</v>
+        <v>107.5</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>51</v>
+        <v>64.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP10" t="n">
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AS10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>52</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB10" t="n">
         <v>5</v>
       </c>
-      <c r="AT10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>49</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2</v>
-      </c>
       <c r="BC10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD10" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="BF10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="BH10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="BO10" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="BP10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR10" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BY10" t="n">
         <v>1.38</v>
@@ -4606,136 +4606,136 @@
         <v>1.43</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="CI10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CP10" t="n">
         <v>1.94</v>
       </c>
-      <c r="CJ10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>1.81</v>
-      </c>
       <c r="CQ10" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="CY10" t="n">
         <v>2.44</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="DA10" t="n">
         <v>1.54</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="DH10" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DK10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>60.5</v>
+        <v>66.33</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DP10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.5</v>
+        <v>14.33</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4747,28 +4747,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>57.5</v>
+        <v>56.67</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>8.5</v>
+        <v>8.67</v>
       </c>
       <c r="DY10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="EA10" t="n">
-        <v>12</v>
+        <v>7.67</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC10" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="11">
@@ -5073,13 +5073,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0.5</v>
@@ -5162,65 +5162,119 @@
       <c r="AE12" t="n">
         <v>1</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>93</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>45</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2</v>
+      </c>
       <c r="BG12" t="n">
         <v>2</v>
       </c>
       <c r="BH12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BP12" t="n">
         <v>5</v>
       </c>
-      <c r="BI12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BQ12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
@@ -5250,69 +5304,73 @@
         <v>3.24</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="CC12" t="inlineStr"/>
-      <c r="CD12" t="inlineStr"/>
+        <v>3.27</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>3.49</v>
+      </c>
       <c r="CE12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CO12" t="n">
         <v>1.28</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="CX12" t="n">
         <v>1.82</v>
@@ -5327,39 +5385,89 @@
         <v>1.58</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="DE12" t="inlineStr"/>
-      <c r="DF12" t="inlineStr"/>
-      <c r="DG12" t="inlineStr"/>
-      <c r="DH12" t="inlineStr"/>
-      <c r="DI12" t="inlineStr"/>
-      <c r="DJ12" t="inlineStr"/>
-      <c r="DK12" t="inlineStr"/>
-      <c r="DL12" t="inlineStr"/>
-      <c r="DM12" t="inlineStr"/>
-      <c r="DN12" t="inlineStr"/>
-      <c r="DO12" t="inlineStr"/>
-      <c r="DP12" t="inlineStr"/>
-      <c r="DQ12" t="inlineStr"/>
-      <c r="DR12" t="inlineStr"/>
-      <c r="DS12" t="inlineStr"/>
-      <c r="DT12" t="inlineStr"/>
-      <c r="DU12" t="inlineStr"/>
-      <c r="DV12" t="inlineStr"/>
-      <c r="DW12" t="inlineStr"/>
-      <c r="DX12" t="inlineStr"/>
-      <c r="DY12" t="inlineStr"/>
-      <c r="DZ12" t="inlineStr"/>
-      <c r="EA12" t="inlineStr"/>
-      <c r="EB12" t="inlineStr"/>
-      <c r="EC12" t="inlineStr"/>
+        <v>3.58</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>110.67</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>54</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>45</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>7</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>9</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>1.33</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,44 +1472,44 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>106</v>
+        <v>84.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>45</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS2" t="n">
         <v>4</v>
       </c>
-      <c r="AL2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>9</v>
-      </c>
       <c r="AT2" t="n">
         <v>1</v>
       </c>
@@ -1517,70 +1517,70 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>20</v>
+        <v>9.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="BF2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BH2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="BP2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
@@ -1589,7 +1589,7 @@
         <v>100</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
@@ -1610,73 +1610,73 @@
         <v>2.26</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="CT2" t="n">
         <v>2.7</v>
       </c>
-      <c r="CG2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>2.82</v>
-      </c>
       <c r="CU2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="CX2" t="n">
         <v>1.88</v>
@@ -1691,88 +1691,88 @@
         <v>1.58</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.88</v>
+        <v>4.16</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DH2" t="n">
-        <v>98.5</v>
+        <v>86.67</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="DK2" t="n">
         <v>4</v>
       </c>
       <c r="DL2" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DM2" t="n">
-        <v>56</v>
+        <v>47.33</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.5</v>
+        <v>11.33</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12</v>
+        <v>11.33</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.5</v>
+        <v>3.33</v>
       </c>
       <c r="DS2" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DT2" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>44.5</v>
+        <v>41.67</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="DX2" t="n">
-        <v>10</v>
+        <v>8.33</v>
       </c>
       <c r="DY2" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="EA2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="EC2" t="n">
-        <v>4</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="3">
@@ -1782,73 +1782,73 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="I3" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>31</v>
+        <v>41.5</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1863,13 +1863,13 @@
         <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>16</v>
+        <v>7.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,37 +1953,37 @@
         <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BH3" t="n">
-        <v>7</v>
+        <v>7.67</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="BO3" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.5</v>
+        <v>3.67</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,13 +1992,13 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BV3" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>100</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.63</v>
+        <v>3.68</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.84</v>
+        <v>3.76</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.88</v>
+        <v>3.69</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.04</v>
+        <v>3.85</v>
       </c>
       <c r="CC3" t="n">
         <v>7.25</v>
@@ -2025,55 +2025,55 @@
         <v>7.54</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="CH3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CR3" t="n">
         <v>1.42</v>
       </c>
-      <c r="CI3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>1.38</v>
-      </c>
       <c r="CS3" t="n">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="CV3" t="n">
         <v>1.95</v>
@@ -2082,100 +2082,100 @@
         <v>1.91</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="DF3" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>87.5</v>
+        <v>107.33</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.5</v>
+        <v>-0.33</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>51</v>
+        <v>57.67</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DP3" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="DQ3" t="n">
         <v>10</v>
       </c>
-      <c r="DQ3" t="n">
-        <v>8.5</v>
-      </c>
       <c r="DR3" t="n">
-        <v>7</v>
+        <v>4.33</v>
       </c>
       <c r="DS3" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DT3" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>32.5</v>
+        <v>39</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="DY3" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.5</v>
+        <v>11.33</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="4">
@@ -2230,10 +2230,10 @@
         <v>10.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -2251,22 +2251,22 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>64</v>
+        <v>57.5</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AD4" t="n">
         <v>1.78</v>
@@ -2413,13 +2413,13 @@
         <v>1.95</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="CA4" t="n">
         <v>3.37</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="CC4" t="n">
         <v>2.02</v>
@@ -2467,22 +2467,22 @@
         <v>3.22</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CX4" t="n">
         <v>1.72</v>
@@ -2497,13 +2497,13 @@
         <v>1.68</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
@@ -2542,10 +2542,10 @@
         <v>9.33</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13</v>
+        <v>12.33</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.33</v>
+        <v>5.33</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,22 +2557,22 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>65.67</v>
+        <v>61.33</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.67</v>
+        <v>14.33</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.33</v>
+        <v>10.67</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.33</v>
+        <v>3.67</v>
       </c>
       <c r="EA4" t="n">
-        <v>11.33</v>
+        <v>18</v>
       </c>
       <c r="EB4" t="n">
         <v>1.7</v>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -2627,88 +2627,88 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH5" t="n">
         <v>3</v>
       </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
       <c r="AI5" t="n">
-        <v>84</v>
+        <v>79.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK5" t="n">
         <v>5</v>
       </c>
       <c r="AL5" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="AO5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AR5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>49</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA5" t="n">
         <v>14</v>
       </c>
-      <c r="AS5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>45</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>13</v>
-      </c>
       <c r="BB5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC5" t="n">
         <v>6</v>
       </c>
-      <c r="BC5" t="n">
-        <v>7</v>
-      </c>
       <c r="BD5" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
         <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BI5" t="n">
         <v>3</v>
@@ -2732,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
@@ -2761,86 +2761,86 @@
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="inlineStr"/>
       <c r="CA5" t="n">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CF5" t="n">
         <v>2.9</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CI5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CM5" t="n">
         <v>1.82</v>
       </c>
-      <c r="CJ5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>1.75</v>
-      </c>
       <c r="CN5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="CR5" t="inlineStr"/>
       <c r="CS5" t="inlineStr"/>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CZ5" t="n">
         <v>1.92</v>
       </c>
-      <c r="CW5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>1.74</v>
-      </c>
       <c r="DA5" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.16</v>
+        <v>4.07</v>
       </c>
       <c r="DE5" t="inlineStr"/>
       <c r="DF5" t="inlineStr"/>
@@ -2875,41 +2875,95 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>71</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>14</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>76</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
@@ -2992,37 +3046,37 @@
         <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BH6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="BI6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BM6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO6" t="n">
         <v>2</v>
       </c>
       <c r="BP6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
@@ -3031,10 +3085,10 @@
         <v>100</v>
       </c>
       <c r="BT6" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3045,10 +3099,14 @@
       <c r="BX6" t="n">
         <v>100</v>
       </c>
-      <c r="BY6" t="inlineStr"/>
-      <c r="BZ6" t="inlineStr"/>
+      <c r="BY6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>2.17</v>
+      </c>
       <c r="CA6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="CB6" t="n">
         <v>3.04</v>
@@ -3060,61 +3118,61 @@
         <v>2.87</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="CS6" t="n">
         <v>3.4</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="CX6" t="n">
         <v>1.78</v>
@@ -3129,39 +3187,89 @@
         <v>1.62</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="DE6" t="inlineStr"/>
-      <c r="DF6" t="inlineStr"/>
-      <c r="DG6" t="inlineStr"/>
-      <c r="DH6" t="inlineStr"/>
-      <c r="DI6" t="inlineStr"/>
-      <c r="DJ6" t="inlineStr"/>
-      <c r="DK6" t="inlineStr"/>
-      <c r="DL6" t="inlineStr"/>
-      <c r="DM6" t="inlineStr"/>
-      <c r="DN6" t="inlineStr"/>
-      <c r="DO6" t="inlineStr"/>
-      <c r="DP6" t="inlineStr"/>
-      <c r="DQ6" t="inlineStr"/>
-      <c r="DR6" t="inlineStr"/>
-      <c r="DS6" t="inlineStr"/>
-      <c r="DT6" t="inlineStr"/>
-      <c r="DU6" t="inlineStr"/>
-      <c r="DV6" t="inlineStr"/>
-      <c r="DW6" t="inlineStr"/>
-      <c r="DX6" t="inlineStr"/>
-      <c r="DY6" t="inlineStr"/>
-      <c r="DZ6" t="inlineStr"/>
-      <c r="EA6" t="inlineStr"/>
-      <c r="EB6" t="inlineStr"/>
-      <c r="EC6" t="inlineStr"/>
+        <v>4.39</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>5</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>8</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>12</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>65</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>14</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>8</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3215,10 +3323,10 @@
         <v>17</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -3236,25 +3344,25 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.74</v>
+        <v>0.9</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -3398,7 +3506,7 @@
         <v>3.47</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.07</v>
+        <v>4.14</v>
       </c>
       <c r="CA7" t="n">
         <v>2.96</v>
@@ -3452,22 +3560,22 @@
         <v>4.53</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CS7" t="n">
         <v>3.36</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CU7" t="n">
         <v>1.34</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CX7" t="n">
         <v>1.98</v>
@@ -3482,13 +3590,13 @@
         <v>1.54</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3527,10 +3635,10 @@
         <v>16</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.67</v>
+        <v>13.33</v>
       </c>
       <c r="DR7" t="n">
-        <v>4</v>
+        <v>8.67</v>
       </c>
       <c r="DS7" t="n">
         <v>0.33</v>
@@ -3542,25 +3650,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.33</v>
+        <v>48.33</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>5.33</v>
+        <v>6.67</v>
       </c>
       <c r="DY7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="EA7" t="n">
-        <v>11.33</v>
+        <v>16.67</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="EC7" t="n">
         <v>2.67</v>
@@ -3573,13 +3681,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3666,19 +3774,19 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL8" t="n">
         <v>3</v>
@@ -3687,94 +3795,94 @@
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="AO8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP8" t="n">
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BF8" t="n">
         <v>3</v>
       </c>
-      <c r="AU8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>63</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>31</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="BH8" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="BI8" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BN8" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="BO8" t="n">
         <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -3783,13 +3891,13 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -3804,90 +3912,94 @@
         <v>2.86</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CB8" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.39</v>
+        <v>2.64</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.99</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.14</v>
+        <v>2.55</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.25</v>
+        <v>4.14</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CS8" t="inlineStr"/>
+        <v>1.58</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>3.34</v>
+      </c>
       <c r="CT8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CU8" t="inlineStr"/>
+        <v>2.44</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>1.35</v>
+      </c>
       <c r="CV8" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="CY8" t="n">
         <v>2.42</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="DA8" t="n">
         <v>1.52</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.86</v>
+        <v>4.88</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
@@ -3896,10 +4008,10 @@
         <v>1</v>
       </c>
       <c r="DG8" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DH8" t="n">
-        <v>111.5</v>
+        <v>105.67</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
@@ -3908,13 +4020,13 @@
         <v>2</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DM8" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
@@ -3923,43 +4035,43 @@
         <v>2</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.5</v>
+        <v>13.33</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.5</v>
+        <v>15.33</v>
       </c>
       <c r="DR8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>59</v>
+        <v>55.33</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="DY8" t="n">
-        <v>10</v>
+        <v>8.67</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="EA8" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="EC8" t="n">
         <v>2</v>
@@ -3972,10 +4084,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -3990,43 +4102,43 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>80</v>
+        <v>72.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="R9" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4038,28 +4150,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>34</v>
+        <v>40.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>18</v>
+        <v>8.5</v>
       </c>
       <c r="AD9" t="n">
         <v>0.98</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4143,13 +4255,13 @@
         <v>1</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="BH9" t="n">
-        <v>7.5</v>
+        <v>8.33</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
@@ -4161,28 +4273,28 @@
         <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="BO9" t="n">
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="BS9" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -4194,19 +4306,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.36</v>
+        <v>3.08</v>
       </c>
       <c r="CA9" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="CC9" t="n">
         <v>3.1</v>
@@ -4215,43 +4327,43 @@
         <v>3.66</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CF9" t="n">
         <v>2.92</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CH9" t="n">
         <v>1.34</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="CM9" t="n">
         <v>1.86</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.25</v>
+        <v>3.93</v>
       </c>
       <c r="CR9" t="n">
         <v>1.55</v>
@@ -4266,31 +4378,31 @@
         <v>1.34</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.69</v>
+        <v>4.45</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
@@ -4299,73 +4411,73 @@
         <v>1</v>
       </c>
       <c r="DG9" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DH9" t="n">
-        <v>93</v>
+        <v>83.67</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DM9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="DN9" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.5</v>
+        <v>14.67</v>
       </c>
       <c r="DQ9" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>5</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>44</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="EA9" t="n">
         <v>12</v>
       </c>
-      <c r="DR9" t="n">
-        <v>8</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>6</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="EA9" t="n">
-        <v>18.5</v>
-      </c>
       <c r="EB9" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="10">
@@ -4489,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>64.5</v>
+        <v>66</v>
       </c>
       <c r="AO10" t="n">
         <v>0.5</v>
@@ -4501,10 +4613,10 @@
         <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
         <v>0.5</v>
@@ -4522,25 +4634,25 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>52</v>
+        <v>53.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB10" t="n">
         <v>7</v>
       </c>
-      <c r="BB10" t="n">
-        <v>5</v>
-      </c>
       <c r="BC10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.06</v>
+        <v>1.46</v>
       </c>
       <c r="BF10" t="n">
         <v>2</v>
@@ -4615,7 +4727,7 @@
         <v>2.04</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CE10" t="n">
         <v>1.37</v>
@@ -4657,22 +4769,22 @@
         <v>3.32</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS10" t="n">
         <v>3.1</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CX10" t="n">
         <v>1.96</v>
@@ -4687,13 +4799,13 @@
         <v>1.54</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
@@ -4720,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>66.33</v>
+        <v>67.33</v>
       </c>
       <c r="DN10" t="n">
         <v>0.67</v>
@@ -4732,40 +4844,40 @@
         <v>13</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.33</v>
+        <v>13.67</v>
       </c>
       <c r="DR10" t="n">
+        <v>6</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="DZ10" t="n">
         <v>4</v>
       </c>
-      <c r="DS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>56.67</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX10" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="DY10" t="n">
-        <v>6</v>
-      </c>
-      <c r="DZ10" t="n">
-        <v>2.67</v>
-      </c>
       <c r="EA10" t="n">
-        <v>7.67</v>
+        <v>12</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="EC10" t="n">
         <v>1.67</v>
@@ -4778,41 +4890,95 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>114</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>59</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>11</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>52</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2</v>
+      </c>
       <c r="AF11" t="n">
         <v>0</v>
       </c>
@@ -4904,16 +5070,16 @@
         <v>2</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BM11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN11" t="n">
         <v>1</v>
@@ -4922,10 +5088,10 @@
         <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -4948,13 +5114,17 @@
       <c r="BX11" t="n">
         <v>100</v>
       </c>
-      <c r="BY11" t="inlineStr"/>
-      <c r="BZ11" t="inlineStr"/>
+      <c r="BY11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>2.77</v>
+      </c>
       <c r="CA11" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CC11" t="n">
         <v>2.27</v>
@@ -4963,108 +5133,158 @@
         <v>2.65</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.79</v>
+        <v>3.08</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.3</v>
+        <v>3.61</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="CY11" t="n">
         <v>2.34</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="DA11" t="n">
         <v>1.55</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="DE11" t="inlineStr"/>
-      <c r="DF11" t="inlineStr"/>
-      <c r="DG11" t="inlineStr"/>
-      <c r="DH11" t="inlineStr"/>
-      <c r="DI11" t="inlineStr"/>
-      <c r="DJ11" t="inlineStr"/>
-      <c r="DK11" t="inlineStr"/>
-      <c r="DL11" t="inlineStr"/>
-      <c r="DM11" t="inlineStr"/>
-      <c r="DN11" t="inlineStr"/>
-      <c r="DO11" t="inlineStr"/>
-      <c r="DP11" t="inlineStr"/>
-      <c r="DQ11" t="inlineStr"/>
-      <c r="DR11" t="inlineStr"/>
-      <c r="DS11" t="inlineStr"/>
-      <c r="DT11" t="inlineStr"/>
-      <c r="DU11" t="inlineStr"/>
-      <c r="DV11" t="inlineStr"/>
-      <c r="DW11" t="inlineStr"/>
-      <c r="DX11" t="inlineStr"/>
-      <c r="DY11" t="inlineStr"/>
-      <c r="DZ11" t="inlineStr"/>
-      <c r="EA11" t="inlineStr"/>
-      <c r="EB11" t="inlineStr"/>
-      <c r="EC11" t="inlineStr"/>
+        <v>4.49</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>108</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>54</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>12</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>50</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>7</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5199,10 +5419,10 @@
         <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS12" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
         <v>1</v>
@@ -5220,7 +5440,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -5235,7 +5455,7 @@
         <v>3</v>
       </c>
       <c r="BD12" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="BE12" t="n">
         <v>1.17</v>
@@ -5307,13 +5527,13 @@
         <v>3.18</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="CC12" t="n">
         <v>3.26</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.49</v>
+        <v>3.37</v>
       </c>
       <c r="CE12" t="n">
         <v>1.39</v>
@@ -5355,22 +5575,22 @@
         <v>3.16</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CX12" t="n">
         <v>1.82</v>
@@ -5385,13 +5605,13 @@
         <v>1.58</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="DE12" t="n">
         <v>0.33</v>
@@ -5430,10 +5650,10 @@
         <v>10.33</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.67</v>
+        <v>11</v>
       </c>
       <c r="DR12" t="n">
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5445,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45</v>
+        <v>49.33</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
@@ -5460,7 +5680,7 @@
         <v>3.33</v>
       </c>
       <c r="EA12" t="n">
-        <v>9</v>
+        <v>17.33</v>
       </c>
       <c r="EB12" t="n">
         <v>1.28</v>
@@ -5476,13 +5696,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5565,65 +5785,119 @@
       <c r="AE13" t="n">
         <v>2</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>113</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1</v>
+      </c>
       <c r="BG13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP13" t="n">
         <v>4</v>
       </c>
-      <c r="BH13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>2</v>
-      </c>
       <c r="BQ13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -5635,7 +5909,7 @@
         <v>100</v>
       </c>
       <c r="BU13" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -5653,21 +5927,25 @@
         <v>2.77</v>
       </c>
       <c r="CA13" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="CC13" t="inlineStr"/>
-      <c r="CD13" t="inlineStr"/>
+        <v>3.25</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>2.11</v>
+      </c>
       <c r="CE13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="CF13" t="n">
         <v>3.1</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.41</v>
+        <v>2.58</v>
       </c>
       <c r="CH13" t="n">
         <v>1.32</v>
@@ -5676,93 +5954,143 @@
         <v>1.85</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="CP13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DC13" t="n">
         <v>2.17</v>
       </c>
-      <c r="CQ13" t="n">
+      <c r="DD13" t="n">
         <v>3.9</v>
       </c>
-      <c r="CR13" t="n">
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>97</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ13" t="n">
         <v>1.5</v>
       </c>
-      <c r="CS13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="DD13" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="DE13" t="inlineStr"/>
-      <c r="DF13" t="inlineStr"/>
-      <c r="DG13" t="inlineStr"/>
-      <c r="DH13" t="inlineStr"/>
-      <c r="DI13" t="inlineStr"/>
-      <c r="DJ13" t="inlineStr"/>
-      <c r="DK13" t="inlineStr"/>
-      <c r="DL13" t="inlineStr"/>
-      <c r="DM13" t="inlineStr"/>
-      <c r="DN13" t="inlineStr"/>
-      <c r="DO13" t="inlineStr"/>
-      <c r="DP13" t="inlineStr"/>
-      <c r="DQ13" t="inlineStr"/>
-      <c r="DR13" t="inlineStr"/>
-      <c r="DS13" t="inlineStr"/>
-      <c r="DT13" t="inlineStr"/>
-      <c r="DU13" t="inlineStr"/>
-      <c r="DV13" t="inlineStr"/>
-      <c r="DW13" t="inlineStr"/>
-      <c r="DX13" t="inlineStr"/>
-      <c r="DY13" t="inlineStr"/>
-      <c r="DZ13" t="inlineStr"/>
-      <c r="EA13" t="inlineStr"/>
-      <c r="EB13" t="inlineStr"/>
-      <c r="EC13" t="inlineStr"/>
+      <c r="DK13" t="n">
+        <v>3</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>61</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>4</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>41</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>12</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>7</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>9</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>1.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>3</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,115 +1472,115 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>89.33</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN2" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BO2" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
@@ -1589,7 +1589,7 @@
         <v>100</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
@@ -1610,55 +1610,55 @@
         <v>2.26</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.92</v>
+        <v>4.64</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="CH2" t="n">
         <v>1.36</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="CR2" t="n">
         <v>1.49</v>
@@ -1673,106 +1673,106 @@
         <v>1.36</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW2" t="n">
         <v>1.97</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.16</v>
+        <v>3.99</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DH2" t="n">
-        <v>86.67</v>
+        <v>89.75</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="DK2" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="DL2" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DM2" t="n">
-        <v>47.33</v>
+        <v>50.5</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.33</v>
+        <v>11</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.33</v>
+        <v>10.75</v>
       </c>
       <c r="DR2" t="n">
-        <v>3.33</v>
+        <v>6.25</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>41.67</v>
+        <v>42.75</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DX2" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="DY2" t="n">
-        <v>3.33</v>
+        <v>4.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="EA2" t="n">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -1782,91 +1782,91 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H3" t="n">
-        <v>113</v>
+        <v>107.33</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5</v>
+        <v>-0.33</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="P3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.5</v>
+        <v>13.33</v>
       </c>
       <c r="R3" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>41.5</v>
+        <v>41.67</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>10</v>
+        <v>8.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1953,70 +1953,70 @@
         <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.67</v>
+        <v>7</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BS3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.76</v>
+        <v>4.17</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.69</v>
+        <v>3.54</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.85</v>
+        <v>3.79</v>
       </c>
       <c r="CC3" t="n">
         <v>7.25</v>
@@ -2025,157 +2025,157 @@
         <v>7.54</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CK3" t="n">
         <v>1.82</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="CP3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CV3" t="n">
         <v>1.9</v>
       </c>
-      <c r="CQ3" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>1.95</v>
-      </c>
       <c r="CW3" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.43</v>
+        <v>3.66</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DH3" t="n">
-        <v>107.33</v>
+        <v>104.5</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.33</v>
+        <v>-0.25</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>57.67</v>
+        <v>52.25</v>
       </c>
       <c r="DN3" t="n">
         <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10</v>
+        <v>12.75</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>39</v>
+        <v>39.75</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>9</v>
+        <v>8.25</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.67</v>
+        <v>5.5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="EA3" t="n">
-        <v>11.33</v>
+        <v>13</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,118 +2275,118 @@
         <v>3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>79</v>
+        <v>54.5</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC4" t="n">
         <v>3</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>69</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2</v>
-      </c>
       <c r="BD4" t="n">
-        <v>16</v>
+        <v>7.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.33</v>
+        <v>9.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="BP4" t="n">
         <v>6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2395,10 +2395,10 @@
         <v>100</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2416,136 +2416,136 @@
         <v>2.13</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="CE4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CU4" t="n">
         <v>1.38</v>
       </c>
-      <c r="CF4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CP4" t="n">
+      <c r="CV4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CX4" t="n">
         <v>1.92</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>3</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CW4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CX4" t="n">
-        <v>1.72</v>
       </c>
       <c r="CY4" t="n">
         <v>2.15</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="DA4" t="n">
         <v>1.68</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="DH4" t="n">
-        <v>146</v>
+        <v>143.5</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.33</v>
+        <v>-0.25</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.67</v>
+        <v>4.75</v>
       </c>
       <c r="DL4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DM4" t="n">
-        <v>73</v>
+        <v>62.25</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.33</v>
+        <v>11</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.33</v>
+        <v>11.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.33</v>
+        <v>3.75</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>61.33</v>
+        <v>58.75</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.33</v>
+        <v>12.5</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.67</v>
+        <v>8.75</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="EA4" t="n">
-        <v>18</v>
+        <v>13.25</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="EC4" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -2624,127 +2624,127 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>54</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BF5" t="n">
         <v>3</v>
       </c>
-      <c r="AI5" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>53</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>49</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="BM5" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="BN5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.5</v>
+        <v>3.33</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="inlineStr"/>
@@ -2767,80 +2767,88 @@
         <v>3.21</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="CE5" t="n">
         <v>1.5</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CH5" t="n">
         <v>1.32</v>
       </c>
       <c r="CI5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CJ5" t="n">
         <v>1.83</v>
       </c>
-      <c r="CJ5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="CK5" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CO5" t="n">
         <v>1.36</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CR5" t="inlineStr"/>
-      <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr"/>
+        <v>3.78</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>1.34</v>
+      </c>
       <c r="CV5" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CX5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CZ5" t="n">
         <v>1.88</v>
       </c>
-      <c r="CY5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>1.92</v>
-      </c>
       <c r="DA5" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.07</v>
+        <v>4.18</v>
       </c>
       <c r="DE5" t="inlineStr"/>
       <c r="DF5" t="inlineStr"/>
@@ -2875,13 +2883,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -2920,10 +2928,10 @@
         <v>9</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -2941,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -2956,7 +2964,7 @@
         <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AD6" t="n">
         <v>1.7</v>
@@ -2974,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -2983,112 +2991,112 @@
         <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AT6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BC6" t="n">
         <v>3</v>
       </c>
-      <c r="AU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>66</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4</v>
-      </c>
       <c r="BD6" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.89</v>
+        <v>1.46</v>
       </c>
       <c r="BF6" t="n">
         <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BN6" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="BO6" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="BP6" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>4.67</v>
       </c>
       <c r="BR6" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3097,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BY6" t="n">
         <v>2.18</v>
@@ -3106,46 +3114,46 @@
         <v>2.17</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="CC6" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CH6" t="n">
         <v>1.3</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CO6" t="n">
         <v>1.39</v>
@@ -3154,88 +3162,88 @@
         <v>2.3</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CU6" t="n">
         <v>1.34</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DF6" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DG6" t="n">
-        <v>5</v>
+        <v>3.67</v>
       </c>
       <c r="DH6" t="n">
-        <v>111.5</v>
+        <v>107</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DK6" t="n">
-        <v>8</v>
+        <v>6.33</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DM6" t="n">
-        <v>87.5</v>
+        <v>72.67</v>
       </c>
       <c r="DN6" t="n">
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="DP6" t="n">
-        <v>12</v>
+        <v>13.33</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11</v>
+        <v>11.67</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3247,28 +3255,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>65</v>
+        <v>59.67</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>14</v>
+        <v>12.33</v>
       </c>
       <c r="DY6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="EA6" t="n">
-        <v>8</v>
+        <v>9.67</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="EC6" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="7">
@@ -3278,13 +3286,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3377,7 +3385,7 @@
         <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>107</v>
+        <v>106.5</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -3386,121 +3394,121 @@
         <v>4</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AO7" t="n">
         <v>2</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>9</v>
       </c>
-      <c r="BB7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>19</v>
-      </c>
       <c r="BE7" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
       <c r="BF7" t="n">
         <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BH7" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.67</v>
+        <v>4.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BS7" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BT7" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>3.47</v>
@@ -3509,94 +3517,94 @@
         <v>4.14</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.11</v>
+        <v>3.23</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.14</v>
+        <v>3.74</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.42</v>
+        <v>4.28</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CJ7" t="n">
         <v>2.03</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="CL7" t="n">
         <v>2.26</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="CU7" t="n">
         <v>1.34</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="DD7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3605,73 +3613,73 @@
         <v>2</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DH7" t="n">
-        <v>107.67</v>
+        <v>107.25</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="DK7" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.33</v>
+        <v>47.5</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DO7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DP7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.33</v>
+        <v>13.75</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.67</v>
+        <v>6.25</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.33</v>
+        <v>50.25</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>6.67</v>
+        <v>5.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.67</v>
+        <v>12.25</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3681,94 +3689,94 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
       <c r="H8" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>51</v>
+        <v>45.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC8" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
         <v>1.02</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3807,10 +3815,10 @@
         <v>13</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AT8" t="n">
         <v>2</v>
@@ -3828,61 +3836,61 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>55.5</v>
+        <v>55</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="BF8" t="n">
         <v>3</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -3891,13 +3899,13 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BU8" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BV8" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -3906,16 +3914,16 @@
         <v>100</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CB8" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="CC8" t="n">
         <v>2.64</v>
@@ -3924,157 +3932,157 @@
         <v>2.64</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="CO8" t="n">
         <v>1.39</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="CX8" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CY8" t="n">
         <v>2.42</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DA8" t="n">
         <v>1.52</v>
       </c>
       <c r="DB8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="DR8" t="n">
         <v>1.5</v>
       </c>
-      <c r="DC8" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>105.67</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>2</v>
-      </c>
-      <c r="DK8" t="n">
+      <c r="DS8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DZ8" t="n">
         <v>4</v>
       </c>
-      <c r="DL8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>67</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>2</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>1</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DT8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV8" t="n">
-        <v>55.33</v>
-      </c>
-      <c r="DW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX8" t="n">
-        <v>12</v>
-      </c>
-      <c r="DY8" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="DZ8" t="n">
-        <v>3.33</v>
-      </c>
       <c r="EA8" t="n">
-        <v>17</v>
+        <v>16.25</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
@@ -4084,11 +4092,11 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
         <v>3</v>
       </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
@@ -4099,46 +4107,46 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="H9" t="n">
-        <v>72.5</v>
+        <v>82.33</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>46</v>
+        <v>46.67</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>13.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.5</v>
+        <v>13.67</v>
       </c>
       <c r="R9" t="n">
-        <v>5.5</v>
+        <v>6.33</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4150,28 +4158,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>40.5</v>
+        <v>41.67</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.5</v>
+        <v>10.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>5</v>
+        <v>6.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.5</v>
+        <v>3.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.5</v>
+        <v>11.67</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.98</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4258,7 +4266,7 @@
         <v>2</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="BI9" t="n">
         <v>2</v>
@@ -4270,10 +4278,10 @@
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BM9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BN9" t="n">
         <v>2</v>
@@ -4282,19 +4290,19 @@
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.33</v>
+        <v>2.25</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -4306,19 +4314,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.08</v>
+        <v>3.39</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="CC9" t="n">
         <v>3.1</v>
@@ -4327,67 +4335,67 @@
         <v>3.66</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="CN9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CR9" t="n">
         <v>1.51</v>
       </c>
-      <c r="CO9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>1.55</v>
-      </c>
       <c r="CS9" t="n">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.53</v>
+        <v>2.68</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="CX9" t="n">
         <v>1.85</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CZ9" t="n">
         <v>1.95</v>
@@ -4396,13 +4404,13 @@
         <v>1.59</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.45</v>
+        <v>4.18</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
@@ -4411,10 +4419,10 @@
         <v>1</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DH9" t="n">
-        <v>83.67</v>
+        <v>88.25</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
@@ -4423,34 +4431,34 @@
         <v>2</v>
       </c>
       <c r="DK9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.67</v>
+        <v>13.75</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.33</v>
+        <v>12.75</v>
       </c>
       <c r="DR9" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
@@ -4459,25 +4467,25 @@
         <v>44</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DX9" t="n">
-        <v>6.67</v>
+        <v>9</v>
       </c>
       <c r="DY9" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.33</v>
+        <v>3.25</v>
       </c>
       <c r="EA9" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.91</v>
+        <v>1.13</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
@@ -4487,58 +4495,58 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H10" t="n">
-        <v>124</v>
+        <v>136.5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
         <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
@@ -4553,28 +4561,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>66</v>
+        <v>61.5</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AA10" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4658,70 +4666,70 @@
         <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="BP10" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BR10" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT10" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="CC10" t="n">
         <v>2.04</v>
@@ -4730,43 +4738,43 @@
         <v>2.11</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI10" t="n">
         <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP10" t="n">
         <v>1.94</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
@@ -4781,73 +4789,73 @@
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DB10" t="n">
         <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="DE10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DF10" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="DH10" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DK10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DM10" t="n">
-        <v>67.33</v>
+        <v>69.25</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DP10" t="n">
+        <v>12</v>
+      </c>
+      <c r="DQ10" t="n">
         <v>13</v>
       </c>
-      <c r="DQ10" t="n">
-        <v>13.67</v>
-      </c>
       <c r="DR10" t="n">
-        <v>6</v>
+        <v>4.25</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4859,28 +4867,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>57.67</v>
+        <v>57.5</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.33</v>
+        <v>10</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.33</v>
+        <v>6.25</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="EA10" t="n">
-        <v>12</v>
+        <v>8.75</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4890,10 +4898,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -4902,49 +4910,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H11" t="n">
-        <v>114</v>
+        <v>97.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="R11" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -4956,28 +4964,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>52</v>
+        <v>48.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AA11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE11" t="n">
         <v>3</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5061,43 +5069,43 @@
         <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BH11" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="BI11" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BN11" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="BO11" t="n">
         <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -5112,19 +5120,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.77</v>
+        <v>3.38</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="CC11" t="n">
         <v>2.27</v>
@@ -5133,124 +5141,124 @@
         <v>2.65</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="CH11" t="n">
         <v>1.34</v>
       </c>
       <c r="CI11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CK11" t="n">
         <v>1.89</v>
       </c>
-      <c r="CJ11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CK11" t="n">
-        <v>1.85</v>
-      </c>
       <c r="CL11" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="CN11" t="n">
         <v>1.44</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.61</v>
+        <v>3.81</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CU11" t="n">
         <v>1.34</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="DB11" t="n">
         <v>1.46</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="DH11" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="DM11" t="n">
-        <v>54</v>
+        <v>49.67</v>
       </c>
       <c r="DN11" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DO11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12</v>
+        <v>10.67</v>
       </c>
       <c r="DR11" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5262,28 +5270,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50</v>
+        <v>48.33</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="DX11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="DY11" t="n">
-        <v>5.5</v>
+        <v>6.33</v>
       </c>
       <c r="DZ11" t="n">
-        <v>1.5</v>
+        <v>2.67</v>
       </c>
       <c r="EA11" t="n">
-        <v>8.5</v>
+        <v>12.33</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.95</v>
+        <v>1.12</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5293,55 +5301,55 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
+        <v>1.67</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>119.5</v>
+        <v>111.67</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2.67</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="M12" t="n">
-        <v>58.5</v>
+        <v>59.67</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>8.5</v>
+        <v>10.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.5</v>
+        <v>13.67</v>
       </c>
       <c r="R12" t="n">
-        <v>5.5</v>
+        <v>3.33</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -5359,28 +5367,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.5</v>
+        <v>49</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>7</v>
+        <v>6.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AC12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5467,34 +5475,34 @@
         <v>2</v>
       </c>
       <c r="BH12" t="n">
-        <v>7</v>
+        <v>8.25</v>
       </c>
       <c r="BI12" t="n">
         <v>2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BP12" t="n">
         <v>5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
@@ -5518,16 +5526,16 @@
         <v>100</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.23</v>
+        <v>3.33</v>
       </c>
       <c r="CC12" t="n">
         <v>3.26</v>
@@ -5536,124 +5544,124 @@
         <v>3.37</v>
       </c>
       <c r="CE12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CH12" t="n">
         <v>1.39</v>
       </c>
-      <c r="CF12" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>1.41</v>
-      </c>
       <c r="CI12" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CN12" t="n">
         <v>1.56</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.16</v>
+        <v>3.49</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="CU12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>2</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DB12" t="n">
         <v>1.36</v>
       </c>
-      <c r="CV12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="DB12" t="n">
-        <v>1.34</v>
-      </c>
       <c r="DC12" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.66</v>
+        <v>3.79</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DF12" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="DH12" t="n">
-        <v>110.67</v>
+        <v>107</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="DK12" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DM12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.33</v>
+        <v>11.25</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11</v>
+        <v>12.75</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.67</v>
+        <v>4.75</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5665,28 +5673,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.33</v>
+        <v>48</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.33</v>
+        <v>10.25</v>
       </c>
       <c r="DY12" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.33</v>
+        <v>12.75</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5696,13 +5704,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5789,115 +5797,115 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR13" t="n">
         <v>13</v>
       </c>
-      <c r="AR13" t="n">
-        <v>17</v>
-      </c>
       <c r="AS13" t="n">
-        <v>-1</v>
+        <v>4.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AU13" t="n">
         <v>2</v>
       </c>
       <c r="AV13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48</v>
+        <v>50.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH13" t="n">
         <v>8</v>
       </c>
-      <c r="BC13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>6.5</v>
-      </c>
       <c r="BI13" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BM13" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BO13" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="BP13" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -5906,10 +5914,10 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -5918,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BY13" t="n">
         <v>2.2</v>
@@ -5927,169 +5935,169 @@
         <v>2.77</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="CI13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CW13" t="n">
         <v>1.85</v>
       </c>
-      <c r="CJ13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CO13" t="n">
+      <c r="CX13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DB13" t="n">
         <v>1.34</v>
       </c>
-      <c r="CP13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>1.36</v>
-      </c>
       <c r="DC13" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>97</v>
+        <v>92.33</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DK13" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>61</v>
+        <v>55.67</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.5</v>
+        <v>11.67</v>
       </c>
       <c r="DQ13" t="n">
-        <v>17</v>
+        <v>14.33</v>
       </c>
       <c r="DR13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>12</v>
+        <v>13.67</v>
       </c>
       <c r="DY13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="EA13" t="n">
-        <v>9</v>
+        <v>10.33</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -1505,10 +1505,10 @@
         <v>11</v>
       </c>
       <c r="AR2" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="AS2" t="n">
         <v>10</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.67</v>
       </c>
       <c r="AT2" t="n">
         <v>1.33</v>
@@ -1526,25 +1526,25 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>40.67</v>
+        <v>37.67</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>8.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="BC2" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>11</v>
+        <v>15.67</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BF2" t="n">
         <v>2</v>
@@ -1736,10 +1736,10 @@
         <v>11</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="DS2" t="n">
         <v>0.5</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>42.75</v>
+        <v>40.5</v>
       </c>
       <c r="DW2" t="n">
         <v>0.25</v>
       </c>
       <c r="DX2" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="DY2" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="EA2" t="n">
-        <v>13.25</v>
+        <v>16.75</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="EC2" t="n">
         <v>2.5</v>
@@ -1827,10 +1827,10 @@
         <v>12</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.33</v>
+        <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>8.67</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -1848,25 +1848,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>41.67</v>
+        <v>39.67</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.67</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>21.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -2139,10 +2139,10 @@
         <v>12</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.75</v>
+        <v>11.75</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="DS3" t="n">
         <v>0.5</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>39.75</v>
+        <v>38.25</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="EA3" t="n">
-        <v>13</v>
+        <v>20.75</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="EC3" t="n">
         <v>1.5</v>
@@ -2311,10 +2311,10 @@
         <v>11.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
@@ -2338,19 +2338,19 @@
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB4" t="n">
         <v>7</v>
       </c>
       <c r="BC4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.5</v>
+        <v>13</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="BF4" t="n">
         <v>1.5</v>
@@ -2542,10 +2542,10 @@
         <v>11</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.5</v>
+        <v>11.25</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2563,19 +2563,19 @@
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.5</v>
+        <v>12.75</v>
       </c>
       <c r="DY4" t="n">
         <v>8.75</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>13.25</v>
+        <v>16</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="EC4" t="n">
         <v>2.25</v>
@@ -2642,7 +2642,7 @@
         <v>3.33</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.33</v>
+        <v>5.67</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2660,10 +2660,10 @@
         <v>12.67</v>
       </c>
       <c r="AR5" t="n">
-        <v>17.33</v>
+        <v>16.67</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
         <v>0.67</v>
@@ -2681,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54.33</v>
+        <v>57.33</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.33</v>
@@ -2690,16 +2690,16 @@
         <v>12.67</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.67</v>
+        <v>7.33</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="BD5" t="n">
-        <v>11</v>
+        <v>20.33</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BF5" t="n">
         <v>3</v>
@@ -2708,7 +2708,7 @@
         <v>2.33</v>
       </c>
       <c r="BH5" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="BI5" t="n">
         <v>2.33</v>
@@ -3009,10 +3009,10 @@
         <v>15.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AT6" t="n">
         <v>1.5</v>
@@ -3030,25 +3030,25 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
         <v>3</v>
       </c>
       <c r="BD6" t="n">
-        <v>8</v>
+        <v>20.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="BF6" t="n">
         <v>3</v>
@@ -3240,10 +3240,10 @@
         <v>13.33</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.67</v>
+        <v>11.33</v>
       </c>
       <c r="DR6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3255,25 +3255,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>59.67</v>
+        <v>61.67</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.33</v>
+        <v>12.67</v>
       </c>
       <c r="DY6" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="DZ6" t="n">
         <v>3.33</v>
       </c>
       <c r="EA6" t="n">
-        <v>9.67</v>
+        <v>18</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="EC6" t="n">
         <v>2.33</v>
@@ -3415,7 +3415,7 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="AT7" t="n">
         <v>0.5</v>
@@ -3433,25 +3433,25 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>61</v>
+        <v>58.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4</v>
       </c>
-      <c r="BC7" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BD7" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.82</v>
+        <v>1.46</v>
       </c>
       <c r="BF7" t="n">
         <v>4</v>
@@ -3646,7 +3646,7 @@
         <v>13.75</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.25</v>
+        <v>8.25</v>
       </c>
       <c r="DS7" t="n">
         <v>0.5</v>
@@ -3658,25 +3658,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.25</v>
+        <v>49</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>5.5</v>
+        <v>9.25</v>
       </c>
       <c r="DY7" t="n">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>12.25</v>
+        <v>16.25</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.86</v>
+        <v>1.18</v>
       </c>
       <c r="EC7" t="n">
         <v>3</v>
@@ -3734,10 +3734,10 @@
         <v>10.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
         <v>2.5</v>
@@ -3761,19 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>19.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
         <v>1.5</v>
@@ -4046,10 +4046,10 @@
         <v>11.75</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.25</v>
+        <v>14.5</v>
       </c>
       <c r="DR8" t="n">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="DS8" t="n">
         <v>0.25</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.5</v>
+        <v>12.25</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.25</v>
+        <v>21</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="EC8" t="n">
         <v>2.25</v>
@@ -4137,10 +4137,10 @@
         <v>13.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.67</v>
+        <v>13.33</v>
       </c>
       <c r="R9" t="n">
-        <v>6.33</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
         <v>1.33</v>
@@ -4158,25 +4158,25 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>41.67</v>
+        <v>37.67</v>
       </c>
       <c r="Y9" t="n">
         <v>0.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.33</v>
+        <v>11.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.67</v>
+        <v>7.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.67</v>
+        <v>18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE9" t="n">
         <v>1.67</v>
@@ -4266,7 +4266,7 @@
         <v>2</v>
       </c>
       <c r="BH9" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="BI9" t="n">
         <v>2</v>
@@ -4449,10 +4449,10 @@
         <v>13.75</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.75</v>
+        <v>12.5</v>
       </c>
       <c r="DR9" t="n">
-        <v>5.75</v>
+        <v>7.75</v>
       </c>
       <c r="DS9" t="n">
         <v>0.25</v>
@@ -4464,25 +4464,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="DW9" t="n">
         <v>0.25</v>
       </c>
       <c r="DX9" t="n">
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>13.5</v>
+        <v>18.25</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="EC9" t="n">
         <v>1.5</v>
@@ -4540,10 +4540,10 @@
         <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="R10" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -4561,25 +4561,25 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>61.5</v>
+        <v>66</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -4852,10 +4852,10 @@
         <v>12</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.25</v>
+        <v>6.25</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4867,25 +4867,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>57.5</v>
+        <v>59.75</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>10</v>
+        <v>12.25</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.25</v>
+        <v>8.25</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="EA10" t="n">
-        <v>8.75</v>
+        <v>15</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="EC10" t="n">
         <v>2</v>
@@ -4910,7 +4910,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
         <v>0.5</v>
@@ -4922,10 +4922,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
       </c>
       <c r="L11" t="n">
         <v>-0.5</v>
@@ -4943,10 +4943,10 @@
         <v>13.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -4964,28 +4964,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>48.5</v>
+        <v>44</v>
       </c>
       <c r="Y11" t="n">
         <v>0.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AB11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE11" t="n">
         <v>3.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>3</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
         <v>1.67</v>
       </c>
       <c r="BH11" t="n">
-        <v>6.67</v>
+        <v>7.33</v>
       </c>
       <c r="BI11" t="n">
         <v>1.67</v>
@@ -5222,7 +5222,7 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="DG11" t="n">
         <v>0.67</v>
@@ -5234,10 +5234,10 @@
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.33</v>
+        <v>3.67</v>
       </c>
       <c r="DL11" t="n">
         <v>-0.33</v>
@@ -5255,10 +5255,10 @@
         <v>12</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.67</v>
+        <v>10.33</v>
       </c>
       <c r="DR11" t="n">
-        <v>3</v>
+        <v>5.67</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5270,28 +5270,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.33</v>
+        <v>45.33</v>
       </c>
       <c r="DW11" t="n">
         <v>0.67</v>
       </c>
       <c r="DX11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="EA11" t="n">
-        <v>12.33</v>
+        <v>18</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="EC11" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="12">
@@ -5346,10 +5346,10 @@
         <v>10.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="R12" t="n">
-        <v>3.33</v>
+        <v>5.33</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -5367,25 +5367,25 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>49</v>
+        <v>50.67</v>
       </c>
       <c r="Y12" t="n">
         <v>0.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.33</v>
+        <v>12.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.33</v>
+        <v>8.33</v>
       </c>
       <c r="AB12" t="n">
         <v>4</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -5658,10 +5658,10 @@
         <v>11.25</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5673,25 +5673,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48</v>
+        <v>49.25</v>
       </c>
       <c r="DW12" t="n">
         <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.25</v>
+        <v>11.75</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="DZ12" t="n">
         <v>3.75</v>
       </c>
       <c r="EA12" t="n">
-        <v>12.75</v>
+        <v>18.75</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="EC12" t="n">
         <v>2</v>
@@ -5812,7 +5812,7 @@
         <v>1.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AM13" t="n">
         <v>-0.5</v>
@@ -5833,7 +5833,7 @@
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>0.5</v>
@@ -5851,25 +5851,25 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>50.5</v>
+        <v>56.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BB13" t="n">
         <v>9</v>
       </c>
       <c r="BC13" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="BF13" t="n">
         <v>1.5</v>
@@ -5878,7 +5878,7 @@
         <v>3</v>
       </c>
       <c r="BH13" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="BI13" t="n">
         <v>3</v>
@@ -6043,7 +6043,7 @@
         <v>1.67</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.33</v>
+        <v>4.67</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>14.33</v>
       </c>
       <c r="DR13" t="n">
-        <v>6</v>
+        <v>8.33</v>
       </c>
       <c r="DS13" t="n">
         <v>0.33</v>
@@ -6076,25 +6076,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.67</v>
+        <v>13.33</v>
       </c>
       <c r="DY13" t="n">
         <v>8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.67</v>
+        <v>5.33</v>
       </c>
       <c r="EA13" t="n">
-        <v>10.33</v>
+        <v>15.33</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="EC13" t="n">
         <v>1.67</v>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -1391,79 +1391,79 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC2" t="n">
-        <v>20</v>
+        <v>9.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.56</v>
+        <v>0.96</v>
       </c>
       <c r="AE2" t="n">
         <v>4</v>
@@ -1550,46 +1550,46 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.25</v>
+        <v>10.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
@@ -1601,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="CC2" t="n">
         <v>4.05</v>
@@ -1622,43 +1622,43 @@
         <v>4.64</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="CR2" t="n">
         <v>1.49</v>
@@ -1673,106 +1673,106 @@
         <v>1.36</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.99</v>
+        <v>4.19</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DH2" t="n">
-        <v>89.75</v>
+        <v>86.8</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="DL2" t="n">
         <v>1</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.5</v>
+        <v>44.4</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="DP2" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DR2" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>40.5</v>
+        <v>37</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DY2" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.75</v>
+        <v>13.2</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0.33</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
         <v>2</v>
       </c>
-      <c r="AH3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>96</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>3</v>
-      </c>
       <c r="AL3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AN3" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AQ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR3" t="n">
         <v>12</v>
       </c>
-      <c r="AR3" t="n">
-        <v>11</v>
-      </c>
       <c r="AS3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB3" t="n">
         <v>6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4</v>
       </c>
       <c r="BC3" t="n">
         <v>3</v>
       </c>
       <c r="BD3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="BF3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BM3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
         <v>3.72</v>
@@ -2013,169 +2013,169 @@
         <v>4.17</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.54</v>
+        <v>3.43</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.79</v>
+        <v>3.66</v>
       </c>
       <c r="CC3" t="n">
-        <v>7.25</v>
+        <v>5.38</v>
       </c>
       <c r="CD3" t="n">
-        <v>7.54</v>
+        <v>5.64</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.92</v>
+        <v>3.02</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="CH3" t="n">
         <v>1.36</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="CP3" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="CU3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DB3" t="n">
         <v>1.38</v>
       </c>
-      <c r="CV3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CX3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CY3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="CZ3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="DA3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DB3" t="n">
-        <v>1.34</v>
-      </c>
       <c r="DC3" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.66</v>
+        <v>4.05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="DH3" t="n">
-        <v>104.5</v>
+        <v>105</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DK3" t="n">
         <v>3</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="DM3" t="n">
-        <v>52.25</v>
+        <v>52</v>
       </c>
       <c r="DN3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="DP3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="DQ3" t="n">
         <v>12</v>
       </c>
-      <c r="DQ3" t="n">
-        <v>11.75</v>
-      </c>
       <c r="DR3" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>38.25</v>
+        <v>40.8</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.25</v>
+        <v>9.6</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="DZ3" t="n">
         <v>3</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.75</v>
+        <v>16.4</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -2200,79 +2200,79 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>146</v>
+        <v>145.67</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>4.67</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>70</v>
+        <v>70.67</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="P4" t="n">
-        <v>10.5</v>
+        <v>10.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.5</v>
+        <v>14.33</v>
       </c>
       <c r="R4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB4" t="n">
         <v>4</v>
       </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AC4" t="n">
-        <v>19</v>
+        <v>12.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AE4" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AF4" t="n">
         <v>0.5</v>
@@ -2356,49 +2356,49 @@
         <v>1.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BM4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BP4" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CB4" t="n">
         <v>3.4</v>
@@ -2434,46 +2434,46 @@
         <v>2.83</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CH4" t="n">
         <v>1.39</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK4" t="n">
         <v>1.76</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO4" t="n">
         <v>1.3</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CU4" t="n">
         <v>1.38</v>
@@ -2485,16 +2485,16 @@
         <v>1.78</v>
       </c>
       <c r="CX4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CZ4" t="n">
         <v>1.92</v>
       </c>
-      <c r="CY4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>1.89</v>
-      </c>
       <c r="DA4" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="DB4" t="n">
         <v>1.32</v>
@@ -2503,49 +2503,49 @@
         <v>2.04</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DG4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DH4" t="n">
-        <v>143.5</v>
+        <v>143.8</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DM4" t="n">
-        <v>62.25</v>
+        <v>64.2</v>
       </c>
       <c r="DN4" t="n">
         <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="DP4" t="n">
         <v>11</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.25</v>
+        <v>11.8</v>
       </c>
       <c r="DR4" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>58.75</v>
+        <v>58.4</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.75</v>
+        <v>12</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="EA4" t="n">
-        <v>16</v>
+        <v>12.6</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="5">
@@ -2588,41 +2588,95 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>98</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>52</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>14</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
       <c r="AF5" t="n">
         <v>0.33</v>
       </c>
@@ -2705,66 +2759,70 @@
         <v>3</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.67</v>
+        <v>8.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BN5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1.44</v>
+      </c>
       <c r="CA5" t="n">
-        <v>3.03</v>
+        <v>3.17</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.21</v>
+        <v>3.54</v>
       </c>
       <c r="CC5" t="n">
         <v>2.21</v>
@@ -2773,31 +2831,31 @@
         <v>2.33</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CN5" t="n">
         <v>1.48</v>
@@ -2806,10 +2864,10 @@
         <v>1.36</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CR5" t="n">
         <v>1.55</v>
@@ -2824,57 +2882,107 @@
         <v>1.34</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="CW5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CX5" t="n">
         <v>1.94</v>
       </c>
-      <c r="CX5" t="n">
-        <v>1.92</v>
-      </c>
       <c r="CY5" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="DA5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>92</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>12</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>5</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>57</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>12</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>15</v>
+      </c>
+      <c r="EB5" t="n">
         <v>1.54</v>
       </c>
-      <c r="DB5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="DE5" t="inlineStr"/>
-      <c r="DF5" t="inlineStr"/>
-      <c r="DG5" t="inlineStr"/>
-      <c r="DH5" t="inlineStr"/>
-      <c r="DI5" t="inlineStr"/>
-      <c r="DJ5" t="inlineStr"/>
-      <c r="DK5" t="inlineStr"/>
-      <c r="DL5" t="inlineStr"/>
-      <c r="DM5" t="inlineStr"/>
-      <c r="DN5" t="inlineStr"/>
-      <c r="DO5" t="inlineStr"/>
-      <c r="DP5" t="inlineStr"/>
-      <c r="DQ5" t="inlineStr"/>
-      <c r="DR5" t="inlineStr"/>
-      <c r="DS5" t="inlineStr"/>
-      <c r="DT5" t="inlineStr"/>
-      <c r="DU5" t="inlineStr"/>
-      <c r="DV5" t="inlineStr"/>
-      <c r="DW5" t="inlineStr"/>
-      <c r="DX5" t="inlineStr"/>
-      <c r="DY5" t="inlineStr"/>
-      <c r="DZ5" t="inlineStr"/>
-      <c r="EA5" t="inlineStr"/>
-      <c r="EB5" t="inlineStr"/>
-      <c r="EC5" t="inlineStr"/>
+      <c r="EC5" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2883,55 +2991,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>71</v>
+        <v>108.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>76</v>
+        <v>98.5</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -2949,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>61</v>
+        <v>68.5</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA6" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3057,46 +3165,46 @@
         <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="BI6" t="n">
         <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.67</v>
+        <v>3.25</v>
       </c>
       <c r="BR6" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BU6" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3105,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.97</v>
+        <v>3.06</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="CC6" t="n">
         <v>2.48</v>
@@ -3126,28 +3234,28 @@
         <v>2.33</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF6" t="n">
         <v>3.24</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CH6" t="n">
         <v>1.3</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="CK6" t="n">
         <v>1.73</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CM6" t="n">
         <v>2.02</v>
@@ -3156,13 +3264,13 @@
         <v>1.62</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.97</v>
+        <v>3.86</v>
       </c>
       <c r="CR6" t="n">
         <v>1.53</v>
@@ -3171,16 +3279,16 @@
         <v>3.39</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CU6" t="n">
         <v>1.34</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="CX6" t="n">
         <v>1.83</v>
@@ -3198,52 +3306,52 @@
         <v>1.44</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DD6" t="n">
         <v>4.38</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.67</v>
+        <v>2.5</v>
       </c>
       <c r="DH6" t="n">
-        <v>107</v>
+        <v>116.75</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DK6" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>72.67</v>
+        <v>84.75</v>
       </c>
       <c r="DN6" t="n">
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.67</v>
+        <v>1.75</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.33</v>
+        <v>10.75</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.33</v>
+        <v>12.5</v>
       </c>
       <c r="DR6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3255,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>61.67</v>
+        <v>65.25</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.67</v>
+        <v>11</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.33</v>
+        <v>8.25</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="EA6" t="n">
-        <v>18</v>
+        <v>13.25</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="7">
@@ -3286,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3379,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>106.5</v>
+        <v>99.67</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="AO7" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>58.5</v>
+        <v>53.67</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD7" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="BF7" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.75</v>
+        <v>1.4</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BS7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BT7" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
         <v>3.47</v>
@@ -3517,55 +3625,55 @@
         <v>4.14</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.23</v>
+        <v>3.49</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.74</v>
+        <v>4.41</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.28</v>
+        <v>5.52</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK7" t="n">
         <v>1.84</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.52</v>
+        <v>4.35</v>
       </c>
       <c r="CR7" t="n">
         <v>1.56</v>
@@ -3580,43 +3688,43 @@
         <v>1.34</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CX7" t="n">
         <v>2.03</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.8</v>
+        <v>4.52</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DG7" t="n">
         <v>2</v>
       </c>
-      <c r="DG7" t="n">
-        <v>2.25</v>
-      </c>
       <c r="DH7" t="n">
-        <v>107.25</v>
+        <v>103</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
@@ -3625,58 +3733,58 @@
         <v>3</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.5</v>
+        <v>46</v>
       </c>
       <c r="DN7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="DP7" t="n">
-        <v>16.5</v>
+        <v>15.8</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.75</v>
+        <v>13.6</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.25</v>
+        <v>6.4</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>9.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.25</v>
+        <v>12.8</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="EC7" t="n">
         <v>3</v>
@@ -3689,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3782,136 +3890,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.5</v>
+        <v>1.67</v>
       </c>
       <c r="AI8" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AL8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>75</v>
+        <v>61.67</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>10.33</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>14.33</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AT8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BN8" t="n">
         <v>2</v>
       </c>
-      <c r="AU8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BU8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BV8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BY8" t="n">
         <v>2.94</v>
@@ -3920,40 +4028,40 @@
         <v>2.84</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CG8" t="n">
         <v>2.4</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="CM8" t="n">
         <v>1.93</v>
@@ -3965,10 +4073,10 @@
         <v>1.39</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.12</v>
+        <v>4.19</v>
       </c>
       <c r="CR8" t="n">
         <v>1.54</v>
@@ -3983,106 +4091,106 @@
         <v>1.36</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CX8" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.63</v>
+        <v>4.7</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="DH8" t="n">
-        <v>107.5</v>
+        <v>107.2</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DM8" t="n">
-        <v>60.25</v>
+        <v>55.2</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.75</v>
+        <v>10.4</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="DR8" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>53.5</v>
+        <v>58.2</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.25</v>
+        <v>10.6</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.75</v>
+        <v>6.8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="EA8" t="n">
-        <v>21</v>
+        <v>16.6</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -4092,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4188,10 +4296,10 @@
         <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>106</v>
+        <v>78.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
@@ -4200,64 +4308,64 @@
         <v>1</v>
       </c>
       <c r="AL9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AS9" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AU9" t="n">
         <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51</v>
+        <v>37.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
       </c>
       <c r="BD9" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.76</v>
+        <v>0.62</v>
       </c>
       <c r="BF9" t="n">
         <v>1</v>
@@ -4266,7 +4374,7 @@
         <v>2</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI9" t="n">
         <v>2</v>
@@ -4275,34 +4383,34 @@
         <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="BN9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -4314,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
         <v>2.99</v>
@@ -4323,73 +4431,73 @@
         <v>3.39</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.66</v>
+        <v>4.82</v>
       </c>
       <c r="CE9" t="n">
         <v>1.48</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CH9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CO9" t="n">
         <v>1.36</v>
       </c>
-      <c r="CI9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>1.35</v>
-      </c>
       <c r="CP9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="CU9" t="n">
         <v>1.36</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="CX9" t="n">
         <v>1.85</v>
@@ -4407,10 +4515,10 @@
         <v>1.41</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
@@ -4419,73 +4527,73 @@
         <v>1</v>
       </c>
       <c r="DG9" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="DH9" t="n">
-        <v>88.25</v>
+        <v>80.8</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="DL9" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="DM9" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.5</v>
+        <v>10.8</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.75</v>
+        <v>6</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41</v>
+        <v>37.6</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.25</v>
+        <v>14.4</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
@@ -4495,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0.5</v>
@@ -4588,49 +4696,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>107.5</v>
+        <v>101.67</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AL10" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>66</v>
+        <v>62.33</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ10" t="n">
         <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4642,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>53.5</v>
+        <v>50</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -4651,73 +4759,73 @@
         <v>11</v>
       </c>
       <c r="BB10" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BH10" t="n">
         <v>7</v>
       </c>
-      <c r="BC10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>6.75</v>
-      </c>
       <c r="BI10" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BO10" t="n">
         <v>1</v>
       </c>
       <c r="BP10" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="BR10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BS10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>1.56</v>
@@ -4726,22 +4834,22 @@
         <v>1.51</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.84</v>
+        <v>3.76</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="CE10" t="n">
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CG10" t="n">
         <v>2.77</v>
@@ -4753,34 +4861,34 @@
         <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CK10" t="n">
         <v>1.85</v>
       </c>
-      <c r="CK10" t="n">
-        <v>1.87</v>
-      </c>
       <c r="CL10" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP10" t="n">
         <v>1.94</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CT10" t="n">
         <v>2.89</v>
@@ -4789,106 +4897,106 @@
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CX10" t="n">
         <v>1.9</v>
       </c>
-      <c r="CW10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>1.92</v>
-      </c>
       <c r="CY10" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC10" t="n">
         <v>2.07</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="DH10" t="n">
-        <v>122</v>
+        <v>115.6</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DM10" t="n">
-        <v>69.25</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="DP10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
         <v>12</v>
       </c>
-      <c r="DQ10" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="DR10" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="DS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX10" t="n">
-        <v>12.25</v>
-      </c>
       <c r="DY10" t="n">
-        <v>8.25</v>
+        <v>7.2</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="EA10" t="n">
-        <v>15</v>
+        <v>11.8</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -4898,11 +5006,11 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
         <v>3</v>
       </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
@@ -4910,13 +5018,13 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>97.5</v>
+        <v>101.33</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -4925,34 +5033,34 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>4.67</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5</v>
+        <v>-0.67</v>
       </c>
       <c r="M11" t="n">
-        <v>50</v>
+        <v>42.67</v>
       </c>
       <c r="N11" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="P11" t="n">
-        <v>13.5</v>
+        <v>12.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="R11" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -4964,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>44</v>
+        <v>45.67</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.5</v>
+        <v>8.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.5</v>
+        <v>5.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC11" t="n">
-        <v>18</v>
+        <v>11.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5069,43 +5177,43 @@
         <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BP11" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="BR11" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -5120,19 +5228,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CC11" t="n">
         <v>2.27</v>
@@ -5141,124 +5249,124 @@
         <v>2.65</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="CH11" t="n">
         <v>1.34</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="CK11" t="n">
         <v>1.89</v>
       </c>
       <c r="CL11" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CN11" t="n">
         <v>1.44</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="CU11" t="n">
         <v>1.34</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="CW11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CX11" t="n">
         <v>2.01</v>
       </c>
-      <c r="CX11" t="n">
-        <v>2</v>
-      </c>
       <c r="CY11" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.46</v>
+        <v>4.74</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.67</v>
+        <v>0.25</v>
       </c>
       <c r="DH11" t="n">
-        <v>99</v>
+        <v>101.5</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.67</v>
+        <v>4.5</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0.33</v>
+        <v>-0.5</v>
       </c>
       <c r="DM11" t="n">
-        <v>49.67</v>
+        <v>44.25</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DO11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DP11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.67</v>
+        <v>4</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5270,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45.33</v>
+        <v>46.25</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DX11" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="DY11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="DZ11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="EC11" t="n">
         <v>3</v>
-      </c>
-      <c r="EA11" t="n">
-        <v>18</v>
-      </c>
-      <c r="EB11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="EC11" t="n">
-        <v>3.33</v>
       </c>
     </row>
     <row r="12">
@@ -5301,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0.33</v>
@@ -5394,121 +5502,121 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP12" t="n">
         <v>2</v>
       </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>93</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AQ12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>47</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC12" t="n">
         <v>2</v>
       </c>
-      <c r="AL12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>45</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>45</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC12" t="n">
+      <c r="BD12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BF12" t="n">
         <v>3</v>
       </c>
-      <c r="BD12" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2</v>
-      </c>
       <c r="BG12" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.25</v>
+        <v>7.4</v>
       </c>
       <c r="BI12" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BS12" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BT12" t="n">
         <v>0</v>
@@ -5523,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BY12" t="n">
         <v>2.58</v>
@@ -5535,22 +5643,22 @@
         <v>3.22</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CH12" t="n">
         <v>1.39</v>
@@ -5559,28 +5667,28 @@
         <v>1.96</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CO12" t="n">
         <v>1.29</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.49</v>
+        <v>3.44</v>
       </c>
       <c r="CR12" t="n">
         <v>1.47</v>
@@ -5595,73 +5703,73 @@
         <v>1.35</v>
       </c>
       <c r="CV12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF12" t="n">
         <v>2</v>
       </c>
-      <c r="CW12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DB12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DC12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="DD12" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="DE12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DF12" t="n">
-        <v>1.75</v>
-      </c>
       <c r="DG12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DH12" t="n">
-        <v>107</v>
+        <v>110.8</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.25</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
-        <v>56</v>
+        <v>57.2</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.25</v>
+        <v>12.8</v>
       </c>
       <c r="DQ12" t="n">
         <v>13</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.25</v>
+        <v>4.8</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5673,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.25</v>
+        <v>49.2</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.75</v>
+        <v>10</v>
       </c>
       <c r="DY12" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.75</v>
+        <v>14.8</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="EC12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -5704,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -5716,82 +5824,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>19</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA13" t="n">
         <v>10</v>
       </c>
-      <c r="Q13" t="n">
-        <v>17</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="AB13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC13" t="n">
         <v>9</v>
       </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>19</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5875,49 +5983,49 @@
         <v>1.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.33</v>
+        <v>7.25</v>
       </c>
       <c r="BI13" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="BR13" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BS13" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -5926,19 +6034,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="CC13" t="n">
         <v>2.01</v>
@@ -5947,16 +6055,16 @@
         <v>2.04</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI13" t="n">
         <v>1.96</v>
@@ -5965,25 +6073,25 @@
         <v>1.8</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CO13" t="n">
         <v>1.31</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.53</v>
+        <v>3.46</v>
       </c>
       <c r="CR13" t="n">
         <v>1.46</v>
@@ -5998,106 +6106,106 @@
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CW13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CX13" t="n">
         <v>1.85</v>
       </c>
-      <c r="CX13" t="n">
-        <v>1.89</v>
-      </c>
       <c r="CY13" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="CZ13" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="DH13" t="n">
-        <v>92.33</v>
+        <v>96.5</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.67</v>
+        <v>4.25</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="DM13" t="n">
-        <v>55.67</v>
+        <v>59.5</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.67</v>
+        <v>11</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.33</v>
+        <v>16</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.33</v>
+        <v>6</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.33</v>
+        <v>14.5</v>
       </c>
       <c r="DY13" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="EA13" t="n">
-        <v>15.33</v>
+        <v>11.25</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -1424,10 +1424,10 @@
         <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1445,25 +1445,25 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>36</v>
+        <v>39.5</v>
       </c>
       <c r="Y2" t="n">
         <v>0.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AB2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.5</v>
+        <v>20.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="AE2" t="n">
         <v>4</v>
@@ -1553,7 +1553,7 @@
         <v>2.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="BI2" t="n">
         <v>2.2</v>
@@ -1736,10 +1736,10 @@
         <v>11.8</v>
       </c>
       <c r="DQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="DS2" t="n">
         <v>0.4</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>37</v>
+        <v>38.4</v>
       </c>
       <c r="DW2" t="n">
         <v>0.4</v>
       </c>
       <c r="DX2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DY2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="EA2" t="n">
-        <v>13.2</v>
+        <v>17.6</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="EC2" t="n">
         <v>2.8</v>
@@ -1890,7 +1890,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AM3" t="n">
         <v>-0.5</v>
@@ -1908,10 +1908,10 @@
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
@@ -1929,25 +1929,25 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42.5</v>
+        <v>42</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BF3" t="n">
         <v>2</v>
@@ -1956,7 +1956,7 @@
         <v>2</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BI3" t="n">
         <v>2</v>
@@ -2121,7 +2121,7 @@
         <v>1.4</v>
       </c>
       <c r="DK3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="DL3" t="n">
         <v>-0.2</v>
@@ -2139,10 +2139,10 @@
         <v>11.4</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="DS3" t="n">
         <v>0.4</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.4</v>
+        <v>19.4</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="EC3" t="n">
         <v>1.4</v>
@@ -2230,10 +2230,10 @@
         <v>10.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.33</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>2.33</v>
+        <v>5.33</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -2251,25 +2251,25 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>57.33</v>
+        <v>59.33</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="AA4" t="n">
         <v>9</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.33</v>
+        <v>19.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE4" t="n">
         <v>2.67</v>
@@ -2542,10 +2542,10 @@
         <v>11</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,25 +2557,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>58.4</v>
+        <v>59.6</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="DY4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>12.6</v>
+        <v>16.8</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="EC4" t="n">
         <v>2.2</v>
@@ -2633,10 +2633,10 @@
         <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -2654,25 +2654,25 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -2945,10 +2945,10 @@
         <v>12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>16</v>
+        <v>15.75</v>
       </c>
       <c r="DR5" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,25 +2960,25 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="DW5" t="n">
         <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="EC5" t="n">
         <v>2.5</v>
@@ -3018,7 +3018,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>11.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -3057,25 +3057,25 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>68.5</v>
+        <v>67</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>6</v>
+        <v>24.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.52</v>
+        <v>1.96</v>
       </c>
       <c r="AE6" t="n">
         <v>1.5</v>
@@ -3165,7 +3165,7 @@
         <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.75</v>
+        <v>10.25</v>
       </c>
       <c r="BI6" t="n">
         <v>2</v>
@@ -3330,7 +3330,7 @@
         <v>2.25</v>
       </c>
       <c r="DK6" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
@@ -3351,7 +3351,7 @@
         <v>12.5</v>
       </c>
       <c r="DR6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>65.25</v>
+        <v>64.5</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.25</v>
+        <v>9.75</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="EA6" t="n">
-        <v>13.25</v>
+        <v>22.5</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="EC6" t="n">
         <v>2.25</v>
@@ -3523,7 +3523,7 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
         <v>2</v>
@@ -3541,25 +3541,25 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.67</v>
+        <v>55</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>10</v>
+        <v>11.33</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>8.33</v>
       </c>
       <c r="BC7" t="n">
         <v>3</v>
       </c>
       <c r="BD7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BF7" t="n">
         <v>3.67</v>
@@ -3754,7 +3754,7 @@
         <v>13.6</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="DS7" t="n">
         <v>0.4</v>
@@ -3766,25 +3766,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="DZ7" t="n">
         <v>3</v>
       </c>
       <c r="EA7" t="n">
-        <v>12.8</v>
+        <v>15.8</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="EC7" t="n">
         <v>3</v>
@@ -3905,7 +3905,7 @@
         <v>2.67</v>
       </c>
       <c r="AL8" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
@@ -3923,10 +3923,10 @@
         <v>10.33</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.33</v>
+        <v>13.67</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.67</v>
+        <v>2.67</v>
       </c>
       <c r="AT8" t="n">
         <v>1.33</v>
@@ -3944,25 +3944,25 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>62.33</v>
+        <v>60</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.67</v>
+        <v>14</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>9.67</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.67</v>
+        <v>4.33</v>
       </c>
       <c r="BD8" t="n">
-        <v>14.67</v>
+        <v>21.33</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="BF8" t="n">
         <v>2.67</v>
@@ -3971,7 +3971,7 @@
         <v>3</v>
       </c>
       <c r="BH8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BI8" t="n">
         <v>3</v>
@@ -4136,7 +4136,7 @@
         <v>2.2</v>
       </c>
       <c r="DK8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="DL8" t="n">
         <v>0.2</v>
@@ -4154,10 +4154,10 @@
         <v>10.4</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="DR8" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="DS8" t="n">
         <v>0.2</v>
@@ -4169,25 +4169,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.2</v>
+        <v>56.8</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.6</v>
+        <v>12</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.6</v>
+        <v>20.6</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="EC8" t="n">
         <v>2.2</v>
@@ -4326,10 +4326,10 @@
         <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="AT9" t="n">
         <v>1.5</v>
@@ -4347,25 +4347,25 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB9" t="n">
         <v>3.5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.5</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
       </c>
       <c r="BD9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="BF9" t="n">
         <v>1</v>
@@ -4374,7 +4374,7 @@
         <v>2</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="BI9" t="n">
         <v>2</v>
@@ -4557,10 +4557,10 @@
         <v>14</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="DR9" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0.2</v>
@@ -4572,25 +4572,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>37.6</v>
+        <v>38.2</v>
       </c>
       <c r="DW9" t="n">
         <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="DY9" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="DZ9" t="n">
         <v>3.2</v>
       </c>
       <c r="EA9" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="EC9" t="n">
         <v>1.4</v>
@@ -4732,7 +4732,7 @@
         <v>14</v>
       </c>
       <c r="AS10" t="n">
-        <v>3</v>
+        <v>6.33</v>
       </c>
       <c r="AT10" t="n">
         <v>0.33</v>
@@ -4750,22 +4750,22 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.67</v>
+        <v>6.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="BD10" t="n">
-        <v>8</v>
+        <v>13.67</v>
       </c>
       <c r="BE10" t="n">
         <v>1.52</v>
@@ -4963,7 +4963,7 @@
         <v>12.6</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,22 +4975,22 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.4</v>
+        <v>55.2</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="EA10" t="n">
-        <v>11.8</v>
+        <v>15.2</v>
       </c>
       <c r="EB10" t="n">
         <v>1.58</v>
@@ -5051,10 +5051,10 @@
         <v>12.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.67</v>
+        <v>9</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>8.33</v>
       </c>
       <c r="S11" t="n">
         <v>0.67</v>
@@ -5072,25 +5072,25 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.67</v>
+        <v>46</v>
       </c>
       <c r="Y11" t="n">
         <v>0.67</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.33</v>
+        <v>10.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.33</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.67</v>
+        <v>17.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
         <v>3</v>
@@ -5180,7 +5180,7 @@
         <v>1.25</v>
       </c>
       <c r="BH11" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="BI11" t="n">
         <v>1.25</v>
@@ -5363,10 +5363,10 @@
         <v>11.5</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="DR11" t="n">
-        <v>4</v>
+        <v>7.25</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5378,25 +5378,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.25</v>
+        <v>46.5</v>
       </c>
       <c r="DW11" t="n">
         <v>0.75</v>
       </c>
       <c r="DX11" t="n">
-        <v>8.5</v>
+        <v>10.25</v>
       </c>
       <c r="DY11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="EA11" t="n">
-        <v>13.25</v>
+        <v>17.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="EC11" t="n">
         <v>3</v>
@@ -5517,7 +5517,7 @@
         <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AM12" t="n">
         <v>-0.5</v>
@@ -5535,10 +5535,10 @@
         <v>16.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
         <v>0.5</v>
@@ -5556,25 +5556,25 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.95</v>
+        <v>1.2</v>
       </c>
       <c r="BF12" t="n">
         <v>3</v>
@@ -5583,7 +5583,7 @@
         <v>1.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BI12" t="n">
         <v>1.6</v>
@@ -5748,7 +5748,7 @@
         <v>2.8</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="DL12" t="n">
         <v>-0</v>
@@ -5766,10 +5766,10 @@
         <v>12.8</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,25 +5781,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.2</v>
+        <v>52</v>
       </c>
       <c r="DW12" t="n">
         <v>0.2</v>
       </c>
       <c r="DX12" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="EA12" t="n">
-        <v>14.8</v>
+        <v>17</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="EC12" t="n">
         <v>2.4</v>
@@ -5839,7 +5839,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>19</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S13" t="n">
         <v>0.5</v>
@@ -5878,25 +5878,25 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>42.5</v>
+        <v>35.5</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AB13" t="n">
         <v>4.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -5986,7 +5986,7 @@
         <v>2.25</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.25</v>
+        <v>7.75</v>
       </c>
       <c r="BI13" t="n">
         <v>2.25</v>
@@ -6151,7 +6151,7 @@
         <v>1.25</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="DL13" t="n">
         <v>-0.25</v>
@@ -6172,7 +6172,7 @@
         <v>16</v>
       </c>
       <c r="DR13" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="DS13" t="n">
         <v>0.25</v>
@@ -6184,25 +6184,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.5</v>
+        <v>46</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.5</v>
+        <v>14.75</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="DZ13" t="n">
         <v>5</v>
       </c>
       <c r="EA13" t="n">
-        <v>11.25</v>
+        <v>15.25</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="EC13" t="n">
         <v>1.25</v>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>0.5</v>
@@ -3084,127 +3084,127 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>117</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC6" t="n">
         <v>2</v>
       </c>
-      <c r="AH6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>125</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>71</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>62</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3</v>
-      </c>
       <c r="BD6" t="n">
-        <v>20.5</v>
+        <v>13.33</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="BF6" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="BG6" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.25</v>
+        <v>11.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BS6" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BT6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY6" t="n">
         <v>1.92</v>
@@ -3222,169 +3222,169 @@
         <v>1.93</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="CC6" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="CG6" t="n">
         <v>2.48</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>2.51</v>
       </c>
       <c r="CH6" t="n">
         <v>1.3</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.86</v>
+        <v>4.01</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CS6" t="n">
         <v>3.39</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CU6" t="n">
         <v>1.34</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.38</v>
+        <v>4.5</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="DH6" t="n">
-        <v>116.75</v>
+        <v>113.6</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="DK6" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>84.75</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="DN6" t="n">
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.75</v>
+        <v>12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="DR6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="DZ6" t="n">
         <v>3</v>
       </c>
-      <c r="DS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="DY6" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="DZ6" t="n">
-        <v>3.75</v>
-      </c>
       <c r="EA6" t="n">
-        <v>22.5</v>
+        <v>17.8</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="7">
@@ -5006,11 +5006,11 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
         <v>4</v>
       </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H11" t="n">
-        <v>101.33</v>
+        <v>100.25</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>4.67</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.67</v>
+        <v>-0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>42.67</v>
+        <v>51.5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.33</v>
+        <v>0.5</v>
       </c>
       <c r="P11" t="n">
-        <v>12.33</v>
+        <v>11.25</v>
       </c>
       <c r="Q11" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z11" t="n">
         <v>9</v>
       </c>
-      <c r="R11" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>46</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>10.67</v>
-      </c>
       <c r="AA11" t="n">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.33</v>
+        <v>12.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,43 +5177,43 @@
         <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.25</v>
+        <v>9.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BP11" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.75</v>
+        <v>1.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BS11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CC11" t="n">
         <v>2.27</v>
@@ -5249,43 +5249,43 @@
         <v>2.65</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.19</v>
+        <v>3.27</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CK11" t="n">
         <v>1.89</v>
       </c>
       <c r="CL11" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="CR11" t="n">
         <v>1.56</v>
@@ -5300,73 +5300,73 @@
         <v>1.34</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CX11" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DB11" t="n">
         <v>1.48</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.74</v>
+        <v>4.78</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.25</v>
+        <v>1.2</v>
       </c>
       <c r="DH11" t="n">
-        <v>101.5</v>
+        <v>100.6</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.25</v>
+        <v>51</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10</v>
+        <v>12.4</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.25</v>
+        <v>5.6</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.5</v>
+        <v>47.4</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.25</v>
+        <v>9</v>
       </c>
       <c r="DY11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.5</v>
+        <v>13.8</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="EC11" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -1394,7 +1394,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>83</v>
@@ -1409,7 +1409,7 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
         <v>36</v>
@@ -1418,7 +1418,7 @@
         <v>1.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="n">
         <v>13</v>
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
         <v>1.33</v>
@@ -1484,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="AL2" t="n">
         <v>3.33</v>
@@ -1547,7 +1547,7 @@
         <v>1.22</v>
       </c>
       <c r="BF2" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BG2" t="n">
         <v>2.2</v>
@@ -1577,10 +1577,10 @@
         <v>0.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
@@ -1703,10 +1703,10 @@
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="DH2" t="n">
         <v>86.8</v>
@@ -1715,13 +1715,13 @@
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="DK2" t="n">
         <v>3.4</v>
       </c>
       <c r="DL2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="DM2" t="n">
         <v>44.4</v>
@@ -1730,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="DP2" t="n">
         <v>11.8</v>
@@ -1772,7 +1772,7 @@
         <v>1.18</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
@@ -1878,7 +1878,7 @@
         <v>1.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="AI3" t="n">
         <v>101.5</v>
@@ -1893,7 +1893,7 @@
         <v>3</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>55</v>
@@ -1902,7 +1902,7 @@
         <v>0.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>10.5</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1980,10 +1980,10 @@
         <v>0.8</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="BR3" t="n">
         <v>60</v>
@@ -2109,7 +2109,7 @@
         <v>0.6</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="DH3" t="n">
         <v>105</v>
@@ -2124,7 +2124,7 @@
         <v>3.2</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
         <v>52</v>
@@ -2133,7 +2133,7 @@
         <v>0.8</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="DP3" t="n">
         <v>11.4</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>59.33</v>
+        <v>59.67</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>59.6</v>
+        <v>59.8</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>1.67</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
         <v>90</v>
@@ -2699,7 +2699,7 @@
         <v>5.67</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
         <v>54</v>
@@ -2708,7 +2708,7 @@
         <v>1.67</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.33</v>
+        <v>2.67</v>
       </c>
       <c r="AQ5" t="n">
         <v>12.67</v>
@@ -2741,10 +2741,10 @@
         <v>0.33</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.67</v>
+        <v>12.33</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
         <v>5.33</v>
@@ -2753,7 +2753,7 @@
         <v>20.33</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BF5" t="n">
         <v>3</v>
@@ -2786,10 +2786,10 @@
         <v>0.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.75</v>
+        <v>4.25</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.75</v>
+        <v>4.25</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
@@ -2915,7 +2915,7 @@
         <v>1.5</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="DH5" t="n">
         <v>92</v>
@@ -2930,7 +2930,7 @@
         <v>4.75</v>
       </c>
       <c r="DL5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DM5" t="n">
         <v>53.5</v>
@@ -2939,7 +2939,7 @@
         <v>1.25</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="DP5" t="n">
         <v>12</v>
@@ -2966,10 +2966,10 @@
         <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.5</v>
+        <v>12.25</v>
       </c>
       <c r="DY5" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="DZ5" t="n">
         <v>5.5</v>
@@ -2978,7 +2978,7 @@
         <v>22</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="EC5" t="n">
         <v>2.5</v>
@@ -3006,7 +3006,7 @@
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
         <v>108.5</v>
@@ -3021,7 +3021,7 @@
         <v>12.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
         <v>98.5</v>
@@ -3030,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="P6" t="n">
         <v>6</v>
@@ -3117,10 +3117,10 @@
         <v>16</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.33</v>
+        <v>11.67</v>
       </c>
       <c r="AS6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AT6" t="n">
         <v>1.33</v>
@@ -3138,25 +3138,25 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>57.67</v>
+        <v>56</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="BC6" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BD6" t="n">
-        <v>13.33</v>
+        <v>21.33</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BF6" t="n">
         <v>2.67</v>
@@ -3189,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="BR6" t="n">
         <v>80</v>
@@ -3318,7 +3318,7 @@
         <v>1.2</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="DH6" t="n">
         <v>113.6</v>
@@ -3333,7 +3333,7 @@
         <v>7.4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DM6" t="n">
         <v>82.59999999999999</v>
@@ -3342,16 +3342,16 @@
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="DP6" t="n">
         <v>12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="DR6" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.8</v>
+        <v>22.6</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="EC6" t="n">
         <v>2.2</v>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
         <v>1.5</v>
@@ -3415,7 +3415,7 @@
         <v>108</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
@@ -3430,7 +3430,7 @@
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3466,19 +3466,19 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
         <v>2.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AC7" t="n">
         <v>15.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -3547,10 +3547,10 @@
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.33</v>
+        <v>11.67</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.33</v>
+        <v>8.67</v>
       </c>
       <c r="BC7" t="n">
         <v>3</v>
@@ -3559,7 +3559,7 @@
         <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BF7" t="n">
         <v>3.67</v>
@@ -3718,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="DG7" t="n">
         <v>2</v>
@@ -3727,7 +3727,7 @@
         <v>103</v>
       </c>
       <c r="DI7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DJ7" t="n">
         <v>3</v>
@@ -3742,7 +3742,7 @@
         <v>46</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DO7" t="n">
         <v>0.6</v>
@@ -3772,19 +3772,19 @@
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="DY7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="EA7" t="n">
         <v>15.8</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="EC7" t="n">
         <v>3</v>
@@ -3893,7 +3893,7 @@
         <v>1.67</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>108</v>
@@ -3908,7 +3908,7 @@
         <v>4.33</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="AN8" t="n">
         <v>61.67</v>
@@ -3917,7 +3917,7 @@
         <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
         <v>10.33</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>14</v>
+        <v>14.33</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
         <v>4.33</v>
@@ -3962,7 +3962,7 @@
         <v>21.33</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="BF8" t="n">
         <v>2.67</v>
@@ -3995,10 +3995,10 @@
         <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -4124,7 +4124,7 @@
         <v>1.2</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="DH8" t="n">
         <v>107.2</v>
@@ -4139,7 +4139,7 @@
         <v>5.2</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
         <v>55.2</v>
@@ -4148,7 +4148,7 @@
         <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="DP8" t="n">
         <v>10.4</v>
@@ -4175,10 +4175,10 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.2</v>
@@ -4187,7 +4187,7 @@
         <v>20.6</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="EC8" t="n">
         <v>2.2</v>
@@ -4215,7 +4215,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.33</v>
+        <v>1.67</v>
       </c>
       <c r="H9" t="n">
         <v>82.33</v>
@@ -4230,7 +4230,7 @@
         <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="M9" t="n">
         <v>46.67</v>
@@ -4239,7 +4239,7 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
         <v>13.67</v>
@@ -4272,19 +4272,19 @@
         <v>0.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.33</v>
+        <v>11</v>
       </c>
       <c r="AA9" t="n">
         <v>7.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AC9" t="n">
         <v>18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
         <v>1.67</v>
@@ -4296,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AI9" t="n">
         <v>78.5</v>
@@ -4311,7 +4311,7 @@
         <v>3.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="AN9" t="n">
         <v>35</v>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ9" t="n">
         <v>14.5</v>
@@ -4398,10 +4398,10 @@
         <v>0.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR9" t="n">
         <v>80</v>
@@ -4527,7 +4527,7 @@
         <v>1</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="DH9" t="n">
         <v>80.8</v>
@@ -4542,7 +4542,7 @@
         <v>3.2</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="DM9" t="n">
         <v>42</v>
@@ -4551,7 +4551,7 @@
         <v>0.6</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DP9" t="n">
         <v>14</v>
@@ -4578,19 +4578,19 @@
         <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DY9" t="n">
         <v>5.8</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="EA9" t="n">
         <v>17.2</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="EC9" t="n">
         <v>1.4</v>
@@ -4615,7 +4615,7 @@
         <v>0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
         <v>3.5</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K10" t="n">
         <v>5</v>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>66</v>
+        <v>66.5</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>1.66</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4927,7 +4927,7 @@
         <v>0.2</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG10" t="n">
         <v>2.8</v>
@@ -4939,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="DK10" t="n">
         <v>4.8</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.2</v>
+        <v>55.4</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
@@ -4996,7 +4996,7 @@
         <v>1.58</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5021,7 +5021,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>100.25</v>
@@ -5036,7 +5036,7 @@
         <v>5.5</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
         <v>51.5</v>
@@ -5045,16 +5045,16 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
         <v>11.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.25</v>
+        <v>11</v>
       </c>
       <c r="R11" t="n">
-        <v>6</v>
+        <v>8.25</v>
       </c>
       <c r="S11" t="n">
         <v>0.5</v>
@@ -5072,25 +5072,25 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>47.25</v>
+        <v>48.5</v>
       </c>
       <c r="Y11" t="n">
         <v>0.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>12.75</v>
+        <v>17.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
         <v>2.5</v>
@@ -5204,10 +5204,10 @@
         <v>0.6</v>
       </c>
       <c r="BP11" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="BR11" t="n">
         <v>80</v>
@@ -5333,7 +5333,7 @@
         <v>2.2</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="DH11" t="n">
         <v>100.6</v>
@@ -5348,7 +5348,7 @@
         <v>5.2</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="DM11" t="n">
         <v>51</v>
@@ -5357,16 +5357,16 @@
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="DP11" t="n">
         <v>10.8</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.4</v>
+        <v>11.4</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5378,25 +5378,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>47.4</v>
+        <v>48.4</v>
       </c>
       <c r="DW11" t="n">
         <v>0.6</v>
       </c>
       <c r="DX11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="DY11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EA11" t="n">
-        <v>13.8</v>
+        <v>17.8</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="EC11" t="n">
         <v>2.6</v>
@@ -5421,7 +5421,7 @@
         <v>0.33</v>
       </c>
       <c r="F12" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -5433,7 +5433,7 @@
         <v>0.33</v>
       </c>
       <c r="J12" t="n">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="K12" t="n">
         <v>4</v>
@@ -5496,7 +5496,7 @@
         <v>1.49</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>2.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
         <v>109.5</v>
@@ -5520,7 +5520,7 @@
         <v>3.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>53.5</v>
@@ -5529,7 +5529,7 @@
         <v>0.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>16.5</v>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -5565,16 +5565,16 @@
         <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="BD12" t="n">
         <v>17</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BF12" t="n">
         <v>3</v>
@@ -5607,10 +5607,10 @@
         <v>0.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="BR12" t="n">
         <v>80</v>
@@ -5733,10 +5733,10 @@
         <v>0.2</v>
       </c>
       <c r="DF12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DG12" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="DH12" t="n">
         <v>110.8</v>
@@ -5745,13 +5745,13 @@
         <v>0.2</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="DK12" t="n">
         <v>3.8</v>
       </c>
       <c r="DL12" t="n">
-        <v>-0</v>
+        <v>0.2</v>
       </c>
       <c r="DM12" t="n">
         <v>57.2</v>
@@ -5760,7 +5760,7 @@
         <v>0.6</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="DP12" t="n">
         <v>12.8</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="DW12" t="n">
         <v>0.2</v>
@@ -5790,19 +5790,19 @@
         <v>11.4</v>
       </c>
       <c r="DY12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="EA12" t="n">
         <v>17</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -5827,7 +5827,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>95</v>
@@ -5842,7 +5842,7 @@
         <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
         <v>60</v>
@@ -5851,7 +5851,7 @@
         <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
         <v>9.5</v>
@@ -5908,7 +5908,7 @@
         <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.5</v>
+        <v>3.5</v>
       </c>
       <c r="AI13" t="n">
         <v>98</v>
@@ -5923,7 +5923,7 @@
         <v>6</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>59</v>
@@ -5932,7 +5932,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>12.5</v>
@@ -6010,10 +6010,10 @@
         <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.75</v>
+        <v>4.5</v>
       </c>
       <c r="BR13" t="n">
         <v>75</v>
@@ -6139,7 +6139,7 @@
         <v>1</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0.25</v>
+        <v>2.25</v>
       </c>
       <c r="DH13" t="n">
         <v>96.5</v>
@@ -6154,7 +6154,7 @@
         <v>4.5</v>
       </c>
       <c r="DL13" t="n">
-        <v>-0.25</v>
+        <v>0.75</v>
       </c>
       <c r="DM13" t="n">
         <v>59.5</v>
@@ -6163,7 +6163,7 @@
         <v>0.25</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
       <c r="DP13" t="n">
         <v>11</v>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -1391,43 +1391,43 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>3.67</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>36</v>
+        <v>40.33</v>
       </c>
       <c r="N2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>14.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.5</v>
+        <v>12.67</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1436,37 +1436,37 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>39.5</v>
+        <v>41.67</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>9</v>
+        <v>7.67</v>
       </c>
       <c r="AA2" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.5</v>
+        <v>13.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AE2" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,46 +1550,46 @@
         <v>1.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.8</v>
+        <v>11.17</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.2</v>
+        <v>4.67</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
@@ -1601,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.35</v>
+        <v>2.82</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.52</v>
+        <v>2.91</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CC2" t="n">
         <v>4.05</v>
@@ -1625,49 +1625,49 @@
         <v>1.43</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CH2" t="n">
         <v>1.34</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.85</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CM2" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP2" t="n">
         <v>2.11</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="CU2" t="n">
         <v>1.36</v>
@@ -1691,88 +1691,88 @@
         <v>1.59</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="DH2" t="n">
-        <v>86.8</v>
+        <v>87.66</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>44.4</v>
+        <v>45.16</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.8</v>
+        <v>12.66</v>
       </c>
       <c r="DQ2" t="n">
-        <v>9.6</v>
+        <v>11.17</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.6</v>
+        <v>6.16</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>38.4</v>
+        <v>39.67</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DX2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="DY2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.2</v>
+        <v>3.67</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.6</v>
+        <v>14.5</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0.33</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AI3" t="n">
-        <v>101.5</v>
+        <v>100.67</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AL3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="AS3" t="n">
         <v>3</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5</v>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AW3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.4</v>
-      </c>
       <c r="BK3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="BR3" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BT3" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>3.72</v>
@@ -2013,40 +2013,40 @@
         <v>4.17</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.66</v>
+        <v>3.57</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.38</v>
+        <v>4.6</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.64</v>
+        <v>4.76</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK3" t="n">
         <v>1.83</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="CM3" t="n">
         <v>1.95</v>
@@ -2058,10 +2058,10 @@
         <v>1.34</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CR3" t="n">
         <v>1.5</v>
@@ -2082,10 +2082,10 @@
         <v>2.04</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CZ3" t="n">
         <v>1.86</v>
@@ -2094,88 +2094,88 @@
         <v>1.52</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.05</v>
+        <v>4.24</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="DH3" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.2</v>
+        <v>-0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="DM3" t="n">
-        <v>52</v>
+        <v>50.16</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.4</v>
+        <v>11.34</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.6</v>
+        <v>11.84</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.2</v>
+        <v>5.84</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>40.4</v>
+        <v>42.5</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.4</v>
+        <v>16</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,130 +2275,130 @@
         <v>2.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>2.67</v>
       </c>
       <c r="AI4" t="n">
-        <v>141</v>
+        <v>123.67</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.5</v>
+        <v>-0.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AM4" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AN4" t="n">
-        <v>54.5</v>
+        <v>54.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>8</v>
+        <v>10.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
       </c>
       <c r="AU4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BG4" t="n">
         <v>2</v>
       </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BH4" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.6</v>
+        <v>4.67</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
         <v>2.26</v>
@@ -2416,64 +2416,64 @@
         <v>2.31</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="CU4" t="n">
         <v>1.38</v>
@@ -2485,67 +2485,67 @@
         <v>1.78</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="CZ4" t="n">
         <v>1.92</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="DH4" t="n">
-        <v>143.8</v>
+        <v>134.67</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.2</v>
+        <v>-0.16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.2</v>
+        <v>4.34</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>64.2</v>
+        <v>62.67</v>
       </c>
       <c r="DN4" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>11</v>
+        <v>11.34</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.6</v>
+        <v>12.34</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.2</v>
+        <v>4.16</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>59.8</v>
+        <v>55.17</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.2</v>
+        <v>10.83</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.8</v>
+        <v>13.83</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -2678,52 +2678,52 @@
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.67</v>
+        <v>6.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>54</v>
+        <v>55.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.67</v>
+        <v>14.25</v>
       </c>
       <c r="AR5" t="n">
-        <v>16.67</v>
+        <v>17.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>57.33</v>
+        <v>56.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.33</v>
+        <v>9.75</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.33</v>
+        <v>15</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BM5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BU5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
         <v>1.6</v>
@@ -2819,46 +2819,46 @@
         <v>1.44</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="CH5" t="n">
         <v>1.33</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.87</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="CO5" t="n">
         <v>1.36</v>
@@ -2867,19 +2867,19 @@
         <v>2.16</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV5" t="n">
         <v>1.85</v>
@@ -2903,52 +2903,52 @@
         <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="DH5" t="n">
-        <v>92</v>
+        <v>93.2</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.75</v>
+        <v>5.6</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>53.5</v>
+        <v>54.8</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="DP5" t="n">
-        <v>12</v>
+        <v>13.4</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.75</v>
+        <v>16.4</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.25</v>
+        <v>4.8</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56</v>
+        <v>55.6</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.25</v>
+        <v>10.2</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.75</v>
+        <v>5.8</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="EA5" t="n">
-        <v>22</v>
+        <v>17.4</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>5.67</v>
       </c>
       <c r="H6" t="n">
-        <v>108.5</v>
+        <v>106.33</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>98.5</v>
+        <v>99.67</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>11.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>67</v>
+        <v>69.33</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -3066,19 +3066,19 @@
         <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AC6" t="n">
-        <v>24.5</v>
+        <v>16</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,49 +3162,49 @@
         <v>2.67</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
       <c r="BR6" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>20</v>
+        <v>33.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.05</v>
+        <v>3.19</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="CC6" t="n">
         <v>2.51</v>
@@ -3234,43 +3234,43 @@
         <v>2.37</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CF6" t="n">
         <v>3.31</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CH6" t="n">
         <v>1.3</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.96</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.01</v>
+        <v>4.06</v>
       </c>
       <c r="CR6" t="n">
         <v>1.54</v>
@@ -3294,13 +3294,13 @@
         <v>1.98</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CZ6" t="n">
         <v>1.85</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DB6" t="n">
         <v>1.45</v>
@@ -3309,49 +3309,49 @@
         <v>2.4</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.5</v>
+        <v>4.51</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="DH6" t="n">
-        <v>113.6</v>
+        <v>111.66</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="DK6" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DM6" t="n">
-        <v>82.59999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="DN6" t="n">
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="DP6" t="n">
-        <v>12</v>
+        <v>13.84</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.6</v>
+        <v>12.34</v>
       </c>
       <c r="DR6" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>60.4</v>
+        <v>62.66</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.8</v>
+        <v>12.34</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.6</v>
+        <v>8.67</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.6</v>
+        <v>18.66</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>99.67</v>
+        <v>90.5</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="AL7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BP7" t="n">
         <v>3.33</v>
       </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>3</v>
-      </c>
       <c r="BQ7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BR7" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BS7" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BY7" t="n">
         <v>3.47</v>
@@ -3625,31 +3625,31 @@
         <v>4.14</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.49</v>
+        <v>3.54</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.41</v>
+        <v>4.8</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.52</v>
+        <v>5.62</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CJ7" t="n">
         <v>2.02</v>
@@ -3661,13 +3661,13 @@
         <v>2.29</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CN7" t="n">
         <v>1.56</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP7" t="n">
         <v>2.25</v>
@@ -3682,7 +3682,7 @@
         <v>3.39</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CU7" t="n">
         <v>1.34</v>
@@ -3694,25 +3694,25 @@
         <v>2.15</v>
       </c>
       <c r="CX7" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DA7" t="n">
         <v>1.49</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3724,70 +3724,70 @@
         <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>103</v>
+        <v>96.33</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>46</v>
+        <v>41.67</v>
       </c>
       <c r="DN7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>45</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>13</v>
+      </c>
+      <c r="EB7" t="n">
         <v>1</v>
       </c>
-      <c r="DO7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>1.16</v>
-      </c>
       <c r="EC7" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="G8" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H8" t="n">
+        <v>100</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M8" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
-        <v>106</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.5</v>
-      </c>
       <c r="P8" t="n">
-        <v>10.5</v>
+        <v>9.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17.33</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>52</v>
+        <v>51.67</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.5</v>
+        <v>12.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3971,67 +3971,67 @@
         <v>3</v>
       </c>
       <c r="BH8" t="n">
-        <v>7.4</v>
+        <v>7.83</v>
       </c>
       <c r="BI8" t="n">
         <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BN8" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BP8" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="CC8" t="n">
         <v>2.62</v>
@@ -4040,43 +4040,43 @@
         <v>2.68</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CK8" t="n">
         <v>1.84</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CN8" t="n">
         <v>1.54</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
       <c r="CR8" t="n">
         <v>1.54</v>
@@ -4097,100 +4097,100 @@
         <v>2.04</v>
       </c>
       <c r="CX8" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CY8" t="n">
         <v>2.4</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DA8" t="n">
         <v>1.53</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="DE8" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="DH8" t="n">
-        <v>107.2</v>
+        <v>104</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>55.2</v>
+        <v>54.5</v>
       </c>
       <c r="DN8" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
         <v>2</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.6</v>
+        <v>15.5</v>
       </c>
       <c r="DR8" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>56.8</v>
+        <v>55.84</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.2</v>
+        <v>11.16</v>
       </c>
       <c r="DY8" t="n">
-        <v>8</v>
+        <v>7.34</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.6</v>
+        <v>17</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -4212,49 +4212,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H9" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M9" t="n">
+        <v>44</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="H9" t="n">
-        <v>82.33</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M9" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P9" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="R9" t="n">
-        <v>9</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.33</v>
-      </c>
       <c r="T9" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>37.67</v>
+        <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>11</v>
+        <v>10.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.33</v>
+        <v>6</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>18</v>
+        <v>13.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,46 +4371,46 @@
         <v>1</v>
       </c>
       <c r="BG9" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.2</v>
+        <v>9.83</v>
       </c>
       <c r="BI9" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BM9" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR9" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -4422,19 +4422,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.99</v>
+        <v>2.79</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="CA9" t="n">
         <v>3.11</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="CC9" t="n">
         <v>4.15</v>
@@ -4449,10 +4449,10 @@
         <v>2.99</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI9" t="n">
         <v>1.89</v>
@@ -4464,7 +4464,7 @@
         <v>1.78</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CM9" t="n">
         <v>1.94</v>
@@ -4473,13 +4473,13 @@
         <v>1.55</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="CR9" t="n">
         <v>1.52</v>
@@ -4500,100 +4500,100 @@
         <v>2</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.22</v>
+        <v>4.38</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DG9" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.8</v>
+        <v>84</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DM9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DP9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.2</v>
+        <v>11.67</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>38.2</v>
+        <v>39.67</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.8</v>
+        <v>5.17</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.2</v>
+        <v>14.17</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
@@ -4603,58 +4603,58 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="H10" t="n">
-        <v>136.5</v>
+        <v>129.67</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>72.5</v>
+        <v>68.67</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>10.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="R10" t="n">
-        <v>7.5</v>
+        <v>4.67</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>66.5</v>
+        <v>61</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.5</v>
+        <v>12.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.5</v>
+        <v>8.33</v>
       </c>
       <c r="AB10" t="n">
         <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.5</v>
+        <v>11.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BH10" t="n">
-        <v>7</v>
+        <v>7.17</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BO10" t="n">
         <v>1</v>
       </c>
       <c r="BP10" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="BR10" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.76</v>
+        <v>3.69</v>
       </c>
       <c r="CC10" t="n">
         <v>2.11</v>
@@ -4849,49 +4849,49 @@
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CR10" t="n">
         <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
@@ -4903,37 +4903,37 @@
         <v>1.93</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="DB10" t="n">
         <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="DH10" t="n">
-        <v>115.6</v>
+        <v>115.67</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
@@ -4942,28 +4942,28 @@
         <v>2</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.4</v>
+        <v>0.66</v>
       </c>
       <c r="DM10" t="n">
-        <v>66.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.4</v>
+        <v>12.34</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.6</v>
+        <v>12.16</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,25 +4975,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.4</v>
+        <v>54.5</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.2</v>
+        <v>11.83</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.6</v>
+        <v>7.33</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.2</v>
+        <v>12.5</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="EC10" t="n">
         <v>2</v>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="n">
         <v>5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>100.25</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.5</v>
-      </c>
       <c r="P11" t="n">
-        <v>11.25</v>
+        <v>11.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="R11" t="n">
-        <v>8.25</v>
+        <v>6.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>48.5</v>
+        <v>52.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.75</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
         <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,43 +5177,43 @@
         <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.6</v>
+        <v>10.17</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.4</v>
+        <v>5.83</v>
       </c>
       <c r="BR11" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CC11" t="n">
         <v>2.27</v>
@@ -5255,10 +5255,10 @@
         <v>3.27</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI11" t="n">
         <v>1.8</v>
@@ -5267,16 +5267,16 @@
         <v>1.93</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CO11" t="n">
         <v>1.4</v>
@@ -5285,16 +5285,16 @@
         <v>2.22</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.12</v>
+        <v>4.13</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="CU11" t="n">
         <v>1.34</v>
@@ -5306,100 +5306,100 @@
         <v>2.11</v>
       </c>
       <c r="CX11" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.78</v>
+        <v>4.64</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.6</v>
+        <v>100.67</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.2</v>
+        <v>5.67</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DM11" t="n">
-        <v>51</v>
+        <v>53.5</v>
       </c>
       <c r="DN11" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.8</v>
+        <v>11.33</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.4</v>
+        <v>11.67</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.4</v>
+        <v>51.67</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DX11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="DY11" t="n">
-        <v>8</v>
+        <v>7.17</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.8</v>
+        <v>14.67</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0.33</v>
@@ -5502,13 +5502,13 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>109.5</v>
+        <v>108.67</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -5517,34 +5517,34 @@
         <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>53.5</v>
+        <v>54.33</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16.5</v>
+        <v>17.33</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.5</v>
+        <v>10.67</v>
       </c>
       <c r="AS12" t="n">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,70 +5556,70 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>53.5</v>
+        <v>52</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>8.33</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>6.33</v>
       </c>
       <c r="BC12" t="n">
         <v>2</v>
       </c>
       <c r="BD12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="BF12" t="n">
         <v>3</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.8</v>
+        <v>8.17</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="BR12" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BY12" t="n">
         <v>2.58</v>
@@ -5640,55 +5640,55 @@
         <v>2.75</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CL12" t="n">
         <v>2.33</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="CR12" t="n">
         <v>1.47</v>
@@ -5712,13 +5712,13 @@
         <v>1.89</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CZ12" t="n">
         <v>1.91</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DB12" t="n">
         <v>1.35</v>
@@ -5727,49 +5727,49 @@
         <v>2.11</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="DH12" t="n">
-        <v>110.8</v>
+        <v>110.17</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.8</v>
+        <v>4.16</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DM12" t="n">
-        <v>57.2</v>
+        <v>57</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.8</v>
+        <v>13.83</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.6</v>
+        <v>12.34</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.2</v>
+        <v>5.83</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.8</v>
+        <v>51.34</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.4</v>
+        <v>10.33</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.33</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="EA12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5905,127 +5905,127 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AI13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.5</v>
+        <v>11.67</v>
       </c>
       <c r="AR13" t="n">
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BF13" t="n">
         <v>2</v>
       </c>
-      <c r="AV13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BG13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BM13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BO13" t="n">
         <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY13" t="n">
         <v>2.1</v>
@@ -6043,67 +6043,67 @@
         <v>2.52</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.01</v>
+        <v>2.41</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.04</v>
+        <v>2.49</v>
       </c>
       <c r="CE13" t="n">
         <v>1.42</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH13" t="n">
         <v>1.36</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV13" t="n">
         <v>2.04</v>
@@ -6112,16 +6112,16 @@
         <v>1.82</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CZ13" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DB13" t="n">
         <v>1.33</v>
@@ -6136,76 +6136,76 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="DH13" t="n">
-        <v>96.5</v>
+        <v>96.2</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DM13" t="n">
-        <v>59.5</v>
+        <v>63</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16</v>
+        <v>15.4</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46</v>
+        <v>46.8</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.75</v>
+        <v>14.2</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.75</v>
+        <v>9.4</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="EA13" t="n">
-        <v>15.25</v>
+        <v>12</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>3.67</v>
@@ -1421,13 +1421,13 @@
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>14.33</v>
+        <v>13.67</v>
       </c>
       <c r="Q2" t="n">
         <v>12.67</v>
       </c>
       <c r="R2" t="n">
-        <v>2.33</v>
+        <v>5.67</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>41.67</v>
+        <v>40.67</v>
       </c>
       <c r="Y2" t="n">
         <v>0.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.67</v>
+        <v>8.67</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.67</v>
+        <v>5.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.33</v>
+        <v>19.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.33</v>
+        <v>3.67</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DG2" t="n">
         <v>1.16</v>
@@ -1715,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="DK2" t="n">
         <v>3.5</v>
@@ -1733,13 +1733,13 @@
         <v>1.66</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.66</v>
+        <v>12.34</v>
       </c>
       <c r="DQ2" t="n">
         <v>11.17</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.16</v>
+        <v>7.84</v>
       </c>
       <c r="DS2" t="n">
         <v>0.33</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>39.67</v>
+        <v>39.17</v>
       </c>
       <c r="DW2" t="n">
         <v>0.33</v>
       </c>
       <c r="DX2" t="n">
-        <v>8.17</v>
+        <v>8.67</v>
       </c>
       <c r="DY2" t="n">
-        <v>4.5</v>
+        <v>4.83</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.67</v>
+        <v>3.83</v>
       </c>
       <c r="EA2" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="3">
@@ -1905,13 +1905,13 @@
         <v>1.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.67</v>
+        <v>11.33</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>45.33</v>
+        <v>46</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>10.67</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
         <v>1.02</v>
@@ -2136,13 +2136,13 @@
         <v>1.5</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.34</v>
+        <v>11.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.84</v>
+        <v>11.66</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.84</v>
+        <v>6.5</v>
       </c>
       <c r="DS3" t="n">
         <v>0.33</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>42.5</v>
+        <v>42.84</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>2.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>16</v>
+        <v>21.16</v>
       </c>
       <c r="EB3" t="n">
         <v>1.12</v>
@@ -2308,13 +2308,13 @@
         <v>1.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>12.33</v>
       </c>
       <c r="AR4" t="n">
         <v>10.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>3</v>
+        <v>5.67</v>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
@@ -2338,19 +2338,19 @@
         <v>0.33</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.33</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>6.67</v>
       </c>
       <c r="BC4" t="n">
         <v>3.33</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.33</v>
+        <v>14</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="BF4" t="n">
         <v>1.33</v>
@@ -2539,13 +2539,13 @@
         <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.34</v>
+        <v>11.5</v>
       </c>
       <c r="DQ4" t="n">
         <v>12.34</v>
       </c>
       <c r="DR4" t="n">
-        <v>4.16</v>
+        <v>5.5</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2563,19 +2563,19 @@
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.83</v>
+        <v>11.66</v>
       </c>
       <c r="DY4" t="n">
-        <v>7</v>
+        <v>7.84</v>
       </c>
       <c r="DZ4" t="n">
         <v>3.83</v>
       </c>
       <c r="EA4" t="n">
-        <v>13.83</v>
+        <v>16.66</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="EC4" t="n">
         <v>2</v>
@@ -2681,7 +2681,7 @@
         <v>0.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
@@ -2693,7 +2693,7 @@
         <v>0.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AL5" t="n">
         <v>6.5</v>
@@ -2714,10 +2714,10 @@
         <v>14.25</v>
       </c>
       <c r="AR5" t="n">
-        <v>17.25</v>
+        <v>16.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AT5" t="n">
         <v>0.75</v>
@@ -2735,28 +2735,28 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>56.5</v>
+        <v>57.25</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.75</v>
+        <v>11.75</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.75</v>
+        <v>7.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>15</v>
+        <v>19.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="BG5" t="n">
         <v>2.8</v>
@@ -2912,7 +2912,7 @@
         <v>0.4</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="DG5" t="n">
         <v>2.4</v>
@@ -2924,7 +2924,7 @@
         <v>0.2</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="DK5" t="n">
         <v>5.6</v>
@@ -2945,10 +2945,10 @@
         <v>13.4</v>
       </c>
       <c r="DQ5" t="n">
-        <v>16.4</v>
+        <v>15.6</v>
       </c>
       <c r="DR5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.6</v>
+        <v>56.2</v>
       </c>
       <c r="DW5" t="n">
         <v>0.2</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.2</v>
+        <v>11.8</v>
       </c>
       <c r="DY5" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.4</v>
+        <v>21.2</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -3039,7 +3039,7 @@
         <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="S6" t="n">
         <v>0.67</v>
@@ -3057,25 +3057,25 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>69.33</v>
+        <v>59.33</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>16.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>10</v>
+        <v>11.33</v>
       </c>
       <c r="AB6" t="n">
         <v>5</v>
       </c>
       <c r="AC6" t="n">
-        <v>16</v>
+        <v>23.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -3351,7 +3351,7 @@
         <v>12.34</v>
       </c>
       <c r="DR6" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>62.66</v>
+        <v>57.66</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.34</v>
+        <v>13</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.67</v>
+        <v>9.33</v>
       </c>
       <c r="DZ6" t="n">
         <v>3.67</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.66</v>
+        <v>22.5</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="EC6" t="n">
         <v>2.34</v>
@@ -3520,10 +3520,10 @@
         <v>15.25</v>
       </c>
       <c r="AR7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.25</v>
+        <v>8.5</v>
       </c>
       <c r="AT7" t="n">
         <v>2.25</v>
@@ -3541,25 +3541,25 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47.75</v>
+        <v>55.25</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="BC7" t="n">
         <v>2.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>11.75</v>
+        <v>18</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF7" t="n">
         <v>3.25</v>
@@ -3751,10 +3751,10 @@
         <v>15.83</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.5</v>
+        <v>15.17</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.17</v>
+        <v>9</v>
       </c>
       <c r="DS7" t="n">
         <v>0.33</v>
@@ -3766,22 +3766,22 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.17</v>
+        <v>5.33</v>
       </c>
       <c r="DZ7" t="n">
         <v>2.67</v>
       </c>
       <c r="EA7" t="n">
-        <v>13</v>
+        <v>17.17</v>
       </c>
       <c r="EB7" t="n">
         <v>1</v>
@@ -3806,7 +3806,7 @@
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0.67</v>
@@ -3842,10 +3842,10 @@
         <v>9.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.33</v>
+        <v>16.67</v>
       </c>
       <c r="R8" t="n">
-        <v>2.33</v>
+        <v>5.33</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -3863,25 +3863,25 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.67</v>
+        <v>49</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>11.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.67</v>
+        <v>7.33</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.67</v>
+        <v>17.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
         <v>1.33</v>
@@ -4118,7 +4118,7 @@
         <v>4.55</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
         <v>1.17</v>
@@ -4154,10 +4154,10 @@
         <v>10</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.5</v>
+        <v>15.17</v>
       </c>
       <c r="DR8" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="DS8" t="n">
         <v>0.34</v>
@@ -4169,25 +4169,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>55.84</v>
+        <v>54.5</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.16</v>
+        <v>12.83</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.34</v>
+        <v>8.67</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.83</v>
+        <v>4.16</v>
       </c>
       <c r="EA8" t="n">
-        <v>17</v>
+        <v>19.33</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="EC8" t="n">
         <v>2</v>
@@ -4242,13 +4242,13 @@
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="Q9" t="n">
         <v>13</v>
       </c>
-      <c r="Q9" t="n">
-        <v>13.5</v>
-      </c>
       <c r="R9" t="n">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -4266,22 +4266,22 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>40</v>
+        <v>39.5</v>
       </c>
       <c r="Y9" t="n">
         <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.25</v>
+        <v>10.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>13.25</v>
+        <v>20.5</v>
       </c>
       <c r="AD9" t="n">
         <v>1.27</v>
@@ -4554,13 +4554,13 @@
         <v>1.17</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.5</v>
+        <v>13.67</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.67</v>
+        <v>11.33</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.5</v>
+        <v>8.33</v>
       </c>
       <c r="DS9" t="n">
         <v>0.17</v>
@@ -4572,22 +4572,22 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>39.67</v>
+        <v>39.33</v>
       </c>
       <c r="DW9" t="n">
         <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.67</v>
+        <v>8.83</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.17</v>
+        <v>5.5</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="EA9" t="n">
-        <v>14.17</v>
+        <v>19</v>
       </c>
       <c r="EB9" t="n">
         <v>1.1</v>
@@ -4651,7 +4651,7 @@
         <v>10.33</v>
       </c>
       <c r="R10" t="n">
-        <v>4.67</v>
+        <v>9</v>
       </c>
       <c r="S10" t="n">
         <v>1.33</v>
@@ -4669,25 +4669,25 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.33</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="AB10" t="n">
         <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.33</v>
+        <v>16.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AE10" t="n">
         <v>1.67</v>
@@ -4963,7 +4963,7 @@
         <v>12.16</v>
       </c>
       <c r="DR10" t="n">
-        <v>5.5</v>
+        <v>7.66</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,25 +4975,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.83</v>
+        <v>12.16</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.33</v>
+        <v>7.66</v>
       </c>
       <c r="DZ10" t="n">
         <v>4.5</v>
       </c>
       <c r="EA10" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="EC10" t="n">
         <v>2</v>
@@ -5048,13 +5048,13 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
         <v>11.4</v>
       </c>
       <c r="R11" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="S11" t="n">
         <v>0.4</v>
@@ -5078,19 +5078,19 @@
         <v>0.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.8</v>
+        <v>12</v>
       </c>
       <c r="AA11" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB11" t="n">
         <v>3.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>18.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
         <v>2.2</v>
@@ -5360,13 +5360,13 @@
         <v>2.17</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.33</v>
+        <v>11.5</v>
       </c>
       <c r="DQ11" t="n">
         <v>11.67</v>
       </c>
       <c r="DR11" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="DS11" t="n">
         <v>0.17</v>
@@ -5384,19 +5384,19 @@
         <v>0.5</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.17</v>
+        <v>8.17</v>
       </c>
       <c r="DZ11" t="n">
         <v>3.33</v>
       </c>
       <c r="EA11" t="n">
-        <v>14.67</v>
+        <v>18.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="EC11" t="n">
         <v>2.33</v>
@@ -5502,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="AH12" t="n">
         <v>2</v>
@@ -5526,7 +5526,7 @@
         <v>54.33</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AP12" t="n">
         <v>2.33</v>
@@ -5535,10 +5535,10 @@
         <v>17.33</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.67</v>
+        <v>9.67</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.33</v>
+        <v>9.33</v>
       </c>
       <c r="AT12" t="n">
         <v>1</v>
@@ -5556,25 +5556,25 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>52</v>
+        <v>54.67</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.33</v>
+        <v>9.33</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BD12" t="n">
-        <v>11</v>
+        <v>17.33</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="BF12" t="n">
         <v>3</v>
@@ -5733,7 +5733,7 @@
         <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DG12" t="n">
         <v>2</v>
@@ -5757,7 +5757,7 @@
         <v>57</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
         <v>2.16</v>
@@ -5766,10 +5766,10 @@
         <v>13.83</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.34</v>
+        <v>11.84</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.83</v>
+        <v>7.33</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,25 +5781,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.34</v>
+        <v>52.67</v>
       </c>
       <c r="DW12" t="n">
         <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.33</v>
+        <v>10.83</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.33</v>
+        <v>7.66</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="EA12" t="n">
-        <v>14</v>
+        <v>17.16</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="EC12" t="n">
         <v>2.34</v>
@@ -5938,10 +5938,10 @@
         <v>11.67</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>9.33</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
@@ -5959,25 +5959,25 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>54.33</v>
+        <v>53.33</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.67</v>
+        <v>14.33</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.67</v>
+        <v>9.67</v>
       </c>
       <c r="BC13" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.67</v>
+        <v>15</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BF13" t="n">
         <v>2</v>
@@ -6169,10 +6169,10 @@
         <v>10.8</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="DS13" t="n">
         <v>0.2</v>
@@ -6184,25 +6184,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.8</v>
+        <v>46.2</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="EA13" t="n">
-        <v>12</v>
+        <v>15.8</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="EC13" t="n">
         <v>1.6</v>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,124 +1472,124 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>89.33</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>50</v>
+        <v>48.25</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>9.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.67</v>
+        <v>9.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>7.25</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>37.67</v>
+        <v>37.75</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.67</v>
+        <v>11.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.17</v>
+        <v>12</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.67</v>
+        <v>4.43</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.67</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BY2" t="n">
         <v>2.82</v>
@@ -1610,67 +1610,67 @@
         <v>2.91</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CB2" t="n">
         <v>3.39</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.05</v>
+        <v>3.76</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.64</v>
+        <v>4.3</v>
       </c>
       <c r="CE2" t="n">
         <v>1.43</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI2" t="n">
         <v>1.88</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL2" t="n">
         <v>2.43</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO2" t="n">
         <v>1.33</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV2" t="n">
         <v>1.87</v>
@@ -1679,100 +1679,100 @@
         <v>2</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.15</v>
+        <v>4.06</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="DH2" t="n">
-        <v>87.66</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DM2" t="n">
-        <v>45.16</v>
+        <v>44.86</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.34</v>
+        <v>11.43</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.84</v>
+        <v>6.57</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>39.17</v>
+        <v>39</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DX2" t="n">
-        <v>8.67</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DY2" t="n">
-        <v>4.83</v>
+        <v>5.14</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.5</v>
+        <v>14.86</v>
       </c>
       <c r="EB2" t="n">
         <v>1.15</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>0.33</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AH3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS3" t="n">
         <v>3</v>
       </c>
-      <c r="AI3" t="n">
-        <v>100.67</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>50.33</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AU3" t="n">
         <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>46</v>
+        <v>46.25</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.83</v>
+        <v>7.29</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BN3" t="n">
         <v>1</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="BR3" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS3" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU3" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY3" t="n">
         <v>3.72</v>
@@ -2013,64 +2013,64 @@
         <v>4.17</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.6</v>
+        <v>4.02</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.76</v>
+        <v>4.15</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.01</v>
+        <v>3.09</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="CS3" t="n">
         <v>3.2</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="CU3" t="n">
         <v>1.37</v>
@@ -2094,88 +2094,88 @@
         <v>1.52</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.24</v>
+        <v>4.5</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>104</v>
+        <v>105.14</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM3" t="n">
-        <v>50.16</v>
+        <v>49.29</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.5</v>
+        <v>10.43</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.66</v>
+        <v>11.43</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.5</v>
+        <v>5.43</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>42.84</v>
+        <v>43.43</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>9</v>
+        <v>8.57</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.5</v>
+        <v>6.14</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="EA3" t="n">
-        <v>21.16</v>
+        <v>18</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -2197,49 +2197,49 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>145.67</v>
+        <v>138.75</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.67</v>
+        <v>4.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>70.67</v>
+        <v>71.25</v>
       </c>
       <c r="N4" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="P4" t="n">
-        <v>10.67</v>
+        <v>10.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>15.75</v>
       </c>
       <c r="R4" t="n">
-        <v>5.33</v>
+        <v>3.75</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>59.67</v>
+        <v>55.75</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.33</v>
+        <v>10.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>19.33</v>
+        <v>14.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
         <v>0.33</v>
@@ -2359,46 +2359,46 @@
         <v>2</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.67</v>
+        <v>9</v>
       </c>
       <c r="BI4" t="n">
         <v>2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.67</v>
+        <v>4.29</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>4.71</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CC4" t="n">
         <v>2.56</v>
@@ -2428,55 +2428,55 @@
         <v>2.65</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CK4" t="n">
         <v>1.77</v>
       </c>
-      <c r="CK4" t="n">
-        <v>1.78</v>
-      </c>
       <c r="CL4" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO4" t="n">
         <v>1.32</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.52</v>
+        <v>3.59</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV4" t="n">
         <v>2.09</v>
@@ -2485,67 +2485,67 @@
         <v>1.78</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CY4" t="n">
         <v>2.28</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DA4" t="n">
         <v>1.59</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>132.29</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="DN4" t="n">
         <v>1</v>
       </c>
-      <c r="DG4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>134.67</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="DJ4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>62.67</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>1.17</v>
-      </c>
       <c r="DO4" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.5</v>
+        <v>11.14</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.34</v>
+        <v>13.57</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.5</v>
+        <v>4.57</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>55.17</v>
+        <v>53.57</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.66</v>
+        <v>10.43</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.84</v>
+        <v>6.86</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.66</v>
+        <v>14.14</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="EC4" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="5">
@@ -2588,19 +2588,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -2612,70 +2612,70 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>52</v>
+        <v>53.5</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC5" t="n">
         <v>13</v>
       </c>
-      <c r="R5" t="n">
-        <v>4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>52</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>27</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0.25</v>
@@ -2759,70 +2759,70 @@
         <v>3</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.4</v>
+        <v>8.17</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.6</v>
+        <v>3.83</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="CC5" t="n">
         <v>2.17</v>
@@ -2834,46 +2834,46 @@
         <v>1.47</v>
       </c>
       <c r="CF5" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="CR5" t="n">
         <v>1.5</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="CT5" t="n">
         <v>2.69</v>
@@ -2888,10 +2888,10 @@
         <v>2.02</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CZ5" t="n">
         <v>1.86</v>
@@ -2903,52 +2903,52 @@
         <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="DH5" t="n">
-        <v>93.2</v>
+        <v>94</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.6</v>
+        <v>4.83</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DM5" t="n">
-        <v>54.8</v>
+        <v>54.83</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.4</v>
+        <v>13.17</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.6</v>
+        <v>16</v>
       </c>
       <c r="DR5" t="n">
-        <v>6</v>
+        <v>4.83</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.2</v>
+        <v>55.67</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.8</v>
+        <v>10.83</v>
       </c>
       <c r="DY5" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.2</v>
+        <v>17.5</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>0.67</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="n">
         <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>117</v>
+        <v>120.25</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>72</v>
+        <v>76.75</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16</v>
+        <v>16.25</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.67</v>
+        <v>11.25</v>
       </c>
       <c r="AS6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3144,67 +3144,67 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.67</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="BD6" t="n">
-        <v>21.33</v>
+        <v>15.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="BG6" t="n">
         <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>11</v>
+        <v>10.14</v>
       </c>
       <c r="BI6" t="n">
         <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.67</v>
+        <v>5.14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY6" t="n">
         <v>1.83</v>
@@ -3222,64 +3222,64 @@
         <v>1.84</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.37</v>
+        <v>2.52</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CH6" t="n">
         <v>1.3</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CK6" t="n">
         <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CM6" t="n">
         <v>1.96</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CU6" t="n">
         <v>1.34</v>
@@ -3291,67 +3291,67 @@
         <v>2.11</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.51</v>
+        <v>4.45</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="DH6" t="n">
-        <v>111.66</v>
+        <v>114.28</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="DK6" t="n">
-        <v>7.5</v>
+        <v>6.71</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM6" t="n">
-        <v>85.84</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="DN6" t="n">
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>4.16</v>
+        <v>3.71</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.84</v>
+        <v>14.29</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.34</v>
+        <v>12</v>
       </c>
       <c r="DR6" t="n">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>57.66</v>
+        <v>57.43</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
@@ -3372,19 +3372,19 @@
         <v>13</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.5</v>
+        <v>19.14</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
@@ -3406,79 +3406,79 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="H7" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>51.33</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>14.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>39.5</v>
+        <v>44</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -3565,70 +3565,70 @@
         <v>3.25</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="BR7" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BV7" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.14</v>
+        <v>4.01</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.54</v>
+        <v>3.46</v>
       </c>
       <c r="CC7" t="n">
         <v>4.8</v>
@@ -3637,16 +3637,16 @@
         <v>5.62</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI7" t="n">
         <v>1.72</v>
@@ -3655,34 +3655,34 @@
         <v>2.02</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.35</v>
+        <v>4.42</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CS7" t="n">
         <v>3.39</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="CU7" t="n">
         <v>1.34</v>
@@ -3706,13 +3706,13 @@
         <v>1.49</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.53</v>
+        <v>4.76</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3724,70 +3724,70 @@
         <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>96.33</v>
+        <v>98.86</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>41.67</v>
+        <v>44.86</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.83</v>
+        <v>15</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.17</v>
+        <v>13.57</v>
       </c>
       <c r="DR7" t="n">
-        <v>9</v>
+        <v>7.57</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50</v>
+        <v>50.43</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.17</v>
+        <v>14.57</v>
       </c>
       <c r="EB7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="G8" t="n">
-        <v>2.67</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>102.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="K8" t="n">
-        <v>5.67</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>47.33</v>
+        <v>51.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>9.67</v>
+        <v>8.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.67</v>
+        <v>16.25</v>
       </c>
       <c r="R8" t="n">
-        <v>5.33</v>
+        <v>3.75</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U8" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>49</v>
+        <v>49.75</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.33</v>
+        <v>10</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.33</v>
+        <v>6.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.33</v>
+        <v>12.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3971,67 +3971,67 @@
         <v>3</v>
       </c>
       <c r="BH8" t="n">
-        <v>7.83</v>
+        <v>7.43</v>
       </c>
       <c r="BI8" t="n">
         <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.17</v>
+        <v>2.57</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.67</v>
+        <v>2.14</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CC8" t="n">
         <v>2.62</v>
@@ -4040,43 +4040,43 @@
         <v>2.68</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CK8" t="n">
         <v>1.84</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="CR8" t="n">
         <v>1.54</v>
@@ -4109,88 +4109,88 @@
         <v>1.53</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.55</v>
+        <v>4.42</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.34</v>
+        <v>1</v>
       </c>
       <c r="DH8" t="n">
-        <v>104</v>
+        <v>104.86</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DK8" t="n">
-        <v>5</v>
+        <v>4.71</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="DM8" t="n">
-        <v>54.5</v>
+        <v>56</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="DO8" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="DP8" t="n">
-        <v>10</v>
+        <v>9.43</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.17</v>
+        <v>15.14</v>
       </c>
       <c r="DR8" t="n">
-        <v>4</v>
+        <v>3.29</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>54.5</v>
+        <v>54.14</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.83</v>
+        <v>11.86</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.67</v>
+        <v>8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.16</v>
+        <v>3.86</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.33</v>
+        <v>16.43</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4293,28 +4293,28 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AI9" t="n">
-        <v>78.5</v>
+        <v>71.67</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>35</v>
+        <v>32.33</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -4323,94 +4323,94 @@
         <v>1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>8</v>
+        <v>9.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>39</v>
+        <v>38.33</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.5</v>
+        <v>4.67</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
       </c>
       <c r="BD9" t="n">
-        <v>16</v>
+        <v>10.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="BF9" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.83</v>
+        <v>9</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6</v>
+        <v>5.29</v>
       </c>
       <c r="BR9" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY9" t="n">
         <v>2.79</v>
@@ -4431,16 +4431,16 @@
         <v>3.21</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.15</v>
+        <v>4.29</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.82</v>
+        <v>4.89</v>
       </c>
       <c r="CE9" t="n">
         <v>1.48</v>
@@ -4449,37 +4449,37 @@
         <v>2.99</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CH9" t="n">
         <v>1.34</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CK9" t="n">
         <v>1.78</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CO9" t="n">
         <v>1.35</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="CR9" t="n">
         <v>1.52</v>
@@ -4488,7 +4488,7 @@
         <v>3.29</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CU9" t="n">
         <v>1.36</v>
@@ -4500,16 +4500,16 @@
         <v>2</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DB9" t="n">
         <v>1.43</v>
@@ -4524,76 +4524,76 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DH9" t="n">
-        <v>84</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DK9" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DM9" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.67</v>
+        <v>13.57</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.33</v>
+        <v>11.43</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.33</v>
+        <v>7</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>39.33</v>
+        <v>39</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.83</v>
+        <v>8</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.5</v>
+        <v>4.86</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="EA9" t="n">
-        <v>19</v>
+        <v>16.14</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>0.67</v>
@@ -4696,49 +4696,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>101.67</v>
+        <v>98.75</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.67</v>
+        <v>3.75</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>62.33</v>
+        <v>60.75</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="AR10" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.33</v>
+        <v>4.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>48</v>
+        <v>47.75</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.33</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.33</v>
+        <v>5.75</v>
       </c>
       <c r="BC10" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="BD10" t="n">
-        <v>13.67</v>
+        <v>10</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.17</v>
+        <v>6.43</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BO10" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BP10" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.17</v>
+        <v>3.57</v>
       </c>
       <c r="BR10" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BT10" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU10" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV10" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY10" t="n">
         <v>1.76</v>
@@ -4834,28 +4834,28 @@
         <v>1.77</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.11</v>
+        <v>2.37</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="CE10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CH10" t="n">
         <v>1.38</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>1.39</v>
       </c>
       <c r="CI10" t="n">
         <v>1.91</v>
@@ -4864,37 +4864,37 @@
         <v>1.78</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV10" t="n">
         <v>1.94</v>
@@ -4903,67 +4903,67 @@
         <v>1.93</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>115.67</v>
+        <v>112</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="DM10" t="n">
-        <v>65.5</v>
+        <v>64.14</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.34</v>
+        <v>12.43</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.16</v>
+        <v>12.28</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.66</v>
+        <v>6.43</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55</v>
+        <v>53.86</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.16</v>
+        <v>11.29</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.66</v>
+        <v>7.14</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="EA10" t="n">
-        <v>15</v>
+        <v>12.71</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="n">
         <v>6</v>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="H11" t="n">
-        <v>100.4</v>
+        <v>104.17</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M11" t="n">
-        <v>54.4</v>
+        <v>58.33</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>11.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.4</v>
+        <v>12.67</v>
       </c>
       <c r="R11" t="n">
-        <v>7.2</v>
+        <v>5.83</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>52.4</v>
+        <v>54.17</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>12</v>
+        <v>10.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.6</v>
+        <v>15.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,43 +5177,43 @@
         <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.17</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.83</v>
+        <v>5.14</v>
       </c>
       <c r="BR11" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="CA11" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="CC11" t="n">
         <v>2.27</v>
@@ -5252,49 +5252,49 @@
         <v>1.51</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP11" t="n">
         <v>2.22</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CS11" t="n">
         <v>3.37</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CU11" t="n">
         <v>1.34</v>
@@ -5306,100 +5306,100 @@
         <v>2.11</v>
       </c>
       <c r="CX11" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.67</v>
+        <v>103.86</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.67</v>
+        <v>5.29</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DM11" t="n">
-        <v>53.5</v>
+        <v>57</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.5</v>
+        <v>11.43</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.67</v>
+        <v>12.72</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.67</v>
+        <v>5.57</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.67</v>
+        <v>53.29</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.5</v>
+        <v>10.57</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.17</v>
+        <v>7.57</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.5</v>
+        <v>15.71</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="12">
@@ -5409,55 +5409,55 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F12" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>111.67</v>
+        <v>114</v>
       </c>
       <c r="I12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="J12" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="M12" t="n">
-        <v>59.67</v>
+        <v>65.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>10.33</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="R12" t="n">
-        <v>5.33</v>
+        <v>3.75</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.67</v>
+        <v>53.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.33</v>
+        <v>12.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.33</v>
+        <v>8.75</v>
       </c>
       <c r="AB12" t="n">
         <v>4</v>
       </c>
       <c r="AC12" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,46 +5580,46 @@
         <v>3</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.17</v>
+        <v>9.43</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.67</v>
+        <v>5.14</v>
       </c>
       <c r="BR12" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
@@ -5631,16 +5631,16 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CB12" t="n">
         <v>3.37</v>
@@ -5652,13 +5652,13 @@
         <v>3.23</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH12" t="n">
         <v>1.38</v>
@@ -5670,37 +5670,37 @@
         <v>1.77</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CO12" t="n">
         <v>1.3</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CV12" t="n">
         <v>2.03</v>
@@ -5709,16 +5709,16 @@
         <v>1.84</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DB12" t="n">
         <v>1.35</v>
@@ -5727,49 +5727,49 @@
         <v>2.11</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF12" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="DG12" t="n">
-        <v>2</v>
+        <v>3.14</v>
       </c>
       <c r="DH12" t="n">
-        <v>110.17</v>
+        <v>111.72</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.16</v>
+        <v>5.28</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.16</v>
+        <v>0.43</v>
       </c>
       <c r="DM12" t="n">
-        <v>57</v>
+        <v>60.71</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.83</v>
+        <v>13.14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.84</v>
+        <v>11.14</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.33</v>
+        <v>6.14</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.67</v>
+        <v>54</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.83</v>
+        <v>11.28</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.66</v>
+        <v>8</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.16</v>
+        <v>14.57</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5905,127 +5905,127 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.67</v>
+        <v>2.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>97</v>
+        <v>96.25</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.67</v>
+        <v>4.75</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>65</v>
+        <v>63.75</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AP13" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.67</v>
+        <v>11.75</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.67</v>
+        <v>12.25</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.33</v>
+        <v>6.75</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
       </c>
       <c r="AU13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>52</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BN13" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.2</v>
       </c>
       <c r="BO13" t="n">
         <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.4</v>
+        <v>2.67</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="BR13" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BS13" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>2.1</v>
@@ -6043,55 +6043,55 @@
         <v>2.52</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="CE13" t="n">
         <v>1.42</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CH13" t="n">
         <v>1.36</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CK13" t="n">
         <v>1.76</v>
       </c>
-      <c r="CK13" t="n">
-        <v>1.75</v>
-      </c>
       <c r="CL13" t="n">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="CR13" t="n">
         <v>1.45</v>
@@ -6130,82 +6130,82 @@
         <v>2.06</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="DH13" t="n">
-        <v>96.2</v>
+        <v>95.83</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.6</v>
+        <v>4.17</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="DM13" t="n">
-        <v>63</v>
+        <v>62.5</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DO13" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.4</v>
+        <v>6.83</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.6</v>
+        <v>12.83</v>
       </c>
       <c r="DY13" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="EA13" t="n">
-        <v>15.8</v>
+        <v>13</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
@@ -1379,298 +1367,298 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" t="n">
         <v>7</v>
       </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="F2" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="H2" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>2.71</v>
       </c>
       <c r="K2" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>40.33</v>
+        <v>51.71</v>
       </c>
       <c r="N2" t="n">
-        <v>1.33</v>
+        <v>0.57</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>13.67</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.67</v>
+        <v>10.71</v>
       </c>
       <c r="R2" t="n">
-        <v>5.67</v>
+        <v>7.86</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="V2" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>40.67</v>
+        <v>44.29</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.33</v>
+        <v>6.43</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.33</v>
+        <v>18.57</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.67</v>
+        <v>2.29</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.75</v>
+        <v>3.12</v>
       </c>
       <c r="AM2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>53.38</v>
+      </c>
+      <c r="AO2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN2" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AP2" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.75</v>
+        <v>11.62</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.75</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.25</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>37.75</v>
+        <v>41.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>5.62</v>
       </c>
       <c r="BC2" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BD2" t="n">
-        <v>11.5</v>
+        <v>18.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="BH2" t="n">
-        <v>12</v>
+        <v>9.33</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.57</v>
+        <v>0.87</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.43</v>
+        <v>3.33</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="BR2" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS2" t="n">
-        <v>85.70999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BX2" t="n">
-        <v>85.70999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.76</v>
+        <v>3.42</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.3</v>
+        <v>3.88</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CM2" t="n">
         <v>2.02</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.71</v>
+        <v>3.9</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV2" t="n">
         <v>1.87</v>
@@ -1679,16 +1667,16 @@
         <v>2</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DB2" t="n">
         <v>1.39</v>
@@ -1697,82 +1685,82 @@
         <v>2.23</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.57</v>
+        <v>1.06</v>
       </c>
       <c r="DH2" t="n">
-        <v>85.43000000000001</v>
+        <v>94.67</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
       <c r="DM2" t="n">
-        <v>44.86</v>
+        <v>52.6</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.53</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.43</v>
+        <v>11.8</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.57</v>
+        <v>8.4</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>39</v>
+        <v>42.8</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX2" t="n">
-        <v>8.859999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.14</v>
+        <v>6</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.71</v>
+        <v>3.53</v>
       </c>
       <c r="EA2" t="n">
-        <v>14.86</v>
+        <v>18.4</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.57</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="3">
@@ -1782,298 +1770,298 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="n">
         <v>7</v>
       </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
       <c r="E3" t="n">
-        <v>0.33</v>
+        <v>0.12</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="G3" t="n">
-        <v>1.67</v>
+        <v>0.88</v>
       </c>
       <c r="H3" t="n">
-        <v>107.33</v>
+        <v>88.5</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.33</v>
+        <v>2.38</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.67</v>
+        <v>0.25</v>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>10.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>12.38</v>
       </c>
       <c r="R3" t="n">
-        <v>8.67</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="U3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>100.57</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BK3" t="n">
         <v>0.33</v>
       </c>
-      <c r="V3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>39.67</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>48.75</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>46.25</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.29</v>
-      </c>
       <c r="BL3" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="BN3" t="n">
         <v>1</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.57</v>
+        <v>2.2</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.57</v>
+        <v>2.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>71.43000000000001</v>
+        <v>80</v>
       </c>
       <c r="BS3" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.29</v>
+        <v>6.67</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>42.86</v>
+        <v>26.67</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.72</v>
+        <v>3.46</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.17</v>
+        <v>3.82</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.49</v>
+        <v>3.43</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.02</v>
+        <v>4.2</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="CN3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="CR3" t="n">
         <v>1.54</v>
       </c>
-      <c r="CO3" t="n">
+      <c r="CS3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CU3" t="n">
         <v>1.36</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>1.37</v>
       </c>
       <c r="CV3" t="n">
         <v>1.84</v>
@@ -2082,13 +2070,13 @@
         <v>2.04</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DA3" t="n">
         <v>1.52</v>
@@ -2100,82 +2088,82 @@
         <v>2.38</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.43</v>
+        <v>1.06</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="DH3" t="n">
-        <v>105.14</v>
+        <v>94.13</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.29</v>
+        <v>1.93</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="DM3" t="n">
-        <v>49.29</v>
+        <v>49.4</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.43</v>
+        <v>0.67</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.43</v>
+        <v>11.2</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.43</v>
+        <v>11.8</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.43</v>
+        <v>8.34</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.43</v>
+        <v>40.6</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.57</v>
+        <v>9.33</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.14</v>
+        <v>6.53</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="EA3" t="n">
-        <v>18</v>
+        <v>19.33</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="4">
@@ -2185,61 +2173,61 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
         <v>7</v>
       </c>
-      <c r="C4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H4" t="n">
+        <v>134</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M4" t="n">
+        <v>69.12</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.75</v>
       </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>138.75</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M4" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="O4" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="P4" t="n">
-        <v>10.25</v>
+        <v>10.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.75</v>
+        <v>11.88</v>
       </c>
       <c r="R4" t="n">
-        <v>3.75</v>
+        <v>5.62</v>
       </c>
       <c r="S4" t="n">
         <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>55.75</v>
+        <v>58.12</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2260,223 +2248,223 @@
         <v>10.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>7</v>
+        <v>7.38</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.25</v>
+        <v>21.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG4" t="n">
         <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AI4" t="n">
-        <v>123.67</v>
+        <v>112.86</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AU4" t="n">
         <v>2</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BP4" t="n">
         <v>4</v>
       </c>
-      <c r="AM4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>54.67</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>50.67</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>4.29</v>
-      </c>
       <c r="BQ4" t="n">
-        <v>4.71</v>
+        <v>4.47</v>
       </c>
       <c r="BR4" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>14.29</v>
+        <v>26.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.14</v>
+        <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.56</v>
+        <v>2.85</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CO4" t="n">
         <v>1.32</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="CR4" t="n">
         <v>1.45</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV4" t="n">
         <v>2.09</v>
@@ -2485,67 +2473,67 @@
         <v>1.78</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CZ4" t="n">
         <v>1.94</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.67</v>
+        <v>3.83</v>
       </c>
       <c r="DE4" t="n">
         <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.29</v>
+        <v>2.07</v>
       </c>
       <c r="DH4" t="n">
-        <v>132.29</v>
+        <v>124.13</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.14</v>
+        <v>3.54</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.43</v>
+        <v>0.34</v>
       </c>
       <c r="DM4" t="n">
-        <v>64.14</v>
+        <v>61.13</v>
       </c>
       <c r="DN4" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.14</v>
+        <v>12.33</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.57</v>
+        <v>10.54</v>
       </c>
       <c r="DR4" t="n">
-        <v>4.57</v>
+        <v>6.53</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2557,28 +2545,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.57</v>
+        <v>53.46</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.43</v>
+        <v>10.87</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.57</v>
+        <v>3.87</v>
       </c>
       <c r="EA4" t="n">
-        <v>14.14</v>
+        <v>18.53</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="5">
@@ -2588,298 +2576,298 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C5" t="n">
         <v>6</v>
       </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
       <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H5" t="n">
+        <v>105</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>101.44</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="BC5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>98</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>92</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>57.25</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD5" t="n">
-        <v>19.75</v>
+        <v>16.89</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="BF5" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.33</v>
+        <v>0.93</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BN5" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.83</v>
+        <v>4.6</v>
       </c>
       <c r="BR5" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS5" t="n">
         <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="CH5" t="n">
         <v>1.34</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.74</v>
+        <v>3.63</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV5" t="n">
         <v>1.85</v>
@@ -2888,100 +2876,100 @@
         <v>2.02</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="DG5" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="DH5" t="n">
-        <v>94</v>
+        <v>102.86</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.83</v>
+        <v>5.27</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.33</v>
+        <v>0.13</v>
       </c>
       <c r="DM5" t="n">
-        <v>54.83</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.17</v>
+        <v>10.86</v>
       </c>
       <c r="DQ5" t="n">
-        <v>16</v>
+        <v>13.87</v>
       </c>
       <c r="DR5" t="n">
-        <v>4.83</v>
+        <v>6.2</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.67</v>
+        <v>57.2</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.83</v>
+        <v>12.53</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.5</v>
+        <v>8.26</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.5</v>
+        <v>18.6</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="6">
@@ -2991,220 +2979,220 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
         <v>7</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H6" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M6" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>53.62</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>111</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="n">
+      <c r="AL6" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="AS6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="AT6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AU6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="H6" t="n">
-        <v>106.33</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>11</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="AV6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>52</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BM6" t="n">
         <v>0.33</v>
       </c>
-      <c r="M6" t="n">
-        <v>99.67</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="BN6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BO6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="P6" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>13</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>59.33</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>23.67</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>120.25</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>76.75</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>56</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BP6" t="n">
-        <v>5.14</v>
+        <v>4.2</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5</v>
+        <v>4.07</v>
       </c>
       <c r="BR6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BU6" t="n">
-        <v>14.29</v>
+        <v>6.67</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,34 +3201,34 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CH6" t="n">
         <v>1.3</v>
@@ -3252,37 +3240,37 @@
         <v>1.94</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.05</v>
+        <v>4.11</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CS6" t="n">
         <v>3.38</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CV6" t="n">
         <v>1.77</v>
@@ -3291,100 +3279,100 @@
         <v>2.11</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.45</v>
+        <v>4.53</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.29</v>
+        <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="DG6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DO6" t="n">
         <v>3</v>
       </c>
-      <c r="DH6" t="n">
-        <v>114.28</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>86.56999999999999</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>3.71</v>
-      </c>
       <c r="DP6" t="n">
-        <v>14.29</v>
+        <v>14.87</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="DR6" t="n">
-        <v>2.29</v>
+        <v>4.6</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>57.43</v>
+        <v>52.86</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.140000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.14</v>
+        <v>22.14</v>
       </c>
       <c r="EB6" t="n">
         <v>1.71</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -3394,298 +3382,298 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" t="n">
         <v>7</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H7" t="n">
+        <v>94</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="H7" t="n">
-        <v>110</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P7" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
+      <c r="T7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="P7" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>11</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>44</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AH7" t="n">
         <v>2</v>
       </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AI7" t="n">
-        <v>90.5</v>
+        <v>94.75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.25</v>
+        <v>16.12</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.5</v>
+        <v>12.25</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.5</v>
+        <v>7.38</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AU7" t="n">
         <v>0.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>55.25</v>
+        <v>48.88</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.75</v>
+        <v>5.62</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="BD7" t="n">
-        <v>18</v>
+        <v>14.75</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.29</v>
+        <v>2.93</v>
       </c>
       <c r="BH7" t="n">
-        <v>7</v>
+        <v>6.87</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.29</v>
+        <v>2.93</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.14</v>
+        <v>0.47</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.71</v>
+        <v>1.13</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.71</v>
+        <v>3.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>71.43000000000001</v>
+        <v>80</v>
       </c>
       <c r="BS7" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.86</v>
+        <v>53.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>28.57</v>
+        <v>46.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.4</v>
+        <v>4.63</v>
       </c>
       <c r="BZ7" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CQ7" t="n">
         <v>4.01</v>
       </c>
-      <c r="CA7" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CN7" t="n">
+      <c r="CR7" t="n">
         <v>1.54</v>
       </c>
-      <c r="CO7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>1.58</v>
-      </c>
       <c r="CS7" t="n">
-        <v>3.39</v>
+        <v>3.24</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CV7" t="n">
         <v>1.74</v>
@@ -3694,25 +3682,25 @@
         <v>2.15</v>
       </c>
       <c r="CX7" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.76</v>
+        <v>4.39</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3721,73 +3709,73 @@
         <v>2</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DH7" t="n">
-        <v>98.86</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>44.86</v>
+        <v>47.93</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.71</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DP7" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.57</v>
+        <v>12</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.57</v>
+        <v>7.8</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.43</v>
+        <v>45.4</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.140000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.57</v>
+        <v>5.53</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.57</v>
+        <v>2.27</v>
       </c>
       <c r="EA7" t="n">
-        <v>14.57</v>
+        <v>14.87</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="8">
@@ -3797,73 +3785,73 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.75</v>
+        <v>1.12</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="H8" t="n">
-        <v>102.5</v>
+        <v>101.25</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="K8" t="n">
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>51.75</v>
+        <v>59.38</v>
       </c>
       <c r="N8" t="n">
         <v>0.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="P8" t="n">
-        <v>8.75</v>
+        <v>10.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.25</v>
+        <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>3.75</v>
+        <v>4.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
         <v>1.25</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>49.75</v>
+        <v>52.88</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -3872,223 +3860,223 @@
         <v>10</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.75</v>
+        <v>18.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI8" t="n">
-        <v>108</v>
+        <v>98.86</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>61.67</v>
+        <v>56.29</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
       </c>
       <c r="AP8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="AT8" t="n">
         <v>1</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>51.57</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BN8" t="n">
         <v>1.33</v>
       </c>
-      <c r="AU8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
+      <c r="BO8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BT8" t="n">
         <v>60</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>100</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>71.43000000000001</v>
-      </c>
       <c r="BU8" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.29</v>
+        <v>6.67</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>85.70999999999999</v>
+        <v>53.33</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.73</v>
+        <v>2.48</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.99</v>
+        <v>3.09</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.15</v>
+        <v>3.26</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.68</v>
+        <v>3.27</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CH8" t="n">
         <v>1.3</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV8" t="n">
         <v>1.84</v>
@@ -4097,100 +4085,100 @@
         <v>2.04</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="CZ8" t="n">
         <v>1.82</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC8" t="n">
         <v>2.37</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.14</v>
+        <v>1.47</v>
       </c>
       <c r="DG8" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="DH8" t="n">
-        <v>104.86</v>
+        <v>100.13</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="DL8" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="DM8" t="n">
-        <v>56</v>
+        <v>57.94</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.43</v>
+        <v>10.87</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.14</v>
+        <v>13</v>
       </c>
       <c r="DR8" t="n">
-        <v>3.29</v>
+        <v>5.33</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>54.14</v>
+        <v>52.27</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.86</v>
+        <v>10.33</v>
       </c>
       <c r="DY8" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.86</v>
+        <v>3.53</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.43</v>
+        <v>18.74</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.86</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="9">
@@ -4200,298 +4188,298 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
         <v>7</v>
       </c>
-      <c r="C9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="H9" t="n">
-        <v>86.75</v>
+        <v>92.25</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
         <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="N9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P9" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T9" t="n">
         <v>0.75</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P9" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>13</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AU9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
+      <c r="AV9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CH9" t="n">
         <v>1.33</v>
       </c>
-      <c r="AH9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>71.67</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>32.33</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>38.33</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>1.34</v>
-      </c>
       <c r="CI9" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CO9" t="n">
         <v>1.35</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV9" t="n">
         <v>1.87</v>
@@ -4500,100 +4488,100 @@
         <v>2</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.38</v>
+        <v>4.27</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.29000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DK9" t="n">
-        <v>2.57</v>
+        <v>3.33</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM9" t="n">
-        <v>39</v>
+        <v>52.67</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.57</v>
+        <v>13.13</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.43</v>
+        <v>12.33</v>
       </c>
       <c r="DR9" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>39</v>
+        <v>43.27</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>8</v>
+        <v>11.93</v>
       </c>
       <c r="DY9" t="n">
-        <v>4.86</v>
+        <v>7.47</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.14</v>
+        <v>4.46</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.14</v>
+        <v>17.33</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="10">
@@ -4603,142 +4591,142 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" t="n">
         <v>7</v>
       </c>
-      <c r="C10" t="n">
-        <v>3</v>
-      </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.67</v>
+        <v>0.29</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="H10" t="n">
-        <v>129.67</v>
+        <v>116.29</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="K10" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="M10" t="n">
-        <v>68.67</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="O10" t="n">
-        <v>1.67</v>
+        <v>2.71</v>
       </c>
       <c r="P10" t="n">
-        <v>10.67</v>
+        <v>12</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.33</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>9</v>
+        <v>6.71</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>59.71</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH10" t="n">
         <v>2</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>62</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AI10" t="n">
-        <v>98.75</v>
+        <v>103.38</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="AM10" t="n">
         <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.75</v>
+        <v>66.75</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.75</v>
+        <v>11.62</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.75</v>
+        <v>11.75</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.5</v>
+        <v>7.12</v>
       </c>
       <c r="AT10" t="n">
         <v>0.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,148 +4738,148 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.75</v>
+        <v>55.62</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>14.62</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.75</v>
+        <v>9.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.25</v>
+        <v>5.12</v>
       </c>
       <c r="BD10" t="n">
-        <v>10</v>
+        <v>16.38</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.37</v>
+        <v>1.76</v>
       </c>
       <c r="BF10" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BG10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>6.43</v>
+        <v>7.87</v>
       </c>
       <c r="BI10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BP10" t="n">
-        <v>2.71</v>
+        <v>3.33</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.57</v>
+        <v>3.73</v>
       </c>
       <c r="BR10" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.29</v>
+        <v>3.52</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="CU10" t="n">
         <v>1.38</v>
@@ -4903,37 +4891,37 @@
         <v>1.93</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.71</v>
+        <v>3.94</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.29</v>
+        <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="DG10" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DH10" t="n">
-        <v>112</v>
+        <v>109.4</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
@@ -4942,58 +4930,58 @@
         <v>1.86</v>
       </c>
       <c r="DK10" t="n">
-        <v>4</v>
+        <v>4.73</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.57</v>
+        <v>0.4</v>
       </c>
       <c r="DM10" t="n">
-        <v>64.14</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.43</v>
+        <v>11.8</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.28</v>
+        <v>11.4</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.43</v>
+        <v>6.93</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.86</v>
+        <v>57.53</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.29</v>
+        <v>14.27</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.14</v>
+        <v>5.06</v>
       </c>
       <c r="EA10" t="n">
-        <v>12.71</v>
+        <v>17.87</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="EC10" t="n">
         <v>1.86</v>
@@ -5006,271 +4994,271 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
         <v>7</v>
       </c>
-      <c r="C11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="H11" t="n">
-        <v>104.17</v>
+        <v>105.12</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="L11" t="n">
-        <v>0.33</v>
+        <v>0.62</v>
       </c>
       <c r="M11" t="n">
-        <v>58.33</v>
+        <v>64.25</v>
       </c>
       <c r="N11" t="n">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="P11" t="n">
-        <v>11.83</v>
+        <v>11.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.67</v>
+        <v>14</v>
       </c>
       <c r="R11" t="n">
-        <v>5.83</v>
+        <v>6.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="T11" t="n">
         <v>0.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="V11" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>54.17</v>
+        <v>57.12</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.83</v>
+        <v>11.88</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>15.33</v>
+        <v>19.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>0.86</v>
       </c>
       <c r="AH11" t="n">
         <v>1</v>
       </c>
       <c r="AI11" t="n">
-        <v>102</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>5</v>
+        <v>1.57</v>
       </c>
       <c r="AL11" t="n">
         <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>49</v>
+        <v>58.71</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AP11" t="n">
-        <v>3</v>
+        <v>1.86</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>7.43</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>11.29</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>6.29</v>
       </c>
       <c r="AT11" t="n">
         <v>1</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>48</v>
+        <v>45.86</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1</v>
+        <v>0.14</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>10.29</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>6.86</v>
       </c>
       <c r="BC11" t="n">
-        <v>1</v>
+        <v>3.43</v>
       </c>
       <c r="BD11" t="n">
-        <v>18</v>
+        <v>18.14</v>
       </c>
       <c r="BE11" t="n">
-        <v>1</v>
+        <v>1.32</v>
       </c>
       <c r="BF11" t="n">
-        <v>3</v>
+        <v>1.29</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.289999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.57</v>
+        <v>0.4</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.14</v>
+        <v>0.47</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.43</v>
+        <v>0.87</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.14</v>
+        <v>3.67</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.14</v>
+        <v>4.6</v>
       </c>
       <c r="BR11" t="n">
-        <v>85.70999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.27</v>
+        <v>3.14</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.65</v>
+        <v>3.58</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="CF11" t="n">
         <v>3.23</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.94</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CM11" t="n">
         <v>1.84</v>
@@ -5279,22 +5267,22 @@
         <v>1.48</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CS11" t="n">
         <v>3.37</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="CU11" t="n">
         <v>1.34</v>
@@ -5306,100 +5294,100 @@
         <v>2.11</v>
       </c>
       <c r="CX11" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.61</v>
+        <v>4.79</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.14</v>
+        <v>2.13</v>
       </c>
       <c r="DH11" t="n">
-        <v>103.86</v>
+        <v>101.53</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.29</v>
+        <v>4.67</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="DM11" t="n">
-        <v>57</v>
+        <v>61.66</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.43</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.72</v>
+        <v>12.74</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.57</v>
+        <v>6.4</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.29</v>
+        <v>51.87</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.57</v>
+        <v>11.14</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.57</v>
+        <v>7.73</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="EA11" t="n">
-        <v>15.71</v>
+        <v>18.87</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="12">
@@ -5409,61 +5397,61 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" t="n">
         <v>7</v>
       </c>
-      <c r="C12" t="n">
-        <v>4</v>
-      </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="H12" t="n">
-        <v>114</v>
+        <v>115.71</v>
       </c>
       <c r="I12" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>5.57</v>
       </c>
       <c r="L12" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="M12" t="n">
-        <v>65.5</v>
+        <v>68.86</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.25</v>
+        <v>13.14</v>
       </c>
       <c r="R12" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5475,184 +5463,184 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>53.5</v>
+        <v>59.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.75</v>
+        <v>13.71</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.75</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AC12" t="n">
-        <v>12.5</v>
+        <v>18.86</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="n">
         <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>108.67</v>
+        <v>98</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.33</v>
+        <v>4.12</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>54.33</v>
+        <v>54.38</v>
       </c>
       <c r="AO12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>53.38</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ12" t="n">
         <v>0.33</v>
       </c>
-      <c r="AP12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>54.67</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.43</v>
-      </c>
       <c r="BK12" t="n">
-        <v>0.14</v>
+        <v>0.6</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.57</v>
+        <v>0.93</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.29</v>
+        <v>3.4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.14</v>
+        <v>4.2</v>
       </c>
       <c r="BR12" t="n">
-        <v>85.70999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>14.29</v>
+        <v>40</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>85.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.23</v>
+        <v>3.46</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF12" t="n">
         <v>2.93</v>
@@ -5661,46 +5649,46 @@
         <v>2.65</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.77</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV12" t="n">
         <v>2.03</v>
@@ -5709,67 +5697,67 @@
         <v>1.84</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="DB12" t="n">
         <v>1.35</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.69</v>
+        <v>3.75</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.14</v>
+        <v>2.67</v>
       </c>
       <c r="DH12" t="n">
-        <v>111.72</v>
+        <v>106.26</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.28</v>
+        <v>4.8</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
       <c r="DM12" t="n">
-        <v>60.71</v>
+        <v>61.14</v>
       </c>
       <c r="DN12" t="n">
         <v>0.86</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.14</v>
+        <v>12.73</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.14</v>
+        <v>12.4</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.14</v>
+        <v>6.93</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,28 +5769,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>54</v>
+        <v>56.07</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.28</v>
+        <v>12.2</v>
       </c>
       <c r="DY12" t="n">
-        <v>8</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.28</v>
+        <v>3.67</v>
       </c>
       <c r="EA12" t="n">
-        <v>14.57</v>
+        <v>18.73</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5800,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5827,76 +5815,76 @@
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3.12</v>
       </c>
       <c r="H13" t="n">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>5.62</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="M13" t="n">
-        <v>60</v>
+        <v>67.25</v>
       </c>
       <c r="N13" t="n">
         <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>9.5</v>
+        <v>8.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>6.62</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>35.5</v>
+        <v>45</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>17</v>
+        <v>15.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -5905,169 +5893,169 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>93.56999999999999</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
         <v>2</v>
       </c>
-      <c r="AH13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>96.25</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AL13" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.25</v>
+        <v>-0.14</v>
       </c>
       <c r="AN13" t="n">
-        <v>63.75</v>
+        <v>62.71</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.75</v>
+        <v>10.57</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.25</v>
+        <v>11.71</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.75</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>52</v>
+        <v>48.57</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.75</v>
+        <v>13.29</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.25</v>
+        <v>4.57</v>
       </c>
       <c r="BD13" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.33</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="BJ13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BK13" t="n">
         <v>0.67</v>
       </c>
-      <c r="BK13" t="n">
-        <v>0.33</v>
-      </c>
       <c r="BL13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="BN13" t="n">
         <v>1.33</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>1.47</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.5</v>
+        <v>4.53</v>
       </c>
       <c r="BR13" t="n">
-        <v>83.33</v>
+        <v>93.33</v>
       </c>
       <c r="BS13" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU13" t="n">
-        <v>16.67</v>
+        <v>26.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.52</v>
+        <v>2.17</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.17</v>
+        <v>3.27</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.36</v>
+        <v>3.46</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF13" t="n">
         <v>2.92</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.77</v>
@@ -6076,34 +6064,34 @@
         <v>1.76</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="CO13" t="n">
         <v>1.3</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV13" t="n">
         <v>2.04</v>
@@ -6112,100 +6100,100 @@
         <v>1.82</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CZ13" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DG13" t="n">
-        <v>2</v>
+        <v>2.73</v>
       </c>
       <c r="DH13" t="n">
-        <v>95.83</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="DI13" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.17</v>
+        <v>4.86</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.33</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM13" t="n">
-        <v>62.5</v>
+        <v>65.13</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="DP13" t="n">
-        <v>11</v>
+        <v>9.33</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.5</v>
+        <v>12.66</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.83</v>
+        <v>7.67</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.5</v>
+        <v>46.67</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.83</v>
+        <v>15.54</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.5</v>
+        <v>10.46</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.33</v>
+        <v>5.07</v>
       </c>
       <c r="EA13" t="n">
-        <v>13</v>
+        <v>16.87</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
